--- a/Base_Producao.xlsx
+++ b/Base_Producao.xlsx
@@ -503,7 +503,7 @@
       <c s="4" t="str" r="A5"/>
       <c s="6" t="inlineStr" r="AE5">
         <is>
-          <t xml:space="preserve">Emissão: 02/10/2026</t>
+          <t xml:space="preserve">Emissão: 05/10/2026</t>
         </is>
       </c>
       <c s="7" t="str" r="AG5"/>
@@ -512,7 +512,7 @@
       <c s="4" t="str" r="A6"/>
       <c s="8" t="inlineStr" r="G6">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 01/10/2026</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 04/10/2026</t>
         </is>
       </c>
       <c s="7" t="str" r="AG6"/>
@@ -6705,46 +6705,7587 @@
       </c>
       <c s="7" t="str" r="AG65"/>
     </row>
-    <row r="66" ht="14.7" customHeight="1">
-      <c s="21" t="inlineStr" r="A66">
-        <is>
-          <t xml:space="preserve">Peso Total: 68220,000</t>
-        </is>
-      </c>
-      <c s="13" t="str" r="B66"/>
-      <c s="13" t="str" r="C66"/>
-      <c s="13" t="str" r="D66"/>
-      <c s="13" t="str" r="E66"/>
-      <c s="13" t="str" r="F66"/>
-      <c s="13" t="str" r="G66"/>
-      <c s="13" t="str" r="H66"/>
-      <c s="13" t="str" r="I66"/>
-      <c s="13" t="str" r="J66"/>
-      <c s="13" t="str" r="K66"/>
-      <c s="13" t="str" r="L66"/>
-      <c s="13" t="str" r="M66"/>
-      <c s="13" t="str" r="N66"/>
-      <c s="13" t="str" r="O66"/>
-      <c s="13" t="str" r="P66"/>
-      <c s="13" t="str" r="Q66"/>
-      <c s="13" t="str" r="R66"/>
-      <c s="13" t="str" r="S66"/>
-      <c s="13" t="str" r="T66"/>
-      <c s="13" t="str" r="U66"/>
-      <c s="13" t="str" r="V66"/>
-      <c s="13" t="str" r="W66"/>
-      <c s="13" t="str" r="X66"/>
-      <c s="13" t="str" r="Y66"/>
-      <c s="13" t="str" r="Z66"/>
-      <c s="13" t="str" r="AA66"/>
-      <c s="13" t="str" r="AB66"/>
-      <c s="13" t="str" r="AC66"/>
-      <c s="13" t="str" r="AD66"/>
-      <c s="13" t="str" r="AE66"/>
-      <c s="13" t="str" r="AF66"/>
-      <c s="14" t="str" r="AG66"/>
+    <row r="66" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A66">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B66">
+        <is>
+          <t xml:space="preserve">07:31:47</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C66">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D66">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E66">
+        <v>200886</v>
+      </c>
+      <c s="16" t="inlineStr" r="F66">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,47mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H66">
+        <is>
+          <t xml:space="preserve">0,47mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I66">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J66">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K66">
+        <is>
+          <t xml:space="preserve">5012451755</t>
+        </is>
+      </c>
+      <c s="17" r="L66">
+        <v>2037.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M66">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N66">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O66"/>
+      <c s="16" t="str" r="P66"/>
+      <c s="16" t="str" r="Q66"/>
+      <c s="16" t="str" r="R66"/>
+      <c s="16" t="inlineStr" r="S66">
+        <is>
+          <t xml:space="preserve">2632005116</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T66"/>
+      <c s="16" t="inlineStr" r="U66">
+        <is>
+          <t xml:space="preserve">5001545391</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V66">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y66">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z66">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="17" r="AA66">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB66">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC66">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD66"/>
+      <c s="16" t="inlineStr" r="AF66">
+        <is>
+          <t xml:space="preserve">2003690479</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG66"/>
     </row>
-    <row r="67" ht="0.05" customHeight="1"/>
+    <row r="67" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A67">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B67">
+        <is>
+          <t xml:space="preserve">07:44:07</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C67">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D67">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E67">
+        <v>200716</v>
+      </c>
+      <c s="19" t="inlineStr" r="F67">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H67">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I67">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J67">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K67">
+        <is>
+          <t xml:space="preserve">5012451804</t>
+        </is>
+      </c>
+      <c s="20" r="L67">
+        <v>1369.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M67">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N67">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O67"/>
+      <c s="19" t="str" r="P67"/>
+      <c s="19" t="str" r="Q67"/>
+      <c s="19" t="str" r="R67"/>
+      <c s="19" t="inlineStr" r="S67">
+        <is>
+          <t xml:space="preserve">2636005744</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T67"/>
+      <c s="19" t="inlineStr" r="U67">
+        <is>
+          <t xml:space="preserve">5001545463</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V67">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y67">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z67">
+        <is>
+          <t xml:space="preserve">10046135    </t>
+        </is>
+      </c>
+      <c s="20" r="AA67">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB67">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC67">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD67"/>
+      <c s="19" t="inlineStr" r="AF67">
+        <is>
+          <t xml:space="preserve">2003908215</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG67"/>
+    </row>
+    <row r="68" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A68">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B68">
+        <is>
+          <t xml:space="preserve">07:46:11</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C68">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D68">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E68">
+        <v>200716</v>
+      </c>
+      <c s="16" t="inlineStr" r="F68">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H68">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I68">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J68">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K68">
+        <is>
+          <t xml:space="preserve">5012451821</t>
+        </is>
+      </c>
+      <c s="17" r="L68">
+        <v>112.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M68">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N68">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O68">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P68">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q68"/>
+      <c s="16" t="str" r="R68"/>
+      <c s="16" t="inlineStr" r="S68">
+        <is>
+          <t xml:space="preserve">2636005745</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T68"/>
+      <c s="16" t="inlineStr" r="U68">
+        <is>
+          <t xml:space="preserve">5001545474</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V68">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y68">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z68">
+        <is>
+          <t xml:space="preserve">10046135    </t>
+        </is>
+      </c>
+      <c s="17" r="AA68">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB68">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC68">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD68"/>
+      <c s="16" t="inlineStr" r="AF68">
+        <is>
+          <t xml:space="preserve">2003908215</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG68"/>
+    </row>
+    <row r="69" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A69">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B69">
+        <is>
+          <t xml:space="preserve">07:52:13</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C69">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D69">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E69">
+        <v>200886</v>
+      </c>
+      <c s="19" t="inlineStr" r="F69">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,47mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H69">
+        <is>
+          <t xml:space="preserve">0,47mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I69">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J69">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K69">
+        <is>
+          <t xml:space="preserve">5012451851</t>
+        </is>
+      </c>
+      <c s="20" r="L69">
+        <v>856.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M69">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N69">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O69"/>
+      <c s="19" t="str" r="P69"/>
+      <c s="19" t="str" r="Q69"/>
+      <c s="19" t="str" r="R69"/>
+      <c s="19" t="inlineStr" r="S69">
+        <is>
+          <t xml:space="preserve">2632005117</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T69"/>
+      <c s="19" t="inlineStr" r="U69">
+        <is>
+          <t xml:space="preserve">5001545524</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V69">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y69">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z69">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="20" r="AA69">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB69">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC69">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD69"/>
+      <c s="19" t="inlineStr" r="AF69">
+        <is>
+          <t xml:space="preserve">2003690479</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG69"/>
+    </row>
+    <row r="70" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A70">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B70">
+        <is>
+          <t xml:space="preserve">07:54:13</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C70">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D70">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E70">
+        <v>200746</v>
+      </c>
+      <c s="16" t="inlineStr" r="F70">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H70">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I70">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J70">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K70">
+        <is>
+          <t xml:space="preserve">5012451861</t>
+        </is>
+      </c>
+      <c s="17" r="L70">
+        <v>1005.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M70">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N70">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O70"/>
+      <c s="16" t="str" r="P70"/>
+      <c s="16" t="str" r="Q70"/>
+      <c s="16" t="str" r="R70"/>
+      <c s="16" t="inlineStr" r="S70">
+        <is>
+          <t xml:space="preserve">2636005746</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T70"/>
+      <c s="16" t="inlineStr" r="U70">
+        <is>
+          <t xml:space="preserve">5001545545</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V70">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y70">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z70">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="17" r="AA70">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB70">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC70">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD70">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF70">
+        <is>
+          <t xml:space="preserve">2003908393</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG70"/>
+    </row>
+    <row r="71" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A71">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B71">
+        <is>
+          <t xml:space="preserve">08:03:21</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C71">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D71">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E71">
+        <v>200746</v>
+      </c>
+      <c s="19" t="inlineStr" r="F71">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H71">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I71">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J71">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K71">
+        <is>
+          <t xml:space="preserve">5012451894</t>
+        </is>
+      </c>
+      <c s="20" r="L71">
+        <v>1058.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M71">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N71">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O71"/>
+      <c s="19" t="str" r="P71"/>
+      <c s="19" t="str" r="Q71"/>
+      <c s="19" t="str" r="R71"/>
+      <c s="19" t="inlineStr" r="S71">
+        <is>
+          <t xml:space="preserve">2636005747</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T71"/>
+      <c s="19" t="inlineStr" r="U71">
+        <is>
+          <t xml:space="preserve">5001545600</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V71">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y71">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z71">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" r="AA71">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB71">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC71">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD71">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF71">
+        <is>
+          <t xml:space="preserve">2003908393</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG71"/>
+    </row>
+    <row r="72" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A72">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B72">
+        <is>
+          <t xml:space="preserve">08:04:19</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C72">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D72">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E72">
+        <v>200886</v>
+      </c>
+      <c s="16" t="inlineStr" r="F72">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,47mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H72">
+        <is>
+          <t xml:space="preserve">0,47mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I72">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J72">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K72">
+        <is>
+          <t xml:space="preserve">5012451897</t>
+        </is>
+      </c>
+      <c s="17" r="L72">
+        <v>249.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M72">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N72">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O72">
+        <is>
+          <t xml:space="preserve">0072</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P72">
+        <is>
+          <t xml:space="preserve">TRV - Quebra de superfície</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q72"/>
+      <c s="16" t="str" r="R72"/>
+      <c s="16" t="inlineStr" r="S72">
+        <is>
+          <t xml:space="preserve">2632005118</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T72"/>
+      <c s="16" t="inlineStr" r="U72">
+        <is>
+          <t xml:space="preserve">5001545603</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V72">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y72">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z72">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="17" r="AA72">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB72">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC72">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD72"/>
+      <c s="16" t="inlineStr" r="AF72">
+        <is>
+          <t xml:space="preserve">2003690479</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG72"/>
+    </row>
+    <row r="73" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A73">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B73">
+        <is>
+          <t xml:space="preserve">08:18:19</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C73">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D73">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E73">
+        <v>200886</v>
+      </c>
+      <c s="19" t="inlineStr" r="F73">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,47mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H73">
+        <is>
+          <t xml:space="preserve">0,47mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I73">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J73">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K73">
+        <is>
+          <t xml:space="preserve">5012451962</t>
+        </is>
+      </c>
+      <c s="20" r="L73">
+        <v>1896.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M73">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N73">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O73"/>
+      <c s="19" t="str" r="P73"/>
+      <c s="19" t="str" r="Q73"/>
+      <c s="19" t="str" r="R73"/>
+      <c s="19" t="inlineStr" r="S73">
+        <is>
+          <t xml:space="preserve">2632005119</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T73"/>
+      <c s="19" t="inlineStr" r="U73">
+        <is>
+          <t xml:space="preserve">5001545696</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V73">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y73">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z73">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="20" r="AA73">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB73">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC73">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD73"/>
+      <c s="19" t="inlineStr" r="AF73">
+        <is>
+          <t xml:space="preserve">2003643805</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG73"/>
+    </row>
+    <row r="74" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A74">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B74">
+        <is>
+          <t xml:space="preserve">08:19:37</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C74">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D74">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E74">
+        <v>200746</v>
+      </c>
+      <c s="16" t="inlineStr" r="F74">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H74">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I74">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J74">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K74">
+        <is>
+          <t xml:space="preserve">5012451965</t>
+        </is>
+      </c>
+      <c s="17" r="L74">
+        <v>1109.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M74">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N74">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O74"/>
+      <c s="16" t="str" r="P74"/>
+      <c s="16" t="str" r="Q74"/>
+      <c s="16" t="str" r="R74"/>
+      <c s="16" t="inlineStr" r="S74">
+        <is>
+          <t xml:space="preserve">2636005748</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T74"/>
+      <c s="16" t="inlineStr" r="U74">
+        <is>
+          <t xml:space="preserve">5001545699</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V74">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y74">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z74">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="17" r="AA74">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB74">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC74">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD74">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF74">
+        <is>
+          <t xml:space="preserve">2003908393</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG74"/>
+    </row>
+    <row r="75" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A75">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B75">
+        <is>
+          <t xml:space="preserve">08:34:33</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C75">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D75">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E75">
+        <v>200886</v>
+      </c>
+      <c s="19" t="inlineStr" r="F75">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,47mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H75">
+        <is>
+          <t xml:space="preserve">0,47mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I75">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J75">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K75">
+        <is>
+          <t xml:space="preserve">5012452038</t>
+        </is>
+      </c>
+      <c s="20" r="L75">
+        <v>1896.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M75">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N75">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O75"/>
+      <c s="19" t="str" r="P75"/>
+      <c s="19" t="str" r="Q75"/>
+      <c s="19" t="str" r="R75"/>
+      <c s="19" t="inlineStr" r="S75">
+        <is>
+          <t xml:space="preserve">2632005120</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T75"/>
+      <c s="19" t="inlineStr" r="U75">
+        <is>
+          <t xml:space="preserve">5001545830</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V75">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y75">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z75">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="20" r="AA75">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB75">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC75">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD75"/>
+      <c s="19" t="inlineStr" r="AF75">
+        <is>
+          <t xml:space="preserve">2003643805</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG75"/>
+    </row>
+    <row r="76" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A76">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B76">
+        <is>
+          <t xml:space="preserve">08:35:42</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C76">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D76">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E76">
+        <v>200746</v>
+      </c>
+      <c s="16" t="inlineStr" r="F76">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H76">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I76">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J76">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K76">
+        <is>
+          <t xml:space="preserve">5012452043</t>
+        </is>
+      </c>
+      <c s="17" r="L76">
+        <v>1110.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M76">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N76">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O76"/>
+      <c s="16" t="str" r="P76"/>
+      <c s="16" t="str" r="Q76"/>
+      <c s="16" t="str" r="R76"/>
+      <c s="16" t="inlineStr" r="S76">
+        <is>
+          <t xml:space="preserve">2636005749</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T76"/>
+      <c s="16" t="inlineStr" r="U76">
+        <is>
+          <t xml:space="preserve">5001545836</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V76">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y76">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z76">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="17" r="AA76">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB76">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC76">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD76">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF76">
+        <is>
+          <t xml:space="preserve">2003908393</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG76"/>
+    </row>
+    <row r="77" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A77">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B77">
+        <is>
+          <t xml:space="preserve">08:51:03</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C77">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D77">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E77">
+        <v>200886</v>
+      </c>
+      <c s="19" t="inlineStr" r="F77">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,47mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H77">
+        <is>
+          <t xml:space="preserve">0,47mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I77">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J77">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K77">
+        <is>
+          <t xml:space="preserve">5012452112</t>
+        </is>
+      </c>
+      <c s="20" r="L77">
+        <v>1985.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M77">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N77">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O77"/>
+      <c s="19" t="str" r="P77"/>
+      <c s="19" t="str" r="Q77"/>
+      <c s="19" t="str" r="R77"/>
+      <c s="19" t="inlineStr" r="S77">
+        <is>
+          <t xml:space="preserve">2632005121</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T77"/>
+      <c s="19" t="inlineStr" r="U77">
+        <is>
+          <t xml:space="preserve">5001545947</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V77">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y77">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z77">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="20" r="AA77">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB77">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC77">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD77"/>
+      <c s="19" t="inlineStr" r="AF77">
+        <is>
+          <t xml:space="preserve">2003643805</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG77"/>
+    </row>
+    <row r="78" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A78">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B78">
+        <is>
+          <t xml:space="preserve">08:51:34</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C78">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D78">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E78">
+        <v>200746</v>
+      </c>
+      <c s="16" t="inlineStr" r="F78">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H78">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I78">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J78">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K78">
+        <is>
+          <t xml:space="preserve">5012452113</t>
+        </is>
+      </c>
+      <c s="17" r="L78">
+        <v>1108.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M78">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N78">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O78"/>
+      <c s="16" t="str" r="P78"/>
+      <c s="16" t="str" r="Q78"/>
+      <c s="16" t="str" r="R78"/>
+      <c s="16" t="inlineStr" r="S78">
+        <is>
+          <t xml:space="preserve">2636005750</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T78"/>
+      <c s="16" t="inlineStr" r="U78">
+        <is>
+          <t xml:space="preserve">5001545948</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V78">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y78">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z78">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="17" r="AA78">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB78">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC78">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD78">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF78">
+        <is>
+          <t xml:space="preserve">2003908393</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG78"/>
+    </row>
+    <row r="79" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A79">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B79">
+        <is>
+          <t xml:space="preserve">09:09:30</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C79">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D79">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E79">
+        <v>200886</v>
+      </c>
+      <c s="19" t="inlineStr" r="F79">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,47mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H79">
+        <is>
+          <t xml:space="preserve">0,47mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I79">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J79">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K79">
+        <is>
+          <t xml:space="preserve">5012452156</t>
+        </is>
+      </c>
+      <c s="20" r="L79">
+        <v>2131.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M79">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N79">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O79"/>
+      <c s="19" t="str" r="P79"/>
+      <c s="19" t="str" r="Q79"/>
+      <c s="19" t="str" r="R79"/>
+      <c s="19" t="inlineStr" r="S79">
+        <is>
+          <t xml:space="preserve">2632005122</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T79"/>
+      <c s="19" t="inlineStr" r="U79">
+        <is>
+          <t xml:space="preserve">5001546015</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V79">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y79">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z79">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="20" r="AA79">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB79">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC79">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD79"/>
+      <c s="19" t="inlineStr" r="AF79">
+        <is>
+          <t xml:space="preserve">2003643805</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG79"/>
+    </row>
+    <row r="80" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A80">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B80">
+        <is>
+          <t xml:space="preserve">09:17:23</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C80">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D80">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E80">
+        <v>200746</v>
+      </c>
+      <c s="16" t="inlineStr" r="F80">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H80">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I80">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J80">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K80">
+        <is>
+          <t xml:space="preserve">5012452166</t>
+        </is>
+      </c>
+      <c s="17" r="L80">
+        <v>1107.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M80">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N80">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O80"/>
+      <c s="16" t="str" r="P80"/>
+      <c s="16" t="str" r="Q80"/>
+      <c s="16" t="str" r="R80"/>
+      <c s="16" t="inlineStr" r="S80">
+        <is>
+          <t xml:space="preserve">2636005751</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T80"/>
+      <c s="16" t="inlineStr" r="U80">
+        <is>
+          <t xml:space="preserve">5001546037</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V80">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y80">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z80">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="17" r="AA80">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB80">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC80">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD80">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF80">
+        <is>
+          <t xml:space="preserve">2003908393</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG80"/>
+    </row>
+    <row r="81" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A81">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B81">
+        <is>
+          <t xml:space="preserve">09:23:44</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C81">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D81">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E81">
+        <v>200886</v>
+      </c>
+      <c s="19" t="inlineStr" r="F81">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,47mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H81">
+        <is>
+          <t xml:space="preserve">0,47mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I81">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J81">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K81">
+        <is>
+          <t xml:space="preserve">5012452178</t>
+        </is>
+      </c>
+      <c s="20" r="L81">
+        <v>109.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M81">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N81">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O81">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P81">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q81"/>
+      <c s="19" t="str" r="R81"/>
+      <c s="19" t="inlineStr" r="S81">
+        <is>
+          <t xml:space="preserve">2632005123</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T81"/>
+      <c s="19" t="inlineStr" r="U81">
+        <is>
+          <t xml:space="preserve">5001546059</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V81">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y81">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z81">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="20" r="AA81">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB81">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC81">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD81"/>
+      <c s="19" t="inlineStr" r="AF81">
+        <is>
+          <t xml:space="preserve">2003643805</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG81"/>
+    </row>
+    <row r="82" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A82">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B82">
+        <is>
+          <t xml:space="preserve">09:52:47</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C82">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D82">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E82">
+        <v>200746</v>
+      </c>
+      <c s="16" t="inlineStr" r="F82">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H82">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I82">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J82">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K82">
+        <is>
+          <t xml:space="preserve">5012452302</t>
+        </is>
+      </c>
+      <c s="17" r="L82">
+        <v>1110.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M82">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N82">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O82"/>
+      <c s="16" t="str" r="P82"/>
+      <c s="16" t="str" r="Q82"/>
+      <c s="16" t="str" r="R82"/>
+      <c s="16" t="inlineStr" r="S82">
+        <is>
+          <t xml:space="preserve">2636005752</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T82"/>
+      <c s="16" t="inlineStr" r="U82">
+        <is>
+          <t xml:space="preserve">5001546340</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V82">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y82">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z82">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="17" r="AA82">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB82">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC82">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD82">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF82">
+        <is>
+          <t xml:space="preserve">2003908393</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG82"/>
+    </row>
+    <row r="83" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A83">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B83">
+        <is>
+          <t xml:space="preserve">10:00:16</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C83">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D83">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E83">
+        <v>222131</v>
+      </c>
+      <c s="19" t="inlineStr" r="F83">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 3000mm X 1200mm CN</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H83">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I83">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J83">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K83">
+        <is>
+          <t xml:space="preserve">5012452331</t>
+        </is>
+      </c>
+      <c s="20" r="L83">
+        <v>2020.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M83">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N83">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O83"/>
+      <c s="19" t="str" r="P83"/>
+      <c s="19" t="str" r="Q83"/>
+      <c s="19" t="str" r="R83"/>
+      <c s="19" t="inlineStr" r="S83">
+        <is>
+          <t xml:space="preserve">2632005124</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T83"/>
+      <c s="19" t="inlineStr" r="U83">
+        <is>
+          <t xml:space="preserve">5001546395</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V83">
+        <is>
+          <t xml:space="preserve">20131549</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y83">
+        <is>
+          <t xml:space="preserve">FRANCISCO ALEXANDRE MIRANDA EUFRASI</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z83">
+        <is>
+          <t xml:space="preserve">10047017    </t>
+        </is>
+      </c>
+      <c s="20" r="AA83">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB83">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC83">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD83"/>
+      <c s="19" t="inlineStr" r="AF83">
+        <is>
+          <t xml:space="preserve">2003936126</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG83"/>
+    </row>
+    <row r="84" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A84">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B84">
+        <is>
+          <t xml:space="preserve">10:06:17</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C84">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D84">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E84">
+        <v>200746</v>
+      </c>
+      <c s="16" t="inlineStr" r="F84">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H84">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I84">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J84">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K84">
+        <is>
+          <t xml:space="preserve">5012452342</t>
+        </is>
+      </c>
+      <c s="17" r="L84">
+        <v>1108.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M84">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N84">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O84"/>
+      <c s="16" t="str" r="P84"/>
+      <c s="16" t="str" r="Q84"/>
+      <c s="16" t="str" r="R84"/>
+      <c s="16" t="inlineStr" r="S84">
+        <is>
+          <t xml:space="preserve">2636005753</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T84"/>
+      <c s="16" t="inlineStr" r="U84">
+        <is>
+          <t xml:space="preserve">5001546407</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V84">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y84">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z84">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="17" r="AA84">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB84">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC84">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD84">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF84">
+        <is>
+          <t xml:space="preserve">2003908392</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG84"/>
+    </row>
+    <row r="85" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A85">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B85">
+        <is>
+          <t xml:space="preserve">10:12:08</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C85">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D85">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E85">
+        <v>222131</v>
+      </c>
+      <c s="19" t="inlineStr" r="F85">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 3000mm X 1200mm CN</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H85">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I85">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J85">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K85">
+        <is>
+          <t xml:space="preserve">5012452364</t>
+        </is>
+      </c>
+      <c s="20" r="L85">
+        <v>2020.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M85">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N85">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O85"/>
+      <c s="19" t="str" r="P85"/>
+      <c s="19" t="str" r="Q85"/>
+      <c s="19" t="str" r="R85"/>
+      <c s="19" t="inlineStr" r="S85">
+        <is>
+          <t xml:space="preserve">2632005125</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T85"/>
+      <c s="19" t="inlineStr" r="U85">
+        <is>
+          <t xml:space="preserve">5001546442</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V85">
+        <is>
+          <t xml:space="preserve">20131549</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y85">
+        <is>
+          <t xml:space="preserve">FRANCISCO ALEXANDRE MIRANDA EUFRASI</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z85">
+        <is>
+          <t xml:space="preserve">10047017    </t>
+        </is>
+      </c>
+      <c s="20" r="AA85">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB85">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC85">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD85"/>
+      <c s="19" t="inlineStr" r="AF85">
+        <is>
+          <t xml:space="preserve">2003936126</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG85"/>
+    </row>
+    <row r="86" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A86">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B86">
+        <is>
+          <t xml:space="preserve">10:15:06</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C86">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D86">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E86">
+        <v>200735</v>
+      </c>
+      <c s="16" t="inlineStr" r="F86">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H86">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I86">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J86">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K86">
+        <is>
+          <t xml:space="preserve">5012452376</t>
+        </is>
+      </c>
+      <c s="17" r="L86">
+        <v>2150.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M86">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N86">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O86">
+        <is>
+          <t xml:space="preserve">0071</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P86">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação galvânica</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q86"/>
+      <c s="16" t="str" r="R86"/>
+      <c s="16" t="inlineStr" r="S86">
+        <is>
+          <t xml:space="preserve">2632005126</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T86"/>
+      <c s="16" t="inlineStr" r="U86">
+        <is>
+          <t xml:space="preserve">5001546474</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V86">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y86">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z86">
+        <is>
+          <t xml:space="preserve">10046879    </t>
+        </is>
+      </c>
+      <c s="17" r="AA86">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB86">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC86">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD86"/>
+      <c s="16" t="inlineStr" r="AF86">
+        <is>
+          <t xml:space="preserve">2003936126</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG86"/>
+    </row>
+    <row r="87" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A87">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B87">
+        <is>
+          <t xml:space="preserve">10:15:48</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C87">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D87">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E87">
+        <v>200735</v>
+      </c>
+      <c s="19" t="inlineStr" r="F87">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H87">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I87">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J87">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K87">
+        <is>
+          <t xml:space="preserve">5012452382</t>
+        </is>
+      </c>
+      <c s="20" r="L87">
+        <v>2046.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M87">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N87">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O87"/>
+      <c s="19" t="str" r="P87"/>
+      <c s="19" t="str" r="Q87"/>
+      <c s="19" t="str" r="R87"/>
+      <c s="19" t="inlineStr" r="S87">
+        <is>
+          <t xml:space="preserve">2632005127</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T87"/>
+      <c s="19" t="inlineStr" r="U87">
+        <is>
+          <t xml:space="preserve">5001546501</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V87">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y87">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z87">
+        <is>
+          <t xml:space="preserve">10046879    </t>
+        </is>
+      </c>
+      <c s="20" r="AA87">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB87">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC87">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD87"/>
+      <c s="19" t="inlineStr" r="AF87">
+        <is>
+          <t xml:space="preserve">2003936126</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG87"/>
+    </row>
+    <row r="88" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A88">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B88">
+        <is>
+          <t xml:space="preserve">10:34:39</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C88">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D88">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E88">
+        <v>200746</v>
+      </c>
+      <c s="16" t="inlineStr" r="F88">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H88">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I88">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J88">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K88">
+        <is>
+          <t xml:space="preserve">5012452457</t>
+        </is>
+      </c>
+      <c s="17" r="L88">
+        <v>1106.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M88">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N88">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O88"/>
+      <c s="16" t="str" r="P88"/>
+      <c s="16" t="str" r="Q88"/>
+      <c s="16" t="str" r="R88"/>
+      <c s="16" t="inlineStr" r="S88">
+        <is>
+          <t xml:space="preserve">2636005754</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T88"/>
+      <c s="16" t="inlineStr" r="U88">
+        <is>
+          <t xml:space="preserve">5001546798</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V88">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y88">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z88">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="17" r="AA88">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB88">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC88">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD88">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF88">
+        <is>
+          <t xml:space="preserve">2003908392</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG88"/>
+    </row>
+    <row r="89" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A89">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B89">
+        <is>
+          <t xml:space="preserve">10:37:34</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C89">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D89">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E89">
+        <v>200735</v>
+      </c>
+      <c s="19" t="inlineStr" r="F89">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H89">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I89">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J89">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K89">
+        <is>
+          <t xml:space="preserve">5012452464</t>
+        </is>
+      </c>
+      <c s="20" r="L89">
+        <v>1364.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M89">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N89">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O89"/>
+      <c s="19" t="str" r="P89"/>
+      <c s="19" t="str" r="Q89"/>
+      <c s="19" t="str" r="R89"/>
+      <c s="19" t="inlineStr" r="S89">
+        <is>
+          <t xml:space="preserve">2632005128</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T89"/>
+      <c s="19" t="inlineStr" r="U89">
+        <is>
+          <t xml:space="preserve">5001546815</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V89">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y89">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z89">
+        <is>
+          <t xml:space="preserve">10046879    </t>
+        </is>
+      </c>
+      <c s="20" r="AA89">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB89">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC89">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD89"/>
+      <c s="19" t="inlineStr" r="AF89">
+        <is>
+          <t xml:space="preserve">2003936126</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG89"/>
+    </row>
+    <row r="90" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A90">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B90">
+        <is>
+          <t xml:space="preserve">10:39:41</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C90">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D90">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E90">
+        <v>200695</v>
+      </c>
+      <c s="16" t="inlineStr" r="F90">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H90">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I90">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J90">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K90">
+        <is>
+          <t xml:space="preserve">5012452468</t>
+        </is>
+      </c>
+      <c s="17" r="L90">
+        <v>229.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M90">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N90">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O90">
+        <is>
+          <t xml:space="preserve">0072</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P90">
+        <is>
+          <t xml:space="preserve">TRV - Quebra de superfície</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q90"/>
+      <c s="16" t="str" r="R90"/>
+      <c s="16" t="inlineStr" r="S90">
+        <is>
+          <t xml:space="preserve">2632005129</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T90"/>
+      <c s="16" t="inlineStr" r="U90">
+        <is>
+          <t xml:space="preserve">5001546832</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V90">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y90">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z90">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="17" r="AA90">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB90">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC90">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD90"/>
+      <c s="16" t="inlineStr" r="AF90">
+        <is>
+          <t xml:space="preserve">2003935927</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG90"/>
+    </row>
+    <row r="91" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A91">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B91">
+        <is>
+          <t xml:space="preserve">10:59:23</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C91">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D91">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E91">
+        <v>200695</v>
+      </c>
+      <c s="19" t="inlineStr" r="F91">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H91">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I91">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J91">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K91">
+        <is>
+          <t xml:space="preserve">5012452543</t>
+        </is>
+      </c>
+      <c s="20" r="L91">
+        <v>2037.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M91">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N91">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O91"/>
+      <c s="19" t="str" r="P91"/>
+      <c s="19" t="str" r="Q91"/>
+      <c s="19" t="str" r="R91"/>
+      <c s="19" t="inlineStr" r="S91">
+        <is>
+          <t xml:space="preserve">2632005130</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T91"/>
+      <c s="19" t="inlineStr" r="U91">
+        <is>
+          <t xml:space="preserve">5001546964</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V91">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y91">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z91">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="20" r="AA91">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB91">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC91">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD91"/>
+      <c s="19" t="inlineStr" r="AF91">
+        <is>
+          <t xml:space="preserve">2003935927</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG91"/>
+    </row>
+    <row r="92" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A92">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B92">
+        <is>
+          <t xml:space="preserve">11:00:30</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C92">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D92">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E92">
+        <v>200746</v>
+      </c>
+      <c s="16" t="inlineStr" r="F92">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H92">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I92">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J92">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K92">
+        <is>
+          <t xml:space="preserve">5012452547</t>
+        </is>
+      </c>
+      <c s="17" r="L92">
+        <v>990.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M92">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N92">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O92"/>
+      <c s="16" t="str" r="P92"/>
+      <c s="16" t="str" r="Q92"/>
+      <c s="16" t="str" r="R92"/>
+      <c s="16" t="inlineStr" r="S92">
+        <is>
+          <t xml:space="preserve">2636005755</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T92"/>
+      <c s="16" t="inlineStr" r="U92">
+        <is>
+          <t xml:space="preserve">5001546968</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V92">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y92">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z92">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="17" r="AA92">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB92">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC92">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD92">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF92">
+        <is>
+          <t xml:space="preserve">2003908392</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG92"/>
+    </row>
+    <row r="93" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A93">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B93">
+        <is>
+          <t xml:space="preserve">11:03:54</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C93">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D93">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E93">
+        <v>200695</v>
+      </c>
+      <c s="19" t="inlineStr" r="F93">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H93">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I93">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J93">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K93">
+        <is>
+          <t xml:space="preserve">5012452543</t>
+        </is>
+      </c>
+      <c s="20" r="L93">
+        <v>-2037.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M93">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N93">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O93"/>
+      <c s="19" t="str" r="P93"/>
+      <c s="19" t="str" r="Q93"/>
+      <c s="19" t="str" r="R93"/>
+      <c s="19" t="inlineStr" r="S93">
+        <is>
+          <t xml:space="preserve">2632005130</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T93"/>
+      <c s="19" t="inlineStr" r="U93">
+        <is>
+          <t xml:space="preserve">5001547002</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V93">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y93">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z93">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="20" r="AA93">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB93">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC93">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD93"/>
+      <c s="19" t="str" r="AF93"/>
+      <c s="7" t="str" r="AG93"/>
+    </row>
+    <row r="94" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A94">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B94">
+        <is>
+          <t xml:space="preserve">11:23:27</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C94">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D94">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E94">
+        <v>200695</v>
+      </c>
+      <c s="16" t="inlineStr" r="F94">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H94">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I94">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J94">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K94">
+        <is>
+          <t xml:space="preserve">5012452591</t>
+        </is>
+      </c>
+      <c s="17" r="L94">
+        <v>2037.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M94">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N94">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O94">
+        <is>
+          <t xml:space="preserve">0073</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P94">
+        <is>
+          <t xml:space="preserve">TRV - Variação de comprimento</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q94"/>
+      <c s="16" t="str" r="R94"/>
+      <c s="16" t="inlineStr" r="S94">
+        <is>
+          <t xml:space="preserve">2632005131</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T94"/>
+      <c s="16" t="inlineStr" r="U94">
+        <is>
+          <t xml:space="preserve">5001547092</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V94">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y94">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z94">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="17" r="AA94">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB94">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC94">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD94"/>
+      <c s="16" t="inlineStr" r="AF94">
+        <is>
+          <t xml:space="preserve">2003935927</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG94"/>
+    </row>
+    <row r="95" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A95">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B95">
+        <is>
+          <t xml:space="preserve">11:25:08</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C95">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D95">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E95">
+        <v>200695</v>
+      </c>
+      <c s="19" t="inlineStr" r="F95">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H95">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I95">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J95">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K95">
+        <is>
+          <t xml:space="preserve">5012452594</t>
+        </is>
+      </c>
+      <c s="20" r="L95">
+        <v>555.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M95">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N95">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O95">
+        <is>
+          <t xml:space="preserve">0073</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P95">
+        <is>
+          <t xml:space="preserve">TRV - Variação de comprimento</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q95"/>
+      <c s="19" t="str" r="R95"/>
+      <c s="19" t="inlineStr" r="S95">
+        <is>
+          <t xml:space="preserve">2632005132</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T95"/>
+      <c s="19" t="inlineStr" r="U95">
+        <is>
+          <t xml:space="preserve">5001547097</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V95">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y95">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z95">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="20" r="AA95">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB95">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC95">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD95"/>
+      <c s="19" t="inlineStr" r="AF95">
+        <is>
+          <t xml:space="preserve">2003935927</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG95"/>
+    </row>
+    <row r="96" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A96">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B96">
+        <is>
+          <t xml:space="preserve">11:33:22</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C96">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D96">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E96">
+        <v>200695</v>
+      </c>
+      <c s="16" t="inlineStr" r="F96">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H96">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I96">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J96">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K96">
+        <is>
+          <t xml:space="preserve">5012452617</t>
+        </is>
+      </c>
+      <c s="17" r="L96">
+        <v>2034.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M96">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N96">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O96"/>
+      <c s="16" t="str" r="P96"/>
+      <c s="16" t="str" r="Q96"/>
+      <c s="16" t="str" r="R96"/>
+      <c s="16" t="inlineStr" r="S96">
+        <is>
+          <t xml:space="preserve">2632005133</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T96"/>
+      <c s="16" t="inlineStr" r="U96">
+        <is>
+          <t xml:space="preserve">5001547239</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V96">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y96">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z96">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="17" r="AA96">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB96">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC96">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD96"/>
+      <c s="16" t="inlineStr" r="AF96">
+        <is>
+          <t xml:space="preserve">2003935927</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG96"/>
+    </row>
+    <row r="97" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A97">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B97">
+        <is>
+          <t xml:space="preserve">12:14:00</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C97">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D97">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E97">
+        <v>222336</v>
+      </c>
+      <c s="19" t="inlineStr" r="F97">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1000mm CN</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H97">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I97">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J97">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K97">
+        <is>
+          <t xml:space="preserve">5012452701</t>
+        </is>
+      </c>
+      <c s="20" r="L97">
+        <v>2000.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M97">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N97">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O97"/>
+      <c s="19" t="str" r="P97"/>
+      <c s="19" t="str" r="Q97"/>
+      <c s="19" t="str" r="R97"/>
+      <c s="19" t="inlineStr" r="S97">
+        <is>
+          <t xml:space="preserve">2635002608</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T97"/>
+      <c s="19" t="inlineStr" r="U97">
+        <is>
+          <t xml:space="preserve">5001547429</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V97">
+        <is>
+          <t xml:space="preserve">20131549</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y97">
+        <is>
+          <t xml:space="preserve">FRANCISCO ALEXANDRE MIRANDA EUFRASI</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z97">
+        <is>
+          <t xml:space="preserve">10047019    </t>
+        </is>
+      </c>
+      <c s="20" r="AA97">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB97">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC97">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD97"/>
+      <c s="19" t="inlineStr" r="AF97">
+        <is>
+          <t xml:space="preserve">2003896512</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG97"/>
+    </row>
+    <row r="98" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A98">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B98">
+        <is>
+          <t xml:space="preserve">12:18:23</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C98">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D98">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E98">
+        <v>200746</v>
+      </c>
+      <c s="16" t="inlineStr" r="F98">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H98">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I98">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J98">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K98">
+        <is>
+          <t xml:space="preserve">5012452728</t>
+        </is>
+      </c>
+      <c s="17" r="L98">
+        <v>988.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M98">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N98">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O98"/>
+      <c s="16" t="str" r="P98"/>
+      <c s="16" t="str" r="Q98"/>
+      <c s="16" t="str" r="R98"/>
+      <c s="16" t="inlineStr" r="S98">
+        <is>
+          <t xml:space="preserve">2636005756</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T98"/>
+      <c s="16" t="inlineStr" r="U98">
+        <is>
+          <t xml:space="preserve">5001547485</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V98">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y98">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z98">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="17" r="AA98">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB98">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC98">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD98">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF98">
+        <is>
+          <t xml:space="preserve">2003908392</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG98"/>
+    </row>
+    <row r="99" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A99">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B99">
+        <is>
+          <t xml:space="preserve">12:18:54</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C99">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D99">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E99">
+        <v>200695</v>
+      </c>
+      <c s="19" t="inlineStr" r="F99">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H99">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I99">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J99">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K99">
+        <is>
+          <t xml:space="preserve">5012452729</t>
+        </is>
+      </c>
+      <c s="20" r="L99">
+        <v>1118.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M99">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N99">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O99"/>
+      <c s="19" t="str" r="P99"/>
+      <c s="19" t="str" r="Q99"/>
+      <c s="19" t="str" r="R99"/>
+      <c s="19" t="inlineStr" r="S99">
+        <is>
+          <t xml:space="preserve">2632005134</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T99"/>
+      <c s="19" t="inlineStr" r="U99">
+        <is>
+          <t xml:space="preserve">5001547486</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V99">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y99">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z99">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="20" r="AA99">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB99">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC99">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD99"/>
+      <c s="19" t="inlineStr" r="AF99">
+        <is>
+          <t xml:space="preserve">2003935927</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG99"/>
+    </row>
+    <row r="100" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A100">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B100">
+        <is>
+          <t xml:space="preserve">12:20:30</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C100">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D100">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E100">
+        <v>200695</v>
+      </c>
+      <c s="16" t="inlineStr" r="F100">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H100">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I100">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J100">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K100">
+        <is>
+          <t xml:space="preserve">5012452733</t>
+        </is>
+      </c>
+      <c s="17" r="L100">
+        <v>411.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M100">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N100">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O100">
+        <is>
+          <t xml:space="preserve">0152</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P100">
+        <is>
+          <t xml:space="preserve">TRV - Fora de especificação</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q100"/>
+      <c s="16" t="str" r="R100"/>
+      <c s="16" t="inlineStr" r="S100">
+        <is>
+          <t xml:space="preserve">2632005135</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T100"/>
+      <c s="16" t="inlineStr" r="U100">
+        <is>
+          <t xml:space="preserve">5001547500</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V100">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y100">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z100">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="17" r="AA100">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB100">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC100">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD100"/>
+      <c s="16" t="inlineStr" r="AF100">
+        <is>
+          <t xml:space="preserve">2003935927</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG100"/>
+    </row>
+    <row r="101" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A101">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B101">
+        <is>
+          <t xml:space="preserve">12:23:09</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C101">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D101">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E101">
+        <v>200716</v>
+      </c>
+      <c s="19" t="inlineStr" r="F101">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H101">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I101">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J101">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K101">
+        <is>
+          <t xml:space="preserve">5012452735</t>
+        </is>
+      </c>
+      <c s="20" r="L101">
+        <v>2034.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M101">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N101">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O101"/>
+      <c s="19" t="str" r="P101"/>
+      <c s="19" t="str" r="Q101"/>
+      <c s="19" t="str" r="R101"/>
+      <c s="19" t="inlineStr" r="S101">
+        <is>
+          <t xml:space="preserve">2635002609</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T101"/>
+      <c s="19" t="inlineStr" r="U101">
+        <is>
+          <t xml:space="preserve">5001547502</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V101">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y101">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z101">
+        <is>
+          <t xml:space="preserve">10046882    </t>
+        </is>
+      </c>
+      <c s="20" r="AA101">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB101">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC101">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD101"/>
+      <c s="19" t="inlineStr" r="AF101">
+        <is>
+          <t xml:space="preserve">2003908219</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG101"/>
+    </row>
+    <row r="102" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A102">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B102">
+        <is>
+          <t xml:space="preserve">12:23:26</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C102">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D102">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E102">
+        <v>200716</v>
+      </c>
+      <c s="16" t="inlineStr" r="F102">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H102">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I102">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J102">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K102">
+        <is>
+          <t xml:space="preserve">5012452736</t>
+        </is>
+      </c>
+      <c s="17" r="L102">
+        <v>2066.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M102">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N102">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O102"/>
+      <c s="16" t="str" r="P102"/>
+      <c s="16" t="str" r="Q102"/>
+      <c s="16" t="str" r="R102"/>
+      <c s="16" t="inlineStr" r="S102">
+        <is>
+          <t xml:space="preserve">2635002610</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T102"/>
+      <c s="16" t="inlineStr" r="U102">
+        <is>
+          <t xml:space="preserve">5001547503</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V102">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y102">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z102">
+        <is>
+          <t xml:space="preserve">10046882    </t>
+        </is>
+      </c>
+      <c s="17" r="AA102">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB102">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC102">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD102"/>
+      <c s="16" t="inlineStr" r="AF102">
+        <is>
+          <t xml:space="preserve">2003908219</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG102"/>
+    </row>
+    <row r="103" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A103">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B103">
+        <is>
+          <t xml:space="preserve">12:32:52</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C103">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D103">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E103">
+        <v>200695</v>
+      </c>
+      <c s="19" t="inlineStr" r="F103">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H103">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I103">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J103">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K103">
+        <is>
+          <t xml:space="preserve">5012452755</t>
+        </is>
+      </c>
+      <c s="20" r="L103">
+        <v>2036.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M103">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N103">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O103"/>
+      <c s="19" t="str" r="P103"/>
+      <c s="19" t="str" r="Q103"/>
+      <c s="19" t="str" r="R103"/>
+      <c s="19" t="inlineStr" r="S103">
+        <is>
+          <t xml:space="preserve">2632005136</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T103"/>
+      <c s="19" t="inlineStr" r="U103">
+        <is>
+          <t xml:space="preserve">5001547522</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V103">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y103">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z103">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="20" r="AA103">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB103">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC103">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD103"/>
+      <c s="19" t="inlineStr" r="AF103">
+        <is>
+          <t xml:space="preserve">2003935928</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG103"/>
+    </row>
+    <row r="104" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A104">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B104">
+        <is>
+          <t xml:space="preserve">12:41:09</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C104">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D104">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E104">
+        <v>200716</v>
+      </c>
+      <c s="16" t="inlineStr" r="F104">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H104">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I104">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J104">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K104">
+        <is>
+          <t xml:space="preserve">5012452768</t>
+        </is>
+      </c>
+      <c s="17" r="L104">
+        <v>2015.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M104">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N104">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O104"/>
+      <c s="16" t="str" r="P104"/>
+      <c s="16" t="str" r="Q104"/>
+      <c s="16" t="str" r="R104"/>
+      <c s="16" t="inlineStr" r="S104">
+        <is>
+          <t xml:space="preserve">2635002611</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T104"/>
+      <c s="16" t="inlineStr" r="U104">
+        <is>
+          <t xml:space="preserve">5001547555</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V104">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y104">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z104">
+        <is>
+          <t xml:space="preserve">10046882    </t>
+        </is>
+      </c>
+      <c s="17" r="AA104">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB104">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC104">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD104"/>
+      <c s="16" t="inlineStr" r="AF104">
+        <is>
+          <t xml:space="preserve">2003908219</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG104"/>
+    </row>
+    <row r="105" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A105">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B105">
+        <is>
+          <t xml:space="preserve">12:54:35</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C105">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D105">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E105">
+        <v>200716</v>
+      </c>
+      <c s="19" t="inlineStr" r="F105">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H105">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I105">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J105">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K105">
+        <is>
+          <t xml:space="preserve">5012452805</t>
+        </is>
+      </c>
+      <c s="20" r="L105">
+        <v>2237.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M105">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N105">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O105"/>
+      <c s="19" t="str" r="P105"/>
+      <c s="19" t="str" r="Q105"/>
+      <c s="19" t="str" r="R105"/>
+      <c s="19" t="inlineStr" r="S105">
+        <is>
+          <t xml:space="preserve">2635002612</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T105"/>
+      <c s="19" t="inlineStr" r="U105">
+        <is>
+          <t xml:space="preserve">5001547609</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V105">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y105">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z105">
+        <is>
+          <t xml:space="preserve">10046882    </t>
+        </is>
+      </c>
+      <c s="20" r="AA105">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB105">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC105">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD105"/>
+      <c s="19" t="inlineStr" r="AF105">
+        <is>
+          <t xml:space="preserve">2003908219</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG105"/>
+    </row>
+    <row r="106" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A106">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B106">
+        <is>
+          <t xml:space="preserve">12:54:39</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C106">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D106">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E106">
+        <v>200746</v>
+      </c>
+      <c s="16" t="inlineStr" r="F106">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H106">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I106">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J106">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K106">
+        <is>
+          <t xml:space="preserve">5012452806</t>
+        </is>
+      </c>
+      <c s="17" r="L106">
+        <v>939.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M106">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N106">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O106"/>
+      <c s="16" t="str" r="P106"/>
+      <c s="16" t="str" r="Q106"/>
+      <c s="16" t="str" r="R106"/>
+      <c s="16" t="inlineStr" r="S106">
+        <is>
+          <t xml:space="preserve">2636005757</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T106"/>
+      <c s="16" t="inlineStr" r="U106">
+        <is>
+          <t xml:space="preserve">5001547630</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V106">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y106">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z106">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="17" r="AA106">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB106">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC106">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD106">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF106">
+        <is>
+          <t xml:space="preserve">2003908392</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG106"/>
+    </row>
+    <row r="107" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A107">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B107">
+        <is>
+          <t xml:space="preserve">13:03:33</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C107">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D107">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E107">
+        <v>200746</v>
+      </c>
+      <c s="19" t="inlineStr" r="F107">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H107">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I107">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J107">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K107">
+        <is>
+          <t xml:space="preserve">5012452821</t>
+        </is>
+      </c>
+      <c s="20" r="L107">
+        <v>1000.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M107">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N107">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O107"/>
+      <c s="19" t="str" r="P107"/>
+      <c s="19" t="str" r="Q107"/>
+      <c s="19" t="str" r="R107"/>
+      <c s="19" t="inlineStr" r="S107">
+        <is>
+          <t xml:space="preserve">2636005758</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T107"/>
+      <c s="19" t="inlineStr" r="U107">
+        <is>
+          <t xml:space="preserve">5001547647</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V107">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y107">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z107">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" r="AA107">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB107">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC107">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD107">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF107">
+        <is>
+          <t xml:space="preserve">2003908392</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG107"/>
+    </row>
+    <row r="108" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A108">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B108">
+        <is>
+          <t xml:space="preserve">13:14:08</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C108">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D108">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E108">
+        <v>200695</v>
+      </c>
+      <c s="16" t="inlineStr" r="F108">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H108">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I108">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J108">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K108">
+        <is>
+          <t xml:space="preserve">5012452861</t>
+        </is>
+      </c>
+      <c s="17" r="L108">
+        <v>2121.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M108">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N108">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O108"/>
+      <c s="16" t="str" r="P108"/>
+      <c s="16" t="str" r="Q108"/>
+      <c s="16" t="str" r="R108"/>
+      <c s="16" t="inlineStr" r="S108">
+        <is>
+          <t xml:space="preserve">2632005137</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T108"/>
+      <c s="16" t="inlineStr" r="U108">
+        <is>
+          <t xml:space="preserve">5001547698</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V108">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y108">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z108">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="17" r="AA108">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB108">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC108">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD108"/>
+      <c s="16" t="inlineStr" r="AF108">
+        <is>
+          <t xml:space="preserve">2003935928</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG108"/>
+    </row>
+    <row r="109" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A109">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B109">
+        <is>
+          <t xml:space="preserve">13:16:45</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C109">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D109">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E109">
+        <v>201026</v>
+      </c>
+      <c s="19" t="inlineStr" r="F109">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H109">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I109">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J109">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K109">
+        <is>
+          <t xml:space="preserve">5012452864</t>
+        </is>
+      </c>
+      <c s="20" r="L109">
+        <v>560.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M109">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N109">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O109">
+        <is>
+          <t xml:space="preserve">0072</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P109">
+        <is>
+          <t xml:space="preserve">TRV - Quebra de superfície</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q109"/>
+      <c s="19" t="str" r="R109"/>
+      <c s="19" t="inlineStr" r="S109">
+        <is>
+          <t xml:space="preserve">2632005138</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T109"/>
+      <c s="19" t="inlineStr" r="U109">
+        <is>
+          <t xml:space="preserve">5001547711</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V109">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y109">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z109">
+        <is>
+          <t xml:space="preserve">10046890    </t>
+        </is>
+      </c>
+      <c s="20" r="AA109">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB109">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC109">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD109">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF109">
+        <is>
+          <t xml:space="preserve">2003984141</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG109"/>
+    </row>
+    <row r="110" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A110">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B110">
+        <is>
+          <t xml:space="preserve">13:22:32</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C110">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D110">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E110">
+        <v>201026</v>
+      </c>
+      <c s="16" t="inlineStr" r="F110">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H110">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I110">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J110">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K110">
+        <is>
+          <t xml:space="preserve">5012452894</t>
+        </is>
+      </c>
+      <c s="17" r="L110">
+        <v>2034.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M110">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N110">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O110"/>
+      <c s="16" t="str" r="P110"/>
+      <c s="16" t="str" r="Q110"/>
+      <c s="16" t="str" r="R110"/>
+      <c s="16" t="inlineStr" r="S110">
+        <is>
+          <t xml:space="preserve">2632005139</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T110"/>
+      <c s="16" t="inlineStr" r="U110">
+        <is>
+          <t xml:space="preserve">5001547748</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V110">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y110">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z110">
+        <is>
+          <t xml:space="preserve">10046890    </t>
+        </is>
+      </c>
+      <c s="17" r="AA110">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB110">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC110">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD110">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF110">
+        <is>
+          <t xml:space="preserve">2003984141</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG110"/>
+    </row>
+    <row r="111" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A111">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B111">
+        <is>
+          <t xml:space="preserve">13:32:09</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C111">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D111">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E111">
+        <v>200716</v>
+      </c>
+      <c s="19" t="inlineStr" r="F111">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H111">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I111">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J111">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K111">
+        <is>
+          <t xml:space="preserve">5012452921</t>
+        </is>
+      </c>
+      <c s="20" r="L111">
+        <v>2492.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M111">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N111">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O111"/>
+      <c s="19" t="str" r="P111"/>
+      <c s="19" t="str" r="Q111"/>
+      <c s="19" t="str" r="R111"/>
+      <c s="19" t="inlineStr" r="S111">
+        <is>
+          <t xml:space="preserve">2635002613</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T111"/>
+      <c s="19" t="inlineStr" r="U111">
+        <is>
+          <t xml:space="preserve">5001547808</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V111">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y111">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z111">
+        <is>
+          <t xml:space="preserve">10046882    </t>
+        </is>
+      </c>
+      <c s="20" r="AA111">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB111">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC111">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD111"/>
+      <c s="19" t="inlineStr" r="AF111">
+        <is>
+          <t xml:space="preserve">2003896512</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG111"/>
+    </row>
+    <row r="112" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A112">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B112">
+        <is>
+          <t xml:space="preserve">13:33:37</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C112">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D112">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E112">
+        <v>201026</v>
+      </c>
+      <c s="16" t="inlineStr" r="F112">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H112">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I112">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J112">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K112">
+        <is>
+          <t xml:space="preserve">5012452924</t>
+        </is>
+      </c>
+      <c s="17" r="L112">
+        <v>2035.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M112">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N112">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O112"/>
+      <c s="16" t="str" r="P112"/>
+      <c s="16" t="str" r="Q112"/>
+      <c s="16" t="str" r="R112"/>
+      <c s="16" t="inlineStr" r="S112">
+        <is>
+          <t xml:space="preserve">2632005140</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T112"/>
+      <c s="16" t="inlineStr" r="U112">
+        <is>
+          <t xml:space="preserve">5001547821</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V112">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y112">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z112">
+        <is>
+          <t xml:space="preserve">10046890    </t>
+        </is>
+      </c>
+      <c s="17" r="AA112">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB112">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC112">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD112">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF112">
+        <is>
+          <t xml:space="preserve">2003984141</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG112"/>
+    </row>
+    <row r="113" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A113">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B113">
+        <is>
+          <t xml:space="preserve">13:42:03</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C113">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D113">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E113">
+        <v>201026</v>
+      </c>
+      <c s="19" t="inlineStr" r="F113">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H113">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I113">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J113">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K113">
+        <is>
+          <t xml:space="preserve">5012452959</t>
+        </is>
+      </c>
+      <c s="20" r="L113">
+        <v>2036.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M113">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N113">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O113"/>
+      <c s="19" t="str" r="P113"/>
+      <c s="19" t="str" r="Q113"/>
+      <c s="19" t="str" r="R113"/>
+      <c s="19" t="inlineStr" r="S113">
+        <is>
+          <t xml:space="preserve">2632005141</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T113"/>
+      <c s="19" t="inlineStr" r="U113">
+        <is>
+          <t xml:space="preserve">5001547891</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V113">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y113">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z113">
+        <is>
+          <t xml:space="preserve">10046890    </t>
+        </is>
+      </c>
+      <c s="20" r="AA113">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB113">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC113">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD113">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF113">
+        <is>
+          <t xml:space="preserve">2003984141</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG113"/>
+    </row>
+    <row r="114" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A114">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B114">
+        <is>
+          <t xml:space="preserve">13:45:45</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C114">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D114">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E114">
+        <v>201081</v>
+      </c>
+      <c s="16" t="inlineStr" r="F114">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H114">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I114">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J114">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K114">
+        <is>
+          <t xml:space="preserve">5012452972</t>
+        </is>
+      </c>
+      <c s="17" r="L114">
+        <v>2075.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M114">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N114">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O114"/>
+      <c s="16" t="str" r="P114"/>
+      <c s="16" t="str" r="Q114"/>
+      <c s="16" t="str" r="R114"/>
+      <c s="16" t="inlineStr" r="S114">
+        <is>
+          <t xml:space="preserve">2635002614</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T114"/>
+      <c s="16" t="inlineStr" r="U114">
+        <is>
+          <t xml:space="preserve">5001547904</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V114">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y114">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z114">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="17" r="AA114">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB114">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC114">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD114">
+        <is>
+          <t xml:space="preserve">PCI</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF114">
+        <is>
+          <t xml:space="preserve">2003932231</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG114"/>
+    </row>
+    <row r="115" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A115">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B115">
+        <is>
+          <t xml:space="preserve">13:53:56</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C115">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D115">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E115">
+        <v>201026</v>
+      </c>
+      <c s="19" t="inlineStr" r="F115">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H115">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I115">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J115">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K115">
+        <is>
+          <t xml:space="preserve">5012453009</t>
+        </is>
+      </c>
+      <c s="20" r="L115">
+        <v>2036.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M115">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N115">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O115"/>
+      <c s="19" t="str" r="P115"/>
+      <c s="19" t="str" r="Q115"/>
+      <c s="19" t="str" r="R115"/>
+      <c s="19" t="inlineStr" r="S115">
+        <is>
+          <t xml:space="preserve">2632005142</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T115"/>
+      <c s="19" t="inlineStr" r="U115">
+        <is>
+          <t xml:space="preserve">5001547955</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V115">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y115">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z115">
+        <is>
+          <t xml:space="preserve">10046890    </t>
+        </is>
+      </c>
+      <c s="20" r="AA115">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB115">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC115">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD115">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF115">
+        <is>
+          <t xml:space="preserve">2003984141</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG115"/>
+    </row>
+    <row r="116" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A116">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B116">
+        <is>
+          <t xml:space="preserve">13:57:13</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C116">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D116">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E116">
+        <v>201081</v>
+      </c>
+      <c s="16" t="inlineStr" r="F116">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H116">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I116">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J116">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K116">
+        <is>
+          <t xml:space="preserve">5012453022</t>
+        </is>
+      </c>
+      <c s="17" r="L116">
+        <v>2079.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M116">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N116">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O116"/>
+      <c s="16" t="str" r="P116"/>
+      <c s="16" t="str" r="Q116"/>
+      <c s="16" t="str" r="R116"/>
+      <c s="16" t="inlineStr" r="S116">
+        <is>
+          <t xml:space="preserve">2635002615</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T116"/>
+      <c s="16" t="inlineStr" r="U116">
+        <is>
+          <t xml:space="preserve">5001547998</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V116">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y116">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z116">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="17" r="AA116">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB116">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC116">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD116">
+        <is>
+          <t xml:space="preserve">PCI</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF116">
+        <is>
+          <t xml:space="preserve">2003932231</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG116"/>
+    </row>
+    <row r="117" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A117">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B117">
+        <is>
+          <t xml:space="preserve">14:03:13</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C117">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D117">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E117">
+        <v>201026</v>
+      </c>
+      <c s="19" t="inlineStr" r="F117">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H117">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I117">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J117">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K117">
+        <is>
+          <t xml:space="preserve">5012453046</t>
+        </is>
+      </c>
+      <c s="20" r="L117">
+        <v>2037.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M117">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N117">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O117"/>
+      <c s="19" t="str" r="P117"/>
+      <c s="19" t="str" r="Q117"/>
+      <c s="19" t="str" r="R117"/>
+      <c s="19" t="inlineStr" r="S117">
+        <is>
+          <t xml:space="preserve">2632005143</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T117"/>
+      <c s="19" t="inlineStr" r="U117">
+        <is>
+          <t xml:space="preserve">5001548029</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V117">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y117">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z117">
+        <is>
+          <t xml:space="preserve">10046890    </t>
+        </is>
+      </c>
+      <c s="20" r="AA117">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB117">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC117">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD117">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF117">
+        <is>
+          <t xml:space="preserve">2003984141</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG117"/>
+    </row>
+    <row r="118" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A118">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B118">
+        <is>
+          <t xml:space="preserve">14:16:55</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C118">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D118">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E118">
+        <v>201081</v>
+      </c>
+      <c s="16" t="inlineStr" r="F118">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H118">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I118">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J118">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K118">
+        <is>
+          <t xml:space="preserve">5012453099</t>
+        </is>
+      </c>
+      <c s="17" r="L118">
+        <v>2080.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M118">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N118">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O118"/>
+      <c s="16" t="str" r="P118"/>
+      <c s="16" t="str" r="Q118"/>
+      <c s="16" t="str" r="R118"/>
+      <c s="16" t="inlineStr" r="S118">
+        <is>
+          <t xml:space="preserve">2635002616</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T118"/>
+      <c s="16" t="inlineStr" r="U118">
+        <is>
+          <t xml:space="preserve">5001548176</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V118">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y118">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z118">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="17" r="AA118">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB118">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC118">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD118">
+        <is>
+          <t xml:space="preserve">PCI</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF118">
+        <is>
+          <t xml:space="preserve">2003932231</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG118"/>
+    </row>
+    <row r="119" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A119">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B119">
+        <is>
+          <t xml:space="preserve">14:23:06</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C119">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D119">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E119">
+        <v>201026</v>
+      </c>
+      <c s="19" t="inlineStr" r="F119">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H119">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I119">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J119">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K119">
+        <is>
+          <t xml:space="preserve">5012453112</t>
+        </is>
+      </c>
+      <c s="20" r="L119">
+        <v>816.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M119">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N119">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O119"/>
+      <c s="19" t="str" r="P119"/>
+      <c s="19" t="str" r="Q119"/>
+      <c s="19" t="str" r="R119"/>
+      <c s="19" t="inlineStr" r="S119">
+        <is>
+          <t xml:space="preserve">2632005144</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T119"/>
+      <c s="19" t="inlineStr" r="U119">
+        <is>
+          <t xml:space="preserve">5001548189</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V119">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y119">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z119">
+        <is>
+          <t xml:space="preserve">10046890    </t>
+        </is>
+      </c>
+      <c s="20" r="AA119">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB119">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC119">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD119">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF119">
+        <is>
+          <t xml:space="preserve">2003984141</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG119"/>
+    </row>
+    <row r="120" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A120">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B120">
+        <is>
+          <t xml:space="preserve">14:27:09</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C120">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D120">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E120">
+        <v>201025</v>
+      </c>
+      <c s="16" t="inlineStr" r="F120">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H120">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I120">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J120">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K120">
+        <is>
+          <t xml:space="preserve">5012453116</t>
+        </is>
+      </c>
+      <c s="17" r="L120">
+        <v>447.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M120">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N120">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O120">
+        <is>
+          <t xml:space="preserve">0072</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P120">
+        <is>
+          <t xml:space="preserve">TRV - Quebra de superfície</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q120"/>
+      <c s="16" t="str" r="R120"/>
+      <c s="16" t="inlineStr" r="S120">
+        <is>
+          <t xml:space="preserve">2632005145</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T120"/>
+      <c s="16" t="inlineStr" r="U120">
+        <is>
+          <t xml:space="preserve">5001548203</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V120">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y120">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z120">
+        <is>
+          <t xml:space="preserve">10046891    </t>
+        </is>
+      </c>
+      <c s="17" r="AA120">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB120">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC120">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD120">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF120">
+        <is>
+          <t xml:space="preserve">2003984177</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG120"/>
+    </row>
+    <row r="121" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A121">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B121">
+        <is>
+          <t xml:space="preserve">14:38:14</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C121">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D121">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E121">
+        <v>201025</v>
+      </c>
+      <c s="19" t="inlineStr" r="F121">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H121">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I121">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J121">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K121">
+        <is>
+          <t xml:space="preserve">5012453130</t>
+        </is>
+      </c>
+      <c s="20" r="L121">
+        <v>2044.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M121">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N121">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O121"/>
+      <c s="19" t="str" r="P121"/>
+      <c s="19" t="str" r="Q121"/>
+      <c s="19" t="str" r="R121"/>
+      <c s="19" t="inlineStr" r="S121">
+        <is>
+          <t xml:space="preserve">2632005146</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T121"/>
+      <c s="19" t="inlineStr" r="U121">
+        <is>
+          <t xml:space="preserve">5001548277</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V121">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y121">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z121">
+        <is>
+          <t xml:space="preserve">10046891    </t>
+        </is>
+      </c>
+      <c s="20" r="AA121">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB121">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC121">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD121">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF121">
+        <is>
+          <t xml:space="preserve">2003984177</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG121"/>
+    </row>
+    <row r="122" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A122">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B122">
+        <is>
+          <t xml:space="preserve">14:46:19</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C122">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D122">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E122">
+        <v>201081</v>
+      </c>
+      <c s="16" t="inlineStr" r="F122">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H122">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I122">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J122">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K122">
+        <is>
+          <t xml:space="preserve">5012453147</t>
+        </is>
+      </c>
+      <c s="17" r="L122">
+        <v>2061.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M122">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N122">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O122"/>
+      <c s="16" t="str" r="P122"/>
+      <c s="16" t="str" r="Q122"/>
+      <c s="16" t="str" r="R122"/>
+      <c s="16" t="inlineStr" r="S122">
+        <is>
+          <t xml:space="preserve">2635002617</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T122"/>
+      <c s="16" t="inlineStr" r="U122">
+        <is>
+          <t xml:space="preserve">5001548334</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V122">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y122">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z122">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="17" r="AA122">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB122">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC122">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD122">
+        <is>
+          <t xml:space="preserve">PCI</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF122">
+        <is>
+          <t xml:space="preserve">2003932231</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG122"/>
+    </row>
+    <row r="123" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A123">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B123">
+        <is>
+          <t xml:space="preserve">14:48:35</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C123">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D123">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E123">
+        <v>201081</v>
+      </c>
+      <c s="19" t="inlineStr" r="F123">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H123">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I123">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J123">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K123">
+        <is>
+          <t xml:space="preserve">5012453165</t>
+        </is>
+      </c>
+      <c s="20" r="L123">
+        <v>2077.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M123">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N123">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O123"/>
+      <c s="19" t="str" r="P123"/>
+      <c s="19" t="str" r="Q123"/>
+      <c s="19" t="str" r="R123"/>
+      <c s="19" t="inlineStr" r="S123">
+        <is>
+          <t xml:space="preserve">2635002618</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T123"/>
+      <c s="19" t="inlineStr" r="U123">
+        <is>
+          <t xml:space="preserve">5001548365</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V123">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y123">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z123">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="20" r="AA123">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB123">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC123">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD123">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF123">
+        <is>
+          <t xml:space="preserve">2003921376</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG123"/>
+    </row>
+    <row r="124" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A124">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B124">
+        <is>
+          <t xml:space="preserve">14:49:26</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C124">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D124">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E124">
+        <v>201025</v>
+      </c>
+      <c s="16" t="inlineStr" r="F124">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H124">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I124">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J124">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K124">
+        <is>
+          <t xml:space="preserve">5012453170</t>
+        </is>
+      </c>
+      <c s="17" r="L124">
+        <v>2026.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M124">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N124">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O124"/>
+      <c s="16" t="str" r="P124"/>
+      <c s="16" t="str" r="Q124"/>
+      <c s="16" t="str" r="R124"/>
+      <c s="16" t="inlineStr" r="S124">
+        <is>
+          <t xml:space="preserve">2632005147</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T124"/>
+      <c s="16" t="inlineStr" r="U124">
+        <is>
+          <t xml:space="preserve">5001548370</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V124">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y124">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z124">
+        <is>
+          <t xml:space="preserve">10046891    </t>
+        </is>
+      </c>
+      <c s="17" r="AA124">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB124">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC124">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD124">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF124">
+        <is>
+          <t xml:space="preserve">2003984177</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG124"/>
+    </row>
+    <row r="125" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A125">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B125">
+        <is>
+          <t xml:space="preserve">14:58:46</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C125">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D125">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E125">
+        <v>201081</v>
+      </c>
+      <c s="19" t="inlineStr" r="F125">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H125">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I125">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J125">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K125">
+        <is>
+          <t xml:space="preserve">5012453193</t>
+        </is>
+      </c>
+      <c s="20" r="L125">
+        <v>2060.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M125">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N125">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O125"/>
+      <c s="19" t="str" r="P125"/>
+      <c s="19" t="str" r="Q125"/>
+      <c s="19" t="str" r="R125"/>
+      <c s="19" t="inlineStr" r="S125">
+        <is>
+          <t xml:space="preserve">2635002619</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T125"/>
+      <c s="19" t="inlineStr" r="U125">
+        <is>
+          <t xml:space="preserve">5001548453</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V125">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y125">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z125">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="20" r="AA125">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB125">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC125">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD125">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF125">
+        <is>
+          <t xml:space="preserve">2003921376</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG125"/>
+    </row>
+    <row r="126" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A126">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B126">
+        <is>
+          <t xml:space="preserve">15:02:47</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C126">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D126">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E126">
+        <v>201025</v>
+      </c>
+      <c s="16" t="inlineStr" r="F126">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H126">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I126">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J126">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K126">
+        <is>
+          <t xml:space="preserve">5012453208</t>
+        </is>
+      </c>
+      <c s="17" r="L126">
+        <v>2025.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M126">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N126">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O126"/>
+      <c s="16" t="str" r="P126"/>
+      <c s="16" t="str" r="Q126"/>
+      <c s="16" t="str" r="R126"/>
+      <c s="16" t="inlineStr" r="S126">
+        <is>
+          <t xml:space="preserve">2632005148</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T126"/>
+      <c s="16" t="inlineStr" r="U126">
+        <is>
+          <t xml:space="preserve">5001548473</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V126">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y126">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z126">
+        <is>
+          <t xml:space="preserve">10046891    </t>
+        </is>
+      </c>
+      <c s="17" r="AA126">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB126">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC126">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD126">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF126">
+        <is>
+          <t xml:space="preserve">2003984177</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG126"/>
+    </row>
+    <row r="127" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A127">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B127">
+        <is>
+          <t xml:space="preserve">15:09:04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C127">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D127">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E127">
+        <v>201081</v>
+      </c>
+      <c s="19" t="inlineStr" r="F127">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H127">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I127">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J127">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K127">
+        <is>
+          <t xml:space="preserve">5012453219</t>
+        </is>
+      </c>
+      <c s="20" r="L127">
+        <v>2056.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M127">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N127">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O127"/>
+      <c s="19" t="str" r="P127"/>
+      <c s="19" t="str" r="Q127"/>
+      <c s="19" t="str" r="R127"/>
+      <c s="19" t="inlineStr" r="S127">
+        <is>
+          <t xml:space="preserve">2635002620</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T127"/>
+      <c s="19" t="inlineStr" r="U127">
+        <is>
+          <t xml:space="preserve">5001548505</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V127">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y127">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z127">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="20" r="AA127">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB127">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC127">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD127">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF127">
+        <is>
+          <t xml:space="preserve">2003921376</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG127"/>
+    </row>
+    <row r="128" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A128">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B128">
+        <is>
+          <t xml:space="preserve">15:14:07</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C128">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D128">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E128">
+        <v>201025</v>
+      </c>
+      <c s="16" t="inlineStr" r="F128">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H128">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I128">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J128">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K128">
+        <is>
+          <t xml:space="preserve">5012453233</t>
+        </is>
+      </c>
+      <c s="17" r="L128">
+        <v>2022.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M128">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N128">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O128"/>
+      <c s="16" t="str" r="P128"/>
+      <c s="16" t="str" r="Q128"/>
+      <c s="16" t="str" r="R128"/>
+      <c s="16" t="inlineStr" r="S128">
+        <is>
+          <t xml:space="preserve">2632005149</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T128"/>
+      <c s="16" t="inlineStr" r="U128">
+        <is>
+          <t xml:space="preserve">5001548549</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V128">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y128">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z128">
+        <is>
+          <t xml:space="preserve">10046891    </t>
+        </is>
+      </c>
+      <c s="17" r="AA128">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB128">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC128">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD128">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF128">
+        <is>
+          <t xml:space="preserve">2003984177</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG128"/>
+    </row>
+    <row r="129" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A129">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B129">
+        <is>
+          <t xml:space="preserve">15:25:45</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C129">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D129">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E129">
+        <v>201025</v>
+      </c>
+      <c s="19" t="inlineStr" r="F129">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H129">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I129">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J129">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K129">
+        <is>
+          <t xml:space="preserve">5012453249</t>
+        </is>
+      </c>
+      <c s="20" r="L129">
+        <v>2028.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M129">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N129">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O129"/>
+      <c s="19" t="str" r="P129"/>
+      <c s="19" t="str" r="Q129"/>
+      <c s="19" t="str" r="R129"/>
+      <c s="19" t="inlineStr" r="S129">
+        <is>
+          <t xml:space="preserve">2632005150</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T129"/>
+      <c s="19" t="inlineStr" r="U129">
+        <is>
+          <t xml:space="preserve">5001548585</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V129">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y129">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z129">
+        <is>
+          <t xml:space="preserve">10046891    </t>
+        </is>
+      </c>
+      <c s="20" r="AA129">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB129">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC129">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD129">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF129">
+        <is>
+          <t xml:space="preserve">2003984177</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG129"/>
+    </row>
+    <row r="130" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A130">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B130">
+        <is>
+          <t xml:space="preserve">15:40:33</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C130">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D130">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E130">
+        <v>201081</v>
+      </c>
+      <c s="16" t="inlineStr" r="F130">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H130">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I130">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J130">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K130">
+        <is>
+          <t xml:space="preserve">5012453288</t>
+        </is>
+      </c>
+      <c s="17" r="L130">
+        <v>2477.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M130">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N130">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O130"/>
+      <c s="16" t="str" r="P130"/>
+      <c s="16" t="str" r="Q130"/>
+      <c s="16" t="str" r="R130"/>
+      <c s="16" t="inlineStr" r="S130">
+        <is>
+          <t xml:space="preserve">2635002621</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T130"/>
+      <c s="16" t="inlineStr" r="U130">
+        <is>
+          <t xml:space="preserve">5001548647</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V130">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y130">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z130">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="17" r="AA130">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB130">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC130">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD130">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF130">
+        <is>
+          <t xml:space="preserve">2003921376</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG130"/>
+    </row>
+    <row r="131" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A131">
+        <is>
+          <t xml:space="preserve">02/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B131">
+        <is>
+          <t xml:space="preserve">15:54:20</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C131">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D131">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E131">
+        <v>201025</v>
+      </c>
+      <c s="19" t="inlineStr" r="F131">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,90mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H131">
+        <is>
+          <t xml:space="preserve">0,90mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I131">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J131">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K131">
+        <is>
+          <t xml:space="preserve">5012453313</t>
+        </is>
+      </c>
+      <c s="20" r="L131">
+        <v>1018.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M131">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N131">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O131"/>
+      <c s="19" t="str" r="P131"/>
+      <c s="19" t="str" r="Q131"/>
+      <c s="19" t="str" r="R131"/>
+      <c s="19" t="inlineStr" r="S131">
+        <is>
+          <t xml:space="preserve">2632005151</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T131"/>
+      <c s="19" t="inlineStr" r="U131">
+        <is>
+          <t xml:space="preserve">5001548695</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V131">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y131">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z131">
+        <is>
+          <t xml:space="preserve">10046891    </t>
+        </is>
+      </c>
+      <c s="20" r="AA131">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB131">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC131">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD131">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF131">
+        <is>
+          <t xml:space="preserve">2003984177</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG131"/>
+    </row>
+    <row r="132" ht="14.7" customHeight="1">
+      <c s="21" t="inlineStr" r="A132">
+        <is>
+          <t xml:space="preserve">Peso Total: 167712,000</t>
+        </is>
+      </c>
+      <c s="13" t="str" r="B132"/>
+      <c s="13" t="str" r="C132"/>
+      <c s="13" t="str" r="D132"/>
+      <c s="13" t="str" r="E132"/>
+      <c s="13" t="str" r="F132"/>
+      <c s="13" t="str" r="G132"/>
+      <c s="13" t="str" r="H132"/>
+      <c s="13" t="str" r="I132"/>
+      <c s="13" t="str" r="J132"/>
+      <c s="13" t="str" r="K132"/>
+      <c s="13" t="str" r="L132"/>
+      <c s="13" t="str" r="M132"/>
+      <c s="13" t="str" r="N132"/>
+      <c s="13" t="str" r="O132"/>
+      <c s="13" t="str" r="P132"/>
+      <c s="13" t="str" r="Q132"/>
+      <c s="13" t="str" r="R132"/>
+      <c s="13" t="str" r="S132"/>
+      <c s="13" t="str" r="T132"/>
+      <c s="13" t="str" r="U132"/>
+      <c s="13" t="str" r="V132"/>
+      <c s="13" t="str" r="W132"/>
+      <c s="13" t="str" r="X132"/>
+      <c s="13" t="str" r="Y132"/>
+      <c s="13" t="str" r="Z132"/>
+      <c s="13" t="str" r="AA132"/>
+      <c s="13" t="str" r="AB132"/>
+      <c s="13" t="str" r="AC132"/>
+      <c s="13" t="str" r="AD132"/>
+      <c s="13" t="str" r="AE132"/>
+      <c s="13" t="str" r="AF132"/>
+      <c s="14" t="str" r="AG132"/>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A2:B6"/>
@@ -6966,7 +14507,271 @@
     <mergeCell ref="V65:X65"/>
     <mergeCell ref="AD65:AE65"/>
     <mergeCell ref="AF65:AG65"/>
-    <mergeCell ref="A66:AG66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="V66:X66"/>
+    <mergeCell ref="AD66:AE66"/>
+    <mergeCell ref="AF66:AG66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="V67:X67"/>
+    <mergeCell ref="AD67:AE67"/>
+    <mergeCell ref="AF67:AG67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="V68:X68"/>
+    <mergeCell ref="AD68:AE68"/>
+    <mergeCell ref="AF68:AG68"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="AD69:AE69"/>
+    <mergeCell ref="AF69:AG69"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="AD70:AE70"/>
+    <mergeCell ref="AF70:AG70"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="AD71:AE71"/>
+    <mergeCell ref="AF71:AG71"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="AD72:AE72"/>
+    <mergeCell ref="AF72:AG72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="V73:X73"/>
+    <mergeCell ref="AD73:AE73"/>
+    <mergeCell ref="AF73:AG73"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="V74:X74"/>
+    <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="AF74:AG74"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="V75:X75"/>
+    <mergeCell ref="AD75:AE75"/>
+    <mergeCell ref="AF75:AG75"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="AD76:AE76"/>
+    <mergeCell ref="AF76:AG76"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="AD77:AE77"/>
+    <mergeCell ref="AF77:AG77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="AD78:AE78"/>
+    <mergeCell ref="AF78:AG78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="V79:X79"/>
+    <mergeCell ref="AD79:AE79"/>
+    <mergeCell ref="AF79:AG79"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="V80:X80"/>
+    <mergeCell ref="AD80:AE80"/>
+    <mergeCell ref="AF80:AG80"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="AD81:AE81"/>
+    <mergeCell ref="AF81:AG81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="AD82:AE82"/>
+    <mergeCell ref="AF82:AG82"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="AD83:AE83"/>
+    <mergeCell ref="AF83:AG83"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="AD84:AE84"/>
+    <mergeCell ref="AF84:AG84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="V85:X85"/>
+    <mergeCell ref="AD85:AE85"/>
+    <mergeCell ref="AF85:AG85"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="V86:X86"/>
+    <mergeCell ref="AD86:AE86"/>
+    <mergeCell ref="AF86:AG86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="V87:X87"/>
+    <mergeCell ref="AD87:AE87"/>
+    <mergeCell ref="AF87:AG87"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="AD88:AE88"/>
+    <mergeCell ref="AF88:AG88"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="AD89:AE89"/>
+    <mergeCell ref="AF89:AG89"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="AD90:AE90"/>
+    <mergeCell ref="AF90:AG90"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="V91:X91"/>
+    <mergeCell ref="AD91:AE91"/>
+    <mergeCell ref="AF91:AG91"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="V92:X92"/>
+    <mergeCell ref="AD92:AE92"/>
+    <mergeCell ref="AF92:AG92"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="V93:X93"/>
+    <mergeCell ref="AD93:AE93"/>
+    <mergeCell ref="AF93:AG93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="AD94:AE94"/>
+    <mergeCell ref="AF94:AG94"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="AD95:AE95"/>
+    <mergeCell ref="AF95:AG95"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="AD96:AE96"/>
+    <mergeCell ref="AF96:AG96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="V97:X97"/>
+    <mergeCell ref="AD97:AE97"/>
+    <mergeCell ref="AF97:AG97"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="V98:X98"/>
+    <mergeCell ref="AD98:AE98"/>
+    <mergeCell ref="AF98:AG98"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="V99:X99"/>
+    <mergeCell ref="AD99:AE99"/>
+    <mergeCell ref="AF99:AG99"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="AD100:AE100"/>
+    <mergeCell ref="AF100:AG100"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="AD101:AE101"/>
+    <mergeCell ref="AF101:AG101"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="AD102:AE102"/>
+    <mergeCell ref="AF102:AG102"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="V103:X103"/>
+    <mergeCell ref="AD103:AE103"/>
+    <mergeCell ref="AF103:AG103"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="V104:X104"/>
+    <mergeCell ref="AD104:AE104"/>
+    <mergeCell ref="AF104:AG104"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="V105:X105"/>
+    <mergeCell ref="AD105:AE105"/>
+    <mergeCell ref="AF105:AG105"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="V106:X106"/>
+    <mergeCell ref="AD106:AE106"/>
+    <mergeCell ref="AF106:AG106"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="V107:X107"/>
+    <mergeCell ref="AD107:AE107"/>
+    <mergeCell ref="AF107:AG107"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="V108:X108"/>
+    <mergeCell ref="AD108:AE108"/>
+    <mergeCell ref="AF108:AG108"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="V109:X109"/>
+    <mergeCell ref="AD109:AE109"/>
+    <mergeCell ref="AF109:AG109"/>
+    <mergeCell ref="F110:G110"/>
+    <mergeCell ref="V110:X110"/>
+    <mergeCell ref="AD110:AE110"/>
+    <mergeCell ref="AF110:AG110"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="V111:X111"/>
+    <mergeCell ref="AD111:AE111"/>
+    <mergeCell ref="AF111:AG111"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="V112:X112"/>
+    <mergeCell ref="AD112:AE112"/>
+    <mergeCell ref="AF112:AG112"/>
+    <mergeCell ref="F113:G113"/>
+    <mergeCell ref="V113:X113"/>
+    <mergeCell ref="AD113:AE113"/>
+    <mergeCell ref="AF113:AG113"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="V114:X114"/>
+    <mergeCell ref="AD114:AE114"/>
+    <mergeCell ref="AF114:AG114"/>
+    <mergeCell ref="F115:G115"/>
+    <mergeCell ref="V115:X115"/>
+    <mergeCell ref="AD115:AE115"/>
+    <mergeCell ref="AF115:AG115"/>
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="V116:X116"/>
+    <mergeCell ref="AD116:AE116"/>
+    <mergeCell ref="AF116:AG116"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="V117:X117"/>
+    <mergeCell ref="AD117:AE117"/>
+    <mergeCell ref="AF117:AG117"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="V118:X118"/>
+    <mergeCell ref="AD118:AE118"/>
+    <mergeCell ref="AF118:AG118"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="V119:X119"/>
+    <mergeCell ref="AD119:AE119"/>
+    <mergeCell ref="AF119:AG119"/>
+    <mergeCell ref="F120:G120"/>
+    <mergeCell ref="V120:X120"/>
+    <mergeCell ref="AD120:AE120"/>
+    <mergeCell ref="AF120:AG120"/>
+    <mergeCell ref="F121:G121"/>
+    <mergeCell ref="V121:X121"/>
+    <mergeCell ref="AD121:AE121"/>
+    <mergeCell ref="AF121:AG121"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="V122:X122"/>
+    <mergeCell ref="AD122:AE122"/>
+    <mergeCell ref="AF122:AG122"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="V123:X123"/>
+    <mergeCell ref="AD123:AE123"/>
+    <mergeCell ref="AF123:AG123"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="V124:X124"/>
+    <mergeCell ref="AD124:AE124"/>
+    <mergeCell ref="AF124:AG124"/>
+    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="V125:X125"/>
+    <mergeCell ref="AD125:AE125"/>
+    <mergeCell ref="AF125:AG125"/>
+    <mergeCell ref="F126:G126"/>
+    <mergeCell ref="V126:X126"/>
+    <mergeCell ref="AD126:AE126"/>
+    <mergeCell ref="AF126:AG126"/>
+    <mergeCell ref="F127:G127"/>
+    <mergeCell ref="V127:X127"/>
+    <mergeCell ref="AD127:AE127"/>
+    <mergeCell ref="AF127:AG127"/>
+    <mergeCell ref="F128:G128"/>
+    <mergeCell ref="V128:X128"/>
+    <mergeCell ref="AD128:AE128"/>
+    <mergeCell ref="AF128:AG128"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="V129:X129"/>
+    <mergeCell ref="AD129:AE129"/>
+    <mergeCell ref="AF129:AG129"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="V130:X130"/>
+    <mergeCell ref="AD130:AE130"/>
+    <mergeCell ref="AF130:AG130"/>
+    <mergeCell ref="F131:G131"/>
+    <mergeCell ref="V131:X131"/>
+    <mergeCell ref="AD131:AE131"/>
+    <mergeCell ref="AF131:AG131"/>
+    <mergeCell ref="A132:AG132"/>
   </mergeCells>
   <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="0.393700787401575" header="0.393700787401575" footer="0.393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/Base_Producao.xlsx
+++ b/Base_Producao.xlsx
@@ -503,7 +503,7 @@
       <c s="4" t="str" r="A5"/>
       <c s="6" t="inlineStr" r="AE5">
         <is>
-          <t xml:space="preserve">Emissão: 05/10/2026</t>
+          <t xml:space="preserve">Emissão: 06/10/2026</t>
         </is>
       </c>
       <c s="7" t="str" r="AG5"/>
@@ -512,7 +512,7 @@
       <c s="4" t="str" r="A6"/>
       <c s="8" t="inlineStr" r="G6">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 04/10/2026</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 05/10/2026</t>
         </is>
       </c>
       <c s="7" t="str" r="AG6"/>
@@ -14247,44 +14247,8237 @@
       </c>
       <c s="7" t="str" r="AG131"/>
     </row>
-    <row r="132" ht="14.7" customHeight="1">
-      <c s="21" t="inlineStr" r="A132">
-        <is>
-          <t xml:space="preserve">Peso Total: 167712,000</t>
-        </is>
-      </c>
-      <c s="13" t="str" r="B132"/>
-      <c s="13" t="str" r="C132"/>
-      <c s="13" t="str" r="D132"/>
-      <c s="13" t="str" r="E132"/>
-      <c s="13" t="str" r="F132"/>
-      <c s="13" t="str" r="G132"/>
-      <c s="13" t="str" r="H132"/>
-      <c s="13" t="str" r="I132"/>
-      <c s="13" t="str" r="J132"/>
-      <c s="13" t="str" r="K132"/>
-      <c s="13" t="str" r="L132"/>
-      <c s="13" t="str" r="M132"/>
-      <c s="13" t="str" r="N132"/>
-      <c s="13" t="str" r="O132"/>
-      <c s="13" t="str" r="P132"/>
-      <c s="13" t="str" r="Q132"/>
-      <c s="13" t="str" r="R132"/>
-      <c s="13" t="str" r="S132"/>
-      <c s="13" t="str" r="T132"/>
-      <c s="13" t="str" r="U132"/>
-      <c s="13" t="str" r="V132"/>
-      <c s="13" t="str" r="W132"/>
-      <c s="13" t="str" r="X132"/>
-      <c s="13" t="str" r="Y132"/>
-      <c s="13" t="str" r="Z132"/>
-      <c s="13" t="str" r="AA132"/>
-      <c s="13" t="str" r="AB132"/>
-      <c s="13" t="str" r="AC132"/>
-      <c s="13" t="str" r="AD132"/>
-      <c s="13" t="str" r="AE132"/>
-      <c s="13" t="str" r="AF132"/>
-      <c s="14" t="str" r="AG132"/>
+    <row r="132" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A132">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B132">
+        <is>
+          <t xml:space="preserve">08:12:14</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C132">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D132">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E132">
+        <v>208891</v>
+      </c>
+      <c s="16" t="inlineStr" r="F132">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H132">
+        <is>
+          <t xml:space="preserve">2,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I132">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J132">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K132">
+        <is>
+          <t xml:space="preserve">5012458308</t>
+        </is>
+      </c>
+      <c s="17" r="L132">
+        <v>297.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M132">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N132">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O132">
+        <is>
+          <t xml:space="preserve">0153</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P132">
+        <is>
+          <t xml:space="preserve">TRV - Variação de largura</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q132"/>
+      <c s="16" t="str" r="R132"/>
+      <c s="16" t="inlineStr" r="S132">
+        <is>
+          <t xml:space="preserve">2633006527</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T132"/>
+      <c s="16" t="inlineStr" r="U132">
+        <is>
+          <t xml:space="preserve">5001558012</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V132">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y132">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z132">
+        <is>
+          <t xml:space="preserve">10047276    </t>
+        </is>
+      </c>
+      <c s="17" r="AA132">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB132">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC132">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD132">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF132">
+        <is>
+          <t xml:space="preserve">2003977951</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG132"/>
+    </row>
+    <row r="133" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A133">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B133">
+        <is>
+          <t xml:space="preserve">08:24:08</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C133">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D133">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E133">
+        <v>216592</v>
+      </c>
+      <c s="19" t="inlineStr" r="F133">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2040mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H133">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I133">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J133">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K133">
+        <is>
+          <t xml:space="preserve">5012458344</t>
+        </is>
+      </c>
+      <c s="20" r="L133">
+        <v>1983.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M133">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N133">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O133"/>
+      <c s="19" t="str" r="P133"/>
+      <c s="19" t="str" r="Q133"/>
+      <c s="19" t="str" r="R133"/>
+      <c s="19" t="inlineStr" r="S133">
+        <is>
+          <t xml:space="preserve">2632005152</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T133"/>
+      <c s="19" t="inlineStr" r="U133">
+        <is>
+          <t xml:space="preserve">5001558120</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V133">
+        <is>
+          <t xml:space="preserve">20131525</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y133">
+        <is>
+          <t xml:space="preserve">L P A METALURGICA LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z133">
+        <is>
+          <t xml:space="preserve">10047268    </t>
+        </is>
+      </c>
+      <c s="20" r="AA133">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB133">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC133">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD133">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF133">
+        <is>
+          <t xml:space="preserve">2003683061</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG133"/>
+    </row>
+    <row r="134" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A134">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B134">
+        <is>
+          <t xml:space="preserve">08:30:12</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C134">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D134">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E134">
+        <v>200746</v>
+      </c>
+      <c s="16" t="inlineStr" r="F134">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H134">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I134">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J134">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K134">
+        <is>
+          <t xml:space="preserve">5012458377</t>
+        </is>
+      </c>
+      <c s="17" r="L134">
+        <v>1000.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M134">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N134">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O134"/>
+      <c s="16" t="str" r="P134"/>
+      <c s="16" t="str" r="Q134"/>
+      <c s="16" t="str" r="R134"/>
+      <c s="16" t="inlineStr" r="S134">
+        <is>
+          <t xml:space="preserve">2636005759</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T134"/>
+      <c s="16" t="inlineStr" r="U134">
+        <is>
+          <t xml:space="preserve">5001558160</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V134">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y134">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z134">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="17" r="AA134">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB134">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC134">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD134">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF134">
+        <is>
+          <t xml:space="preserve">2003908400</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG134"/>
+    </row>
+    <row r="135" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A135">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B135">
+        <is>
+          <t xml:space="preserve">08:41:23</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C135">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D135">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E135">
+        <v>208891</v>
+      </c>
+      <c s="19" t="inlineStr" r="F135">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H135">
+        <is>
+          <t xml:space="preserve">2,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I135">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J135">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K135">
+        <is>
+          <t xml:space="preserve">5012458404</t>
+        </is>
+      </c>
+      <c s="20" r="L135">
+        <v>140.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M135">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N135">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O135">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P135">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q135"/>
+      <c s="19" t="str" r="R135"/>
+      <c s="19" t="inlineStr" r="S135">
+        <is>
+          <t xml:space="preserve">2633006528</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T135"/>
+      <c s="19" t="inlineStr" r="U135">
+        <is>
+          <t xml:space="preserve">5001558198</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V135">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y135">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z135">
+        <is>
+          <t xml:space="preserve">10047276    </t>
+        </is>
+      </c>
+      <c s="20" r="AA135">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB135">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC135">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD135">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF135">
+        <is>
+          <t xml:space="preserve">2003977951</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG135"/>
+    </row>
+    <row r="136" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A136">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B136">
+        <is>
+          <t xml:space="preserve">08:46:40</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C136">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D136">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E136">
+        <v>216592</v>
+      </c>
+      <c s="16" t="inlineStr" r="F136">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2040mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H136">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I136">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J136">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K136">
+        <is>
+          <t xml:space="preserve">5012458431</t>
+        </is>
+      </c>
+      <c s="17" r="L136">
+        <v>2015.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M136">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N136">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O136"/>
+      <c s="16" t="str" r="P136"/>
+      <c s="16" t="str" r="Q136"/>
+      <c s="16" t="str" r="R136"/>
+      <c s="16" t="inlineStr" r="S136">
+        <is>
+          <t xml:space="preserve">2632005153</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T136"/>
+      <c s="16" t="inlineStr" r="U136">
+        <is>
+          <t xml:space="preserve">5001558248</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V136">
+        <is>
+          <t xml:space="preserve">20131525</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y136">
+        <is>
+          <t xml:space="preserve">L P A METALURGICA LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z136">
+        <is>
+          <t xml:space="preserve">10047268    </t>
+        </is>
+      </c>
+      <c s="17" r="AA136">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB136">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC136">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD136">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF136">
+        <is>
+          <t xml:space="preserve">2003683061</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG136"/>
+    </row>
+    <row r="137" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A137">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B137">
+        <is>
+          <t xml:space="preserve">08:51:02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C137">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D137">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E137">
+        <v>201081</v>
+      </c>
+      <c s="19" t="inlineStr" r="F137">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H137">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I137">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J137">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K137">
+        <is>
+          <t xml:space="preserve">5012458443</t>
+        </is>
+      </c>
+      <c s="20" r="L137">
+        <v>2043.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M137">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N137">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O137"/>
+      <c s="19" t="str" r="P137"/>
+      <c s="19" t="str" r="Q137"/>
+      <c s="19" t="str" r="R137"/>
+      <c s="19" t="inlineStr" r="S137">
+        <is>
+          <t xml:space="preserve">2635002622</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T137"/>
+      <c s="19" t="inlineStr" r="U137">
+        <is>
+          <t xml:space="preserve">5001558280</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V137">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y137">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z137">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="20" r="AA137">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB137">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC137">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD137">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AF137"/>
+      <c s="7" t="str" r="AG137"/>
+    </row>
+    <row r="138" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A138">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B138">
+        <is>
+          <t xml:space="preserve">08:55:20</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C138">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D138">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E138">
+        <v>221300</v>
+      </c>
+      <c s="16" t="inlineStr" r="F138">
+        <is>
+          <t xml:space="preserve">CH PLANA 3,75mm SAC 300 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H138">
+        <is>
+          <t xml:space="preserve">3,75mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I138">
+        <is>
+          <t xml:space="preserve">SAC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J138">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K138">
+        <is>
+          <t xml:space="preserve">5012458461</t>
+        </is>
+      </c>
+      <c s="17" r="L138">
+        <v>2082.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M138">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N138">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O138"/>
+      <c s="16" t="str" r="P138"/>
+      <c s="16" t="str" r="Q138"/>
+      <c s="16" t="str" r="R138"/>
+      <c s="16" t="inlineStr" r="S138">
+        <is>
+          <t xml:space="preserve">2633006529</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T138"/>
+      <c s="16" t="inlineStr" r="U138">
+        <is>
+          <t xml:space="preserve">5001558300</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V138">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y138">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z138">
+        <is>
+          <t xml:space="preserve">10047279    </t>
+        </is>
+      </c>
+      <c s="17" r="AA138">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB138">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC138">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD138"/>
+      <c s="16" t="inlineStr" r="AF138">
+        <is>
+          <t xml:space="preserve">5010550206</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG138"/>
+    </row>
+    <row r="139" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A139">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B139">
+        <is>
+          <t xml:space="preserve">08:56:21</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C139">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D139">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E139">
+        <v>201081</v>
+      </c>
+      <c s="19" t="inlineStr" r="F139">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H139">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I139">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J139">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K139">
+        <is>
+          <t xml:space="preserve">5012458463</t>
+        </is>
+      </c>
+      <c s="20" r="L139">
+        <v>2021.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M139">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N139">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O139"/>
+      <c s="19" t="str" r="P139"/>
+      <c s="19" t="str" r="Q139"/>
+      <c s="19" t="str" r="R139"/>
+      <c s="19" t="inlineStr" r="S139">
+        <is>
+          <t xml:space="preserve">2635002623</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T139"/>
+      <c s="19" t="inlineStr" r="U139">
+        <is>
+          <t xml:space="preserve">5001558302</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V139">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y139">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z139">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="20" r="AA139">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB139">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC139">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD139">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF139">
+        <is>
+          <t xml:space="preserve">2003984074</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG139"/>
+    </row>
+    <row r="140" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A140">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B140">
+        <is>
+          <t xml:space="preserve">09:04:09</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C140">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D140">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E140">
+        <v>221300</v>
+      </c>
+      <c s="16" t="inlineStr" r="F140">
+        <is>
+          <t xml:space="preserve">CH PLANA 3,75mm SAC 300 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H140">
+        <is>
+          <t xml:space="preserve">3,75mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I140">
+        <is>
+          <t xml:space="preserve">SAC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J140">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K140">
+        <is>
+          <t xml:space="preserve">5012458493</t>
+        </is>
+      </c>
+      <c s="17" r="L140">
+        <v>2086.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M140">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N140">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O140"/>
+      <c s="16" t="str" r="P140"/>
+      <c s="16" t="str" r="Q140"/>
+      <c s="16" t="str" r="R140"/>
+      <c s="16" t="inlineStr" r="S140">
+        <is>
+          <t xml:space="preserve">2633006530</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T140"/>
+      <c s="16" t="inlineStr" r="U140">
+        <is>
+          <t xml:space="preserve">5001558348</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V140">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y140">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z140">
+        <is>
+          <t xml:space="preserve">10047279    </t>
+        </is>
+      </c>
+      <c s="17" r="AA140">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB140">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC140">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD140"/>
+      <c s="16" t="inlineStr" r="AF140">
+        <is>
+          <t xml:space="preserve">5010550206</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG140"/>
+    </row>
+    <row r="141" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A141">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B141">
+        <is>
+          <t xml:space="preserve">09:07:27</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C141">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D141">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E141">
+        <v>200746</v>
+      </c>
+      <c s="19" t="inlineStr" r="F141">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H141">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I141">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J141">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K141">
+        <is>
+          <t xml:space="preserve">5012458500</t>
+        </is>
+      </c>
+      <c s="20" r="L141">
+        <v>1058.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M141">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N141">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O141"/>
+      <c s="19" t="str" r="P141"/>
+      <c s="19" t="str" r="Q141"/>
+      <c s="19" t="str" r="R141"/>
+      <c s="19" t="inlineStr" r="S141">
+        <is>
+          <t xml:space="preserve">2636005760</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T141"/>
+      <c s="19" t="inlineStr" r="U141">
+        <is>
+          <t xml:space="preserve">5001558366</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V141">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y141">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z141">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" r="AA141">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB141">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC141">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD141">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF141">
+        <is>
+          <t xml:space="preserve">2003908400</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG141"/>
+    </row>
+    <row r="142" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A142">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B142">
+        <is>
+          <t xml:space="preserve">09:13:07</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C142">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D142">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E142">
+        <v>201081</v>
+      </c>
+      <c s="16" t="inlineStr" r="F142">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H142">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I142">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J142">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K142">
+        <is>
+          <t xml:space="preserve">5012458516</t>
+        </is>
+      </c>
+      <c s="17" r="L142">
+        <v>2561.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M142">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N142">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O142"/>
+      <c s="16" t="str" r="P142"/>
+      <c s="16" t="str" r="Q142"/>
+      <c s="16" t="str" r="R142"/>
+      <c s="16" t="inlineStr" r="S142">
+        <is>
+          <t xml:space="preserve">2635002624</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T142"/>
+      <c s="16" t="inlineStr" r="U142">
+        <is>
+          <t xml:space="preserve">5001558413</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V142">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y142">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z142">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="17" r="AA142">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB142">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC142">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD142">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF142">
+        <is>
+          <t xml:space="preserve">2003984074</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG142"/>
+    </row>
+    <row r="143" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A143">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B143">
+        <is>
+          <t xml:space="preserve">09:14:36</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C143">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D143">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E143">
+        <v>221300</v>
+      </c>
+      <c s="19" t="inlineStr" r="F143">
+        <is>
+          <t xml:space="preserve">CH PLANA 3,75mm SAC 300 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H143">
+        <is>
+          <t xml:space="preserve">3,75mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I143">
+        <is>
+          <t xml:space="preserve">SAC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J143">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K143">
+        <is>
+          <t xml:space="preserve">5012458519</t>
+        </is>
+      </c>
+      <c s="20" r="L143">
+        <v>2084.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M143">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N143">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O143"/>
+      <c s="19" t="str" r="P143"/>
+      <c s="19" t="str" r="Q143"/>
+      <c s="19" t="str" r="R143"/>
+      <c s="19" t="inlineStr" r="S143">
+        <is>
+          <t xml:space="preserve">2633006531</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T143"/>
+      <c s="19" t="inlineStr" r="U143">
+        <is>
+          <t xml:space="preserve">5001558416</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V143">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y143">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z143">
+        <is>
+          <t xml:space="preserve">10047279    </t>
+        </is>
+      </c>
+      <c s="20" r="AA143">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB143">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC143">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD143"/>
+      <c s="19" t="inlineStr" r="AF143">
+        <is>
+          <t xml:space="preserve">5010550206</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG143"/>
+    </row>
+    <row r="144" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A144">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B144">
+        <is>
+          <t xml:space="preserve">09:18:16</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C144">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D144">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E144">
+        <v>216592</v>
+      </c>
+      <c s="16" t="inlineStr" r="F144">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2040mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H144">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I144">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J144">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K144">
+        <is>
+          <t xml:space="preserve">5012458535</t>
+        </is>
+      </c>
+      <c s="17" r="L144">
+        <v>2013.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M144">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N144">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O144"/>
+      <c s="16" t="str" r="P144"/>
+      <c s="16" t="str" r="Q144"/>
+      <c s="16" t="str" r="R144"/>
+      <c s="16" t="inlineStr" r="S144">
+        <is>
+          <t xml:space="preserve">2632005154</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T144"/>
+      <c s="16" t="inlineStr" r="U144">
+        <is>
+          <t xml:space="preserve">5001558436</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V144">
+        <is>
+          <t xml:space="preserve">20131525</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y144">
+        <is>
+          <t xml:space="preserve">L P A METALURGICA LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z144">
+        <is>
+          <t xml:space="preserve">10047268    </t>
+        </is>
+      </c>
+      <c s="17" r="AA144">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB144">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC144">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD144">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF144">
+        <is>
+          <t xml:space="preserve">2003683061</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG144"/>
+    </row>
+    <row r="145" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A145">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B145">
+        <is>
+          <t xml:space="preserve">09:23:01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C145">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D145">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E145">
+        <v>221300</v>
+      </c>
+      <c s="19" t="inlineStr" r="F145">
+        <is>
+          <t xml:space="preserve">CH PLANA 3,75mm SAC 300 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H145">
+        <is>
+          <t xml:space="preserve">3,75mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I145">
+        <is>
+          <t xml:space="preserve">SAC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J145">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K145">
+        <is>
+          <t xml:space="preserve">5012458551</t>
+        </is>
+      </c>
+      <c s="20" r="L145">
+        <v>2092.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M145">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N145">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O145"/>
+      <c s="19" t="str" r="P145"/>
+      <c s="19" t="str" r="Q145"/>
+      <c s="19" t="str" r="R145"/>
+      <c s="19" t="inlineStr" r="S145">
+        <is>
+          <t xml:space="preserve">2633006532</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T145"/>
+      <c s="19" t="inlineStr" r="U145">
+        <is>
+          <t xml:space="preserve">5001558463</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V145">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y145">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z145">
+        <is>
+          <t xml:space="preserve">10047279    </t>
+        </is>
+      </c>
+      <c s="20" r="AA145">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB145">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC145">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD145"/>
+      <c s="19" t="inlineStr" r="AF145">
+        <is>
+          <t xml:space="preserve">5010550206</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG145"/>
+    </row>
+    <row r="146" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A146">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B146">
+        <is>
+          <t xml:space="preserve">09:24:23</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C146">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D146">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E146">
+        <v>201081</v>
+      </c>
+      <c s="16" t="inlineStr" r="F146">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H146">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I146">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J146">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K146">
+        <is>
+          <t xml:space="preserve">5012458554</t>
+        </is>
+      </c>
+      <c s="17" r="L146">
+        <v>2445.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M146">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N146">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O146"/>
+      <c s="16" t="str" r="P146"/>
+      <c s="16" t="str" r="Q146"/>
+      <c s="16" t="str" r="R146"/>
+      <c s="16" t="inlineStr" r="S146">
+        <is>
+          <t xml:space="preserve">2635002625</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T146"/>
+      <c s="16" t="inlineStr" r="U146">
+        <is>
+          <t xml:space="preserve">5001558466</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V146">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y146">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z146">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="17" r="AA146">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB146">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC146">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD146">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF146">
+        <is>
+          <t xml:space="preserve">2003984074</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG146"/>
+    </row>
+    <row r="147" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A147">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B147">
+        <is>
+          <t xml:space="preserve">09:30:54</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C147">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D147">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E147">
+        <v>201081</v>
+      </c>
+      <c s="19" t="inlineStr" r="F147">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H147">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I147">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J147">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K147">
+        <is>
+          <t xml:space="preserve">5012458570</t>
+        </is>
+      </c>
+      <c s="20" r="L147">
+        <v>260.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M147">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N147">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O147">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P147">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q147"/>
+      <c s="19" t="str" r="R147"/>
+      <c s="19" t="inlineStr" r="S147">
+        <is>
+          <t xml:space="preserve">2635002626</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T147"/>
+      <c s="19" t="inlineStr" r="U147">
+        <is>
+          <t xml:space="preserve">5001558502</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V147">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y147">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z147">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="20" r="AA147">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB147">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC147">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD147">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF147">
+        <is>
+          <t xml:space="preserve">2003984074</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG147"/>
+    </row>
+    <row r="148" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A148">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B148">
+        <is>
+          <t xml:space="preserve">09:32:00</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C148">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D148">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E148">
+        <v>221300</v>
+      </c>
+      <c s="16" t="inlineStr" r="F148">
+        <is>
+          <t xml:space="preserve">CH PLANA 3,75mm SAC 300 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H148">
+        <is>
+          <t xml:space="preserve">3,75mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I148">
+        <is>
+          <t xml:space="preserve">SAC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J148">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K148">
+        <is>
+          <t xml:space="preserve">5012458579</t>
+        </is>
+      </c>
+      <c s="17" r="L148">
+        <v>1677.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M148">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N148">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O148"/>
+      <c s="16" t="str" r="P148"/>
+      <c s="16" t="str" r="Q148"/>
+      <c s="16" t="str" r="R148"/>
+      <c s="16" t="inlineStr" r="S148">
+        <is>
+          <t xml:space="preserve">2633006533</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T148"/>
+      <c s="16" t="inlineStr" r="U148">
+        <is>
+          <t xml:space="preserve">5001558506</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V148">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y148">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z148">
+        <is>
+          <t xml:space="preserve">10047279    </t>
+        </is>
+      </c>
+      <c s="17" r="AA148">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB148">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC148">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD148"/>
+      <c s="16" t="inlineStr" r="AF148">
+        <is>
+          <t xml:space="preserve">5010550206</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG148"/>
+    </row>
+    <row r="149" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A149">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B149">
+        <is>
+          <t xml:space="preserve">09:34:33</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C149">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D149">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E149">
+        <v>222300</v>
+      </c>
+      <c s="19" t="inlineStr" r="F149">
+        <is>
+          <t xml:space="preserve">CH PLANA 3,75mm SAC 300 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H149">
+        <is>
+          <t xml:space="preserve">3,75mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I149">
+        <is>
+          <t xml:space="preserve">SAC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J149">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K149">
+        <is>
+          <t xml:space="preserve">5012458591</t>
+        </is>
+      </c>
+      <c s="20" r="L149">
+        <v>129.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M149">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N149">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O149">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P149">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q149"/>
+      <c s="19" t="str" r="R149"/>
+      <c s="19" t="inlineStr" r="S149">
+        <is>
+          <t xml:space="preserve">2633006534</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T149"/>
+      <c s="19" t="inlineStr" r="U149">
+        <is>
+          <t xml:space="preserve">5001558518</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V149">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y149">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z149">
+        <is>
+          <t xml:space="preserve">10047280    </t>
+        </is>
+      </c>
+      <c s="20" r="AA149">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB149">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC149">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD149"/>
+      <c s="19" t="inlineStr" r="AF149">
+        <is>
+          <t xml:space="preserve">5010550206</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG149"/>
+    </row>
+    <row r="150" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A150">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B150">
+        <is>
+          <t xml:space="preserve">09:40:31</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C150">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D150">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E150">
+        <v>216592</v>
+      </c>
+      <c s="16" t="inlineStr" r="F150">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2040mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H150">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I150">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J150">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K150">
+        <is>
+          <t xml:space="preserve">5012458604</t>
+        </is>
+      </c>
+      <c s="17" r="L150">
+        <v>1993.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M150">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N150">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O150"/>
+      <c s="16" t="str" r="P150"/>
+      <c s="16" t="str" r="Q150"/>
+      <c s="16" t="str" r="R150"/>
+      <c s="16" t="inlineStr" r="S150">
+        <is>
+          <t xml:space="preserve">2632005155</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T150"/>
+      <c s="16" t="inlineStr" r="U150">
+        <is>
+          <t xml:space="preserve">5001558542</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V150">
+        <is>
+          <t xml:space="preserve">20131525</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y150">
+        <is>
+          <t xml:space="preserve">L P A METALURGICA LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z150">
+        <is>
+          <t xml:space="preserve">10047268    </t>
+        </is>
+      </c>
+      <c s="17" r="AA150">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB150">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC150">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD150">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF150">
+        <is>
+          <t xml:space="preserve">2003683061</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG150"/>
+    </row>
+    <row r="151" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A151">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B151">
+        <is>
+          <t xml:space="preserve">09:48:06</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C151">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D151">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E151">
+        <v>200746</v>
+      </c>
+      <c s="19" t="inlineStr" r="F151">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H151">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I151">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J151">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K151">
+        <is>
+          <t xml:space="preserve">5012458635</t>
+        </is>
+      </c>
+      <c s="20" r="L151">
+        <v>1058.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M151">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N151">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O151"/>
+      <c s="19" t="str" r="P151"/>
+      <c s="19" t="str" r="Q151"/>
+      <c s="19" t="str" r="R151"/>
+      <c s="19" t="inlineStr" r="S151">
+        <is>
+          <t xml:space="preserve">2636005761</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T151"/>
+      <c s="19" t="inlineStr" r="U151">
+        <is>
+          <t xml:space="preserve">5001558588</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V151">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y151">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z151">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" r="AA151">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB151">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC151">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD151">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF151">
+        <is>
+          <t xml:space="preserve">2003908400</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG151"/>
+    </row>
+    <row r="152" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A152">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B152">
+        <is>
+          <t xml:space="preserve">10:04:10</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C152">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D152">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E152">
+        <v>220588</v>
+      </c>
+      <c s="16" t="inlineStr" r="F152">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2150mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H152">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I152">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J152">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K152">
+        <is>
+          <t xml:space="preserve">5012458706</t>
+        </is>
+      </c>
+      <c s="17" r="L152">
+        <v>1662.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M152">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N152">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O152"/>
+      <c s="16" t="str" r="P152"/>
+      <c s="16" t="str" r="Q152"/>
+      <c s="16" t="str" r="R152"/>
+      <c s="16" t="inlineStr" r="S152">
+        <is>
+          <t xml:space="preserve">2632005156</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T152"/>
+      <c s="16" t="inlineStr" r="U152">
+        <is>
+          <t xml:space="preserve">5001558710</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V152">
+        <is>
+          <t xml:space="preserve">20131525</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y152">
+        <is>
+          <t xml:space="preserve">L P A METALURGICA LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z152">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="17" r="AA152">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB152">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC152">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD152">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF152">
+        <is>
+          <t xml:space="preserve">2003683061</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG152"/>
+    </row>
+    <row r="153" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A153">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B153">
+        <is>
+          <t xml:space="preserve">10:19:19</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C153">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D153">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E153">
+        <v>200746</v>
+      </c>
+      <c s="19" t="inlineStr" r="F153">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H153">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I153">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J153">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K153">
+        <is>
+          <t xml:space="preserve">5012458755</t>
+        </is>
+      </c>
+      <c s="20" r="L153">
+        <v>1055.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M153">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N153">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O153"/>
+      <c s="19" t="str" r="P153"/>
+      <c s="19" t="str" r="Q153"/>
+      <c s="19" t="str" r="R153"/>
+      <c s="19" t="inlineStr" r="S153">
+        <is>
+          <t xml:space="preserve">2636005762</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T153"/>
+      <c s="19" t="inlineStr" r="U153">
+        <is>
+          <t xml:space="preserve">5001558784</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V153">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y153">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z153">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" r="AA153">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB153">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC153">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD153">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF153">
+        <is>
+          <t xml:space="preserve">2003908400</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG153"/>
+    </row>
+    <row r="154" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A154">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B154">
+        <is>
+          <t xml:space="preserve">10:23:05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C154">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D154">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E154">
+        <v>200943</v>
+      </c>
+      <c s="16" t="inlineStr" r="F154">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H154">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I154">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J154">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K154">
+        <is>
+          <t xml:space="preserve">5012458770</t>
+        </is>
+      </c>
+      <c s="17" r="L154">
+        <v>921.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M154">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N154">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O154">
+        <is>
+          <t xml:space="preserve">0070</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P154">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q154"/>
+      <c s="16" t="str" r="R154"/>
+      <c s="16" t="inlineStr" r="S154">
+        <is>
+          <t xml:space="preserve">2635002627</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T154"/>
+      <c s="16" t="inlineStr" r="U154">
+        <is>
+          <t xml:space="preserve">5001558799</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V154">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y154">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z154">
+        <is>
+          <t xml:space="preserve">10047456    </t>
+        </is>
+      </c>
+      <c s="17" r="AA154">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB154">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC154">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD154">
+        <is>
+          <t xml:space="preserve">TRO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF154">
+        <is>
+          <t xml:space="preserve">2003390329</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG154"/>
+    </row>
+    <row r="155" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A155">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B155">
+        <is>
+          <t xml:space="preserve">10:23:21</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C155">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D155">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E155">
+        <v>200943</v>
+      </c>
+      <c s="19" t="inlineStr" r="F155">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H155">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I155">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J155">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K155">
+        <is>
+          <t xml:space="preserve">5012458771</t>
+        </is>
+      </c>
+      <c s="20" r="L155">
+        <v>2043.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M155">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N155">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O155"/>
+      <c s="19" t="str" r="P155"/>
+      <c s="19" t="str" r="Q155"/>
+      <c s="19" t="str" r="R155"/>
+      <c s="19" t="inlineStr" r="S155">
+        <is>
+          <t xml:space="preserve">2635002628</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T155"/>
+      <c s="19" t="inlineStr" r="U155">
+        <is>
+          <t xml:space="preserve">5001558810</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V155">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y155">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z155">
+        <is>
+          <t xml:space="preserve">10047456    </t>
+        </is>
+      </c>
+      <c s="20" r="AA155">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB155">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC155">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD155">
+        <is>
+          <t xml:space="preserve">TRO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF155">
+        <is>
+          <t xml:space="preserve">2003390329</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG155"/>
+    </row>
+    <row r="156" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A156">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B156">
+        <is>
+          <t xml:space="preserve">10:40:14</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C156">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D156">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E156">
+        <v>200943</v>
+      </c>
+      <c s="16" t="inlineStr" r="F156">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H156">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I156">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J156">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K156">
+        <is>
+          <t xml:space="preserve">5012458826</t>
+        </is>
+      </c>
+      <c s="17" r="L156">
+        <v>2036.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M156">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N156">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O156"/>
+      <c s="16" t="str" r="P156"/>
+      <c s="16" t="str" r="Q156"/>
+      <c s="16" t="str" r="R156"/>
+      <c s="16" t="inlineStr" r="S156">
+        <is>
+          <t xml:space="preserve">2635002629</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T156"/>
+      <c s="16" t="inlineStr" r="U156">
+        <is>
+          <t xml:space="preserve">5001558903</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V156">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y156">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z156">
+        <is>
+          <t xml:space="preserve">10047456    </t>
+        </is>
+      </c>
+      <c s="17" r="AA156">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB156">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC156">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD156">
+        <is>
+          <t xml:space="preserve">TRO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF156">
+        <is>
+          <t xml:space="preserve">2003390329</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG156"/>
+    </row>
+    <row r="157" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A157">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B157">
+        <is>
+          <t xml:space="preserve">11:03:06</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C157">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D157">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E157">
+        <v>220588</v>
+      </c>
+      <c s="19" t="inlineStr" r="F157">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2150mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H157">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I157">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J157">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K157">
+        <is>
+          <t xml:space="preserve">5012458887</t>
+        </is>
+      </c>
+      <c s="20" r="L157">
+        <v>249.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M157">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N157">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O157"/>
+      <c s="19" t="str" r="P157"/>
+      <c s="19" t="str" r="Q157"/>
+      <c s="19" t="str" r="R157"/>
+      <c s="19" t="inlineStr" r="S157">
+        <is>
+          <t xml:space="preserve">2632005157</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T157"/>
+      <c s="19" t="inlineStr" r="U157">
+        <is>
+          <t xml:space="preserve">5001559004</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V157">
+        <is>
+          <t xml:space="preserve">20131525</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y157">
+        <is>
+          <t xml:space="preserve">L P A METALURGICA LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z157">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="20" r="AA157">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB157">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC157">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD157">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF157">
+        <is>
+          <t xml:space="preserve">2003683109</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG157"/>
+    </row>
+    <row r="158" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A158">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B158">
+        <is>
+          <t xml:space="preserve">11:04:16</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C158">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D158">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E158">
+        <v>200943</v>
+      </c>
+      <c s="16" t="inlineStr" r="F158">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H158">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I158">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J158">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K158">
+        <is>
+          <t xml:space="preserve">5012458891</t>
+        </is>
+      </c>
+      <c s="17" r="L158">
+        <v>2038.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M158">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N158">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O158"/>
+      <c s="16" t="str" r="P158"/>
+      <c s="16" t="str" r="Q158"/>
+      <c s="16" t="str" r="R158"/>
+      <c s="16" t="inlineStr" r="S158">
+        <is>
+          <t xml:space="preserve">2635002630</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T158"/>
+      <c s="16" t="inlineStr" r="U158">
+        <is>
+          <t xml:space="preserve">5001559008</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V158">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y158">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z158">
+        <is>
+          <t xml:space="preserve">10047456    </t>
+        </is>
+      </c>
+      <c s="17" r="AA158">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB158">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC158">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD158">
+        <is>
+          <t xml:space="preserve">TRO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF158">
+        <is>
+          <t xml:space="preserve">2003390329</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG158"/>
+    </row>
+    <row r="159" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A159">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B159">
+        <is>
+          <t xml:space="preserve">11:17:56</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C159">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D159">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E159">
+        <v>200746</v>
+      </c>
+      <c s="19" t="inlineStr" r="F159">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H159">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I159">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J159">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K159">
+        <is>
+          <t xml:space="preserve">5012458948</t>
+        </is>
+      </c>
+      <c s="20" r="L159">
+        <v>826.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M159">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N159">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O159"/>
+      <c s="19" t="str" r="P159"/>
+      <c s="19" t="str" r="Q159"/>
+      <c s="19" t="str" r="R159"/>
+      <c s="19" t="inlineStr" r="S159">
+        <is>
+          <t xml:space="preserve">2636005763</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T159"/>
+      <c s="19" t="inlineStr" r="U159">
+        <is>
+          <t xml:space="preserve">5001559133</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V159">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y159">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z159">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" r="AA159">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB159">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC159">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD159">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF159">
+        <is>
+          <t xml:space="preserve">2003908400</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG159"/>
+    </row>
+    <row r="160" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A160">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B160">
+        <is>
+          <t xml:space="preserve">11:23:27</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C160">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D160">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E160">
+        <v>200943</v>
+      </c>
+      <c s="16" t="inlineStr" r="F160">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H160">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I160">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J160">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K160">
+        <is>
+          <t xml:space="preserve">5012458966</t>
+        </is>
+      </c>
+      <c s="17" r="L160">
+        <v>811.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M160">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N160">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O160"/>
+      <c s="16" t="str" r="P160"/>
+      <c s="16" t="str" r="Q160"/>
+      <c s="16" t="str" r="R160"/>
+      <c s="16" t="inlineStr" r="S160">
+        <is>
+          <t xml:space="preserve">2635002631</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T160"/>
+      <c s="16" t="inlineStr" r="U160">
+        <is>
+          <t xml:space="preserve">5001559172</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V160">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y160">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z160">
+        <is>
+          <t xml:space="preserve">10047456    </t>
+        </is>
+      </c>
+      <c s="17" r="AA160">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB160">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC160">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD160">
+        <is>
+          <t xml:space="preserve">TRO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF160">
+        <is>
+          <t xml:space="preserve">2003390329</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG160"/>
+    </row>
+    <row r="161" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A161">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B161">
+        <is>
+          <t xml:space="preserve">11:49:39</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C161">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D161">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E161">
+        <v>200800</v>
+      </c>
+      <c s="19" t="inlineStr" r="F161">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,95mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H161">
+        <is>
+          <t xml:space="preserve">1,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I161">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J161">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K161">
+        <is>
+          <t xml:space="preserve">5012459023</t>
+        </is>
+      </c>
+      <c s="20" r="L161">
+        <v>1010.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M161">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N161">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O161"/>
+      <c s="19" t="str" r="P161"/>
+      <c s="19" t="str" r="Q161"/>
+      <c s="19" t="str" r="R161"/>
+      <c s="19" t="inlineStr" r="S161">
+        <is>
+          <t xml:space="preserve">2636005764</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T161"/>
+      <c s="19" t="inlineStr" r="U161">
+        <is>
+          <t xml:space="preserve">5001559274</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V161">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y161">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z161">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" r="AA161">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB161">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC161">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD161">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF161">
+        <is>
+          <t xml:space="preserve">2003908612</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG161"/>
+    </row>
+    <row r="162" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A162">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B162">
+        <is>
+          <t xml:space="preserve">11:58:02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C162">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D162">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E162">
+        <v>220588</v>
+      </c>
+      <c s="16" t="inlineStr" r="F162">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2150mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H162">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I162">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J162">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K162">
+        <is>
+          <t xml:space="preserve">5012459046</t>
+        </is>
+      </c>
+      <c s="17" r="L162">
+        <v>2062.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M162">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N162">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O162"/>
+      <c s="16" t="str" r="P162"/>
+      <c s="16" t="str" r="Q162"/>
+      <c s="16" t="str" r="R162"/>
+      <c s="16" t="inlineStr" r="S162">
+        <is>
+          <t xml:space="preserve">2632005158</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T162"/>
+      <c s="16" t="inlineStr" r="U162">
+        <is>
+          <t xml:space="preserve">5001559322</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V162">
+        <is>
+          <t xml:space="preserve">20131525</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y162">
+        <is>
+          <t xml:space="preserve">L P A METALURGICA LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z162">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="17" r="AA162">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB162">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC162">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD162">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF162">
+        <is>
+          <t xml:space="preserve">2003683109</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG162"/>
+    </row>
+    <row r="163" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A163">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B163">
+        <is>
+          <t xml:space="preserve">12:09:35</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C163">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D163">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E163">
+        <v>200943</v>
+      </c>
+      <c s="19" t="inlineStr" r="F163">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H163">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I163">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J163">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K163">
+        <is>
+          <t xml:space="preserve">5012459061</t>
+        </is>
+      </c>
+      <c s="20" r="L163">
+        <v>1537.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M163">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N163">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O163">
+        <is>
+          <t xml:space="preserve">0070</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P163">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q163"/>
+      <c s="19" t="str" r="R163"/>
+      <c s="19" t="inlineStr" r="S163">
+        <is>
+          <t xml:space="preserve">2635002632</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T163"/>
+      <c s="19" t="inlineStr" r="U163">
+        <is>
+          <t xml:space="preserve">5001559349</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V163">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y163">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z163">
+        <is>
+          <t xml:space="preserve">10047456    </t>
+        </is>
+      </c>
+      <c s="20" r="AA163">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB163">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC163">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD163">
+        <is>
+          <t xml:space="preserve">TRO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF163">
+        <is>
+          <t xml:space="preserve">2003390329</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG163"/>
+    </row>
+    <row r="164" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A164">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B164">
+        <is>
+          <t xml:space="preserve">12:15:45</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C164">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D164">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E164">
+        <v>220588</v>
+      </c>
+      <c s="16" t="inlineStr" r="F164">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2150mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H164">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I164">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J164">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K164">
+        <is>
+          <t xml:space="preserve">5012459070</t>
+        </is>
+      </c>
+      <c s="17" r="L164">
+        <v>1040.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M164">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N164">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O164"/>
+      <c s="16" t="str" r="P164"/>
+      <c s="16" t="str" r="Q164"/>
+      <c s="16" t="str" r="R164"/>
+      <c s="16" t="inlineStr" r="S164">
+        <is>
+          <t xml:space="preserve">2632005159</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T164"/>
+      <c s="16" t="inlineStr" r="U164">
+        <is>
+          <t xml:space="preserve">5001559368</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V164">
+        <is>
+          <t xml:space="preserve">20131525</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y164">
+        <is>
+          <t xml:space="preserve">L P A METALURGICA LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z164">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="17" r="AA164">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB164">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC164">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD164">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF164">
+        <is>
+          <t xml:space="preserve">2003683109</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG164"/>
+    </row>
+    <row r="165" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A165">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B165">
+        <is>
+          <t xml:space="preserve">12:30:02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C165">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D165">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E165">
+        <v>200943</v>
+      </c>
+      <c s="19" t="inlineStr" r="F165">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H165">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I165">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J165">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K165">
+        <is>
+          <t xml:space="preserve">5012459099</t>
+        </is>
+      </c>
+      <c s="20" r="L165">
+        <v>2009.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M165">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N165">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O165"/>
+      <c s="19" t="str" r="P165"/>
+      <c s="19" t="str" r="Q165"/>
+      <c s="19" t="str" r="R165"/>
+      <c s="19" t="inlineStr" r="S165">
+        <is>
+          <t xml:space="preserve">2635002633</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T165"/>
+      <c s="19" t="inlineStr" r="U165">
+        <is>
+          <t xml:space="preserve">5001559423</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V165">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y165">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z165">
+        <is>
+          <t xml:space="preserve">10047456    </t>
+        </is>
+      </c>
+      <c s="20" r="AA165">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB165">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC165">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD165">
+        <is>
+          <t xml:space="preserve">TRO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF165">
+        <is>
+          <t xml:space="preserve">2003401644</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG165"/>
+    </row>
+    <row r="166" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A166">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B166">
+        <is>
+          <t xml:space="preserve">12:30:28</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C166">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D166">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E166">
+        <v>200800</v>
+      </c>
+      <c s="16" t="inlineStr" r="F166">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,95mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H166">
+        <is>
+          <t xml:space="preserve">1,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I166">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J166">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K166">
+        <is>
+          <t xml:space="preserve">5012459101</t>
+        </is>
+      </c>
+      <c s="17" r="L166">
+        <v>1014.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M166">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N166">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O166"/>
+      <c s="16" t="str" r="P166"/>
+      <c s="16" t="str" r="Q166"/>
+      <c s="16" t="str" r="R166"/>
+      <c s="16" t="inlineStr" r="S166">
+        <is>
+          <t xml:space="preserve">2636005765</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T166"/>
+      <c s="16" t="inlineStr" r="U166">
+        <is>
+          <t xml:space="preserve">5001559425</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V166">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y166">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z166">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="17" r="AA166">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB166">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC166">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD166">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF166">
+        <is>
+          <t xml:space="preserve">2003908612</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG166"/>
+    </row>
+    <row r="167" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A167">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B167">
+        <is>
+          <t xml:space="preserve">12:44:16</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C167">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D167">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E167">
+        <v>216593</v>
+      </c>
+      <c s="19" t="inlineStr" r="F167">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2100mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H167">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I167">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J167">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K167">
+        <is>
+          <t xml:space="preserve">5012459150</t>
+        </is>
+      </c>
+      <c s="20" r="L167">
+        <v>2031.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M167">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N167">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O167"/>
+      <c s="19" t="str" r="P167"/>
+      <c s="19" t="str" r="Q167"/>
+      <c s="19" t="str" r="R167"/>
+      <c s="19" t="inlineStr" r="S167">
+        <is>
+          <t xml:space="preserve">2632005160</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T167"/>
+      <c s="19" t="inlineStr" r="U167">
+        <is>
+          <t xml:space="preserve">5001559492</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V167">
+        <is>
+          <t xml:space="preserve">20131525</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y167">
+        <is>
+          <t xml:space="preserve">L P A METALURGICA LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z167">
+        <is>
+          <t xml:space="preserve">10047270    </t>
+        </is>
+      </c>
+      <c s="20" r="AA167">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB167">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC167">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD167">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF167">
+        <is>
+          <t xml:space="preserve">2003683109</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG167"/>
+    </row>
+    <row r="168" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A168">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B168">
+        <is>
+          <t xml:space="preserve">12:56:56</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C168">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D168">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E168">
+        <v>200943</v>
+      </c>
+      <c s="16" t="inlineStr" r="F168">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H168">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I168">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J168">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K168">
+        <is>
+          <t xml:space="preserve">5012459183</t>
+        </is>
+      </c>
+      <c s="17" r="L168">
+        <v>2010.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M168">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N168">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O168"/>
+      <c s="16" t="str" r="P168"/>
+      <c s="16" t="str" r="Q168"/>
+      <c s="16" t="str" r="R168"/>
+      <c s="16" t="inlineStr" r="S168">
+        <is>
+          <t xml:space="preserve">2635002634</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T168"/>
+      <c s="16" t="inlineStr" r="U168">
+        <is>
+          <t xml:space="preserve">5001559535</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V168">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y168">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z168">
+        <is>
+          <t xml:space="preserve">10047456    </t>
+        </is>
+      </c>
+      <c s="17" r="AA168">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB168">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC168">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD168">
+        <is>
+          <t xml:space="preserve">TRO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF168">
+        <is>
+          <t xml:space="preserve">2003401644</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG168"/>
+    </row>
+    <row r="169" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A169">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B169">
+        <is>
+          <t xml:space="preserve">13:05:04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C169">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D169">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E169">
+        <v>216593</v>
+      </c>
+      <c s="19" t="inlineStr" r="F169">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2100mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H169">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I169">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J169">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K169">
+        <is>
+          <t xml:space="preserve">5012459219</t>
+        </is>
+      </c>
+      <c s="20" r="L169">
+        <v>2005.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M169">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N169">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O169"/>
+      <c s="19" t="str" r="P169"/>
+      <c s="19" t="str" r="Q169"/>
+      <c s="19" t="str" r="R169"/>
+      <c s="19" t="inlineStr" r="S169">
+        <is>
+          <t xml:space="preserve">2632005161</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T169"/>
+      <c s="19" t="inlineStr" r="U169">
+        <is>
+          <t xml:space="preserve">5001559569</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V169">
+        <is>
+          <t xml:space="preserve">20131525</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y169">
+        <is>
+          <t xml:space="preserve">L P A METALURGICA LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z169">
+        <is>
+          <t xml:space="preserve">10047270    </t>
+        </is>
+      </c>
+      <c s="20" r="AA169">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB169">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC169">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD169">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF169">
+        <is>
+          <t xml:space="preserve">2003683109</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG169"/>
+    </row>
+    <row r="170" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A170">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B170">
+        <is>
+          <t xml:space="preserve">13:23:08</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C170">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D170">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E170">
+        <v>200943</v>
+      </c>
+      <c s="16" t="inlineStr" r="F170">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H170">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I170">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J170">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K170">
+        <is>
+          <t xml:space="preserve">5012459295</t>
+        </is>
+      </c>
+      <c s="17" r="L170">
+        <v>157.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M170">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N170">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O170">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P170">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q170"/>
+      <c s="16" t="str" r="R170"/>
+      <c s="16" t="inlineStr" r="S170">
+        <is>
+          <t xml:space="preserve">2635002635</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T170"/>
+      <c s="16" t="inlineStr" r="U170">
+        <is>
+          <t xml:space="preserve">5001559653</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V170">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y170">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z170">
+        <is>
+          <t xml:space="preserve">10047456    </t>
+        </is>
+      </c>
+      <c s="17" r="AA170">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB170">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC170">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD170">
+        <is>
+          <t xml:space="preserve">TRO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF170">
+        <is>
+          <t xml:space="preserve">2003401644</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG170"/>
+    </row>
+    <row r="171" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A171">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B171">
+        <is>
+          <t xml:space="preserve">13:27:59</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C171">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D171">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E171">
+        <v>200800</v>
+      </c>
+      <c s="19" t="inlineStr" r="F171">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,95mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H171">
+        <is>
+          <t xml:space="preserve">1,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I171">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J171">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K171">
+        <is>
+          <t xml:space="preserve">5012459304</t>
+        </is>
+      </c>
+      <c s="20" r="L171">
+        <v>1014.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M171">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N171">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O171"/>
+      <c s="19" t="str" r="P171"/>
+      <c s="19" t="str" r="Q171"/>
+      <c s="19" t="str" r="R171"/>
+      <c s="19" t="inlineStr" r="S171">
+        <is>
+          <t xml:space="preserve">2636005766</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T171"/>
+      <c s="19" t="inlineStr" r="U171">
+        <is>
+          <t xml:space="preserve">5001559663</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V171">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y171">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z171">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" r="AA171">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB171">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC171">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD171">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF171">
+        <is>
+          <t xml:space="preserve">2003908612</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG171"/>
+    </row>
+    <row r="172" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A172">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B172">
+        <is>
+          <t xml:space="preserve">13:28:15</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C172">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D172">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E172">
+        <v>200800</v>
+      </c>
+      <c s="16" t="inlineStr" r="F172">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,95mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H172">
+        <is>
+          <t xml:space="preserve">1,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I172">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J172">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K172">
+        <is>
+          <t xml:space="preserve">5012459306</t>
+        </is>
+      </c>
+      <c s="17" r="L172">
+        <v>1015.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M172">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N172">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O172"/>
+      <c s="16" t="str" r="P172"/>
+      <c s="16" t="str" r="Q172"/>
+      <c s="16" t="str" r="R172"/>
+      <c s="16" t="inlineStr" r="S172">
+        <is>
+          <t xml:space="preserve">2636005767</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T172"/>
+      <c s="16" t="inlineStr" r="U172">
+        <is>
+          <t xml:space="preserve">5001559665</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V172">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y172">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z172">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="17" r="AA172">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB172">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC172">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD172">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF172">
+        <is>
+          <t xml:space="preserve">2003908612</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG172"/>
+    </row>
+    <row r="173" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A173">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B173">
+        <is>
+          <t xml:space="preserve">13:42:02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C173">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D173">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E173">
+        <v>200800</v>
+      </c>
+      <c s="19" t="inlineStr" r="F173">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,95mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H173">
+        <is>
+          <t xml:space="preserve">1,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I173">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J173">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K173">
+        <is>
+          <t xml:space="preserve">5012459357</t>
+        </is>
+      </c>
+      <c s="20" r="L173">
+        <v>1011.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M173">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N173">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O173"/>
+      <c s="19" t="str" r="P173"/>
+      <c s="19" t="str" r="Q173"/>
+      <c s="19" t="str" r="R173"/>
+      <c s="19" t="inlineStr" r="S173">
+        <is>
+          <t xml:space="preserve">2636005768</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T173"/>
+      <c s="19" t="inlineStr" r="U173">
+        <is>
+          <t xml:space="preserve">5001559774</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V173">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y173">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z173">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" r="AA173">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB173">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC173">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD173">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF173">
+        <is>
+          <t xml:space="preserve">2003908612</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG173"/>
+    </row>
+    <row r="174" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A174">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B174">
+        <is>
+          <t xml:space="preserve">13:48:52</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C174">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D174">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E174">
+        <v>200943</v>
+      </c>
+      <c s="16" t="inlineStr" r="F174">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H174">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I174">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J174">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K174">
+        <is>
+          <t xml:space="preserve">5012459386</t>
+        </is>
+      </c>
+      <c s="17" r="L174">
+        <v>2008.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M174">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N174">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O174"/>
+      <c s="16" t="str" r="P174"/>
+      <c s="16" t="str" r="Q174"/>
+      <c s="16" t="str" r="R174"/>
+      <c s="16" t="inlineStr" r="S174">
+        <is>
+          <t xml:space="preserve">2635002636</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T174"/>
+      <c s="16" t="inlineStr" r="U174">
+        <is>
+          <t xml:space="preserve">5001559829</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V174">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y174">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z174">
+        <is>
+          <t xml:space="preserve">10047456    </t>
+        </is>
+      </c>
+      <c s="17" r="AA174">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB174">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC174">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD174">
+        <is>
+          <t xml:space="preserve">TRO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF174">
+        <is>
+          <t xml:space="preserve">2003401644</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG174"/>
+    </row>
+    <row r="175" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A175">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B175">
+        <is>
+          <t xml:space="preserve">14:00:14</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C175">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D175">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E175">
+        <v>200717</v>
+      </c>
+      <c s="19" t="inlineStr" r="F175">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H175">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I175">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J175">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K175">
+        <is>
+          <t xml:space="preserve">5012459412</t>
+        </is>
+      </c>
+      <c s="20" r="L175">
+        <v>179.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M175">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N175">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O175">
+        <is>
+          <t xml:space="preserve">0072</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P175">
+        <is>
+          <t xml:space="preserve">TRV - Quebra de superfície</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q175"/>
+      <c s="19" t="str" r="R175"/>
+      <c s="19" t="inlineStr" r="S175">
+        <is>
+          <t xml:space="preserve">2632005162</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T175"/>
+      <c s="19" t="inlineStr" r="U175">
+        <is>
+          <t xml:space="preserve">5001559929</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V175">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y175">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z175">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="20" r="AA175">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB175">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC175">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD175"/>
+      <c s="19" t="inlineStr" r="AF175">
+        <is>
+          <t xml:space="preserve">2003908285</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG175"/>
+    </row>
+    <row r="176" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A176">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B176">
+        <is>
+          <t xml:space="preserve">14:01:04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C176">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D176">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E176">
+        <v>201052</v>
+      </c>
+      <c s="16" t="inlineStr" r="F176">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H176">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I176">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J176">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K176">
+        <is>
+          <t xml:space="preserve">5012459419</t>
+        </is>
+      </c>
+      <c s="17" r="L176">
+        <v>2053.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M176">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N176">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O176"/>
+      <c s="16" t="str" r="P176"/>
+      <c s="16" t="str" r="Q176"/>
+      <c s="16" t="str" r="R176"/>
+      <c s="16" t="inlineStr" r="S176">
+        <is>
+          <t xml:space="preserve">2635002637</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T176"/>
+      <c s="16" t="inlineStr" r="U176">
+        <is>
+          <t xml:space="preserve">5001559937</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V176">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y176">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z176">
+        <is>
+          <t xml:space="preserve">10048030    </t>
+        </is>
+      </c>
+      <c s="17" r="AA176">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB176">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC176">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD176">
+        <is>
+          <t xml:space="preserve">USI</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF176">
+        <is>
+          <t xml:space="preserve">2003976352</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG176"/>
+    </row>
+    <row r="177" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A177">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B177">
+        <is>
+          <t xml:space="preserve">14:07:45</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C177">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D177">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E177">
+        <v>200717</v>
+      </c>
+      <c s="19" t="inlineStr" r="F177">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H177">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I177">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J177">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K177">
+        <is>
+          <t xml:space="preserve">5012459432</t>
+        </is>
+      </c>
+      <c s="20" r="L177">
+        <v>2014.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M177">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N177">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O177"/>
+      <c s="19" t="str" r="P177"/>
+      <c s="19" t="str" r="Q177"/>
+      <c s="19" t="str" r="R177"/>
+      <c s="19" t="inlineStr" r="S177">
+        <is>
+          <t xml:space="preserve">2632005163</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T177"/>
+      <c s="19" t="inlineStr" r="U177">
+        <is>
+          <t xml:space="preserve">5001559990</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V177">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y177">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z177">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="20" r="AA177">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB177">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC177">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD177"/>
+      <c s="19" t="inlineStr" r="AF177">
+        <is>
+          <t xml:space="preserve">2003908285</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG177"/>
+    </row>
+    <row r="178" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A178">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B178">
+        <is>
+          <t xml:space="preserve">14:16:56</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C178">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D178">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E178">
+        <v>201052</v>
+      </c>
+      <c s="16" t="inlineStr" r="F178">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H178">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I178">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J178">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K178">
+        <is>
+          <t xml:space="preserve">5012459470</t>
+        </is>
+      </c>
+      <c s="17" r="L178">
+        <v>2050.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M178">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N178">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O178"/>
+      <c s="16" t="str" r="P178"/>
+      <c s="16" t="str" r="Q178"/>
+      <c s="16" t="str" r="R178"/>
+      <c s="16" t="inlineStr" r="S178">
+        <is>
+          <t xml:space="preserve">2635002638</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T178"/>
+      <c s="16" t="inlineStr" r="U178">
+        <is>
+          <t xml:space="preserve">5001560061</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V178">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y178">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z178">
+        <is>
+          <t xml:space="preserve">10048030    </t>
+        </is>
+      </c>
+      <c s="17" r="AA178">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB178">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC178">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD178">
+        <is>
+          <t xml:space="preserve">USI</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF178">
+        <is>
+          <t xml:space="preserve">2003976352</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG178"/>
+    </row>
+    <row r="179" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A179">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B179">
+        <is>
+          <t xml:space="preserve">14:20:24</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C179">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D179">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E179">
+        <v>200717</v>
+      </c>
+      <c s="19" t="inlineStr" r="F179">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H179">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I179">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J179">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K179">
+        <is>
+          <t xml:space="preserve">5012459481</t>
+        </is>
+      </c>
+      <c s="20" r="L179">
+        <v>2012.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M179">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N179">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O179"/>
+      <c s="19" t="str" r="P179"/>
+      <c s="19" t="str" r="Q179"/>
+      <c s="19" t="str" r="R179"/>
+      <c s="19" t="inlineStr" r="S179">
+        <is>
+          <t xml:space="preserve">2632005164</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T179"/>
+      <c s="19" t="inlineStr" r="U179">
+        <is>
+          <t xml:space="preserve">5001560083</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V179">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y179">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z179">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="20" r="AA179">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB179">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC179">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD179"/>
+      <c s="19" t="inlineStr" r="AF179">
+        <is>
+          <t xml:space="preserve">2003908285</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG179"/>
+    </row>
+    <row r="180" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A180">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B180">
+        <is>
+          <t xml:space="preserve">14:30:35</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C180">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D180">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E180">
+        <v>201052</v>
+      </c>
+      <c s="16" t="inlineStr" r="F180">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H180">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I180">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J180">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K180">
+        <is>
+          <t xml:space="preserve">5012459501</t>
+        </is>
+      </c>
+      <c s="17" r="L180">
+        <v>2055.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M180">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N180">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O180"/>
+      <c s="16" t="str" r="P180"/>
+      <c s="16" t="str" r="Q180"/>
+      <c s="16" t="str" r="R180"/>
+      <c s="16" t="inlineStr" r="S180">
+        <is>
+          <t xml:space="preserve">2635002639</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T180"/>
+      <c s="16" t="inlineStr" r="U180">
+        <is>
+          <t xml:space="preserve">5001560127</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V180">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y180">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z180">
+        <is>
+          <t xml:space="preserve">10048030    </t>
+        </is>
+      </c>
+      <c s="17" r="AA180">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB180">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC180">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD180">
+        <is>
+          <t xml:space="preserve">USI</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF180">
+        <is>
+          <t xml:space="preserve">2003976352</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG180"/>
+    </row>
+    <row r="181" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A181">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B181">
+        <is>
+          <t xml:space="preserve">14:40:09</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C181">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D181">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E181">
+        <v>200800</v>
+      </c>
+      <c s="19" t="inlineStr" r="F181">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,95mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H181">
+        <is>
+          <t xml:space="preserve">1,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I181">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J181">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K181">
+        <is>
+          <t xml:space="preserve">5012459520</t>
+        </is>
+      </c>
+      <c s="20" r="L181">
+        <v>977.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M181">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N181">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O181"/>
+      <c s="19" t="str" r="P181"/>
+      <c s="19" t="str" r="Q181"/>
+      <c s="19" t="str" r="R181"/>
+      <c s="19" t="inlineStr" r="S181">
+        <is>
+          <t xml:space="preserve">2636005769</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T181"/>
+      <c s="19" t="inlineStr" r="U181">
+        <is>
+          <t xml:space="preserve">5001560176</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V181">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y181">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z181">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" r="AA181">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB181">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC181">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD181">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF181">
+        <is>
+          <t xml:space="preserve">2003908612</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG181"/>
+    </row>
+    <row r="182" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A182">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B182">
+        <is>
+          <t xml:space="preserve">14:41:04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C182">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D182">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E182">
+        <v>200717</v>
+      </c>
+      <c s="16" t="inlineStr" r="F182">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H182">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I182">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J182">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K182">
+        <is>
+          <t xml:space="preserve">5012459524</t>
+        </is>
+      </c>
+      <c s="17" r="L182">
+        <v>1796.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M182">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N182">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O182"/>
+      <c s="16" t="str" r="P182"/>
+      <c s="16" t="str" r="Q182"/>
+      <c s="16" t="str" r="R182"/>
+      <c s="16" t="inlineStr" r="S182">
+        <is>
+          <t xml:space="preserve">2632005165</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T182"/>
+      <c s="16" t="inlineStr" r="U182">
+        <is>
+          <t xml:space="preserve">5001560180</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V182">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y182">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z182">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="17" r="AA182">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB182">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC182">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD182"/>
+      <c s="16" t="inlineStr" r="AF182">
+        <is>
+          <t xml:space="preserve">2003908285</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG182"/>
+    </row>
+    <row r="183" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A183">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B183">
+        <is>
+          <t xml:space="preserve">14:45:46</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C183">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D183">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E183">
+        <v>200717</v>
+      </c>
+      <c s="19" t="inlineStr" r="F183">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H183">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I183">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J183">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K183">
+        <is>
+          <t xml:space="preserve">5012459540</t>
+        </is>
+      </c>
+      <c s="20" r="L183">
+        <v>300.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M183">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N183">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O183"/>
+      <c s="19" t="str" r="P183"/>
+      <c s="19" t="str" r="Q183"/>
+      <c s="19" t="str" r="R183"/>
+      <c s="19" t="inlineStr" r="S183">
+        <is>
+          <t xml:space="preserve">2632005166</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T183"/>
+      <c s="19" t="inlineStr" r="U183">
+        <is>
+          <t xml:space="preserve">5001560196</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V183">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y183">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z183">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="20" r="AA183">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB183">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC183">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD183"/>
+      <c s="19" t="inlineStr" r="AF183">
+        <is>
+          <t xml:space="preserve">2003896622</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG183"/>
+    </row>
+    <row r="184" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A184">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B184">
+        <is>
+          <t xml:space="preserve">14:46:01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C184">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D184">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E184">
+        <v>200717</v>
+      </c>
+      <c s="16" t="inlineStr" r="F184">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H184">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I184">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J184">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K184">
+        <is>
+          <t xml:space="preserve">5012459540</t>
+        </is>
+      </c>
+      <c s="17" r="L184">
+        <v>-300.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M184">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N184">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O184"/>
+      <c s="16" t="str" r="P184"/>
+      <c s="16" t="str" r="Q184"/>
+      <c s="16" t="str" r="R184"/>
+      <c s="16" t="inlineStr" r="S184">
+        <is>
+          <t xml:space="preserve">2632005166</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T184"/>
+      <c s="16" t="inlineStr" r="U184">
+        <is>
+          <t xml:space="preserve">5001560197</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V184">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y184">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z184">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="17" r="AA184">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB184">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC184">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD184"/>
+      <c s="16" t="str" r="AF184"/>
+      <c s="7" t="str" r="AG184"/>
+    </row>
+    <row r="185" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A185">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B185">
+        <is>
+          <t xml:space="preserve">14:46:33</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C185">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D185">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E185">
+        <v>200717</v>
+      </c>
+      <c s="19" t="inlineStr" r="F185">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H185">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I185">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J185">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K185">
+        <is>
+          <t xml:space="preserve">5012459542</t>
+        </is>
+      </c>
+      <c s="20" r="L185">
+        <v>300.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M185">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N185">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O185">
+        <is>
+          <t xml:space="preserve">0072</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P185">
+        <is>
+          <t xml:space="preserve">TRV - Quebra de superfície</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q185"/>
+      <c s="19" t="str" r="R185"/>
+      <c s="19" t="inlineStr" r="S185">
+        <is>
+          <t xml:space="preserve">2632005167</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T185"/>
+      <c s="19" t="inlineStr" r="U185">
+        <is>
+          <t xml:space="preserve">5001560199</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V185">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y185">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z185">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="20" r="AA185">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB185">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC185">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD185"/>
+      <c s="19" t="inlineStr" r="AF185">
+        <is>
+          <t xml:space="preserve">2003896622</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG185"/>
+    </row>
+    <row r="186" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A186">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B186">
+        <is>
+          <t xml:space="preserve">14:47:25</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C186">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D186">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E186">
+        <v>201052</v>
+      </c>
+      <c s="16" t="inlineStr" r="F186">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H186">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I186">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J186">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K186">
+        <is>
+          <t xml:space="preserve">5012459544</t>
+        </is>
+      </c>
+      <c s="17" r="L186">
+        <v>2051.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M186">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N186">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O186"/>
+      <c s="16" t="str" r="P186"/>
+      <c s="16" t="str" r="Q186"/>
+      <c s="16" t="str" r="R186"/>
+      <c s="16" t="inlineStr" r="S186">
+        <is>
+          <t xml:space="preserve">2635002640</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T186"/>
+      <c s="16" t="inlineStr" r="U186">
+        <is>
+          <t xml:space="preserve">5001560221</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V186">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y186">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z186">
+        <is>
+          <t xml:space="preserve">10048030    </t>
+        </is>
+      </c>
+      <c s="17" r="AA186">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB186">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC186">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD186">
+        <is>
+          <t xml:space="preserve">USI</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF186">
+        <is>
+          <t xml:space="preserve">2003976352</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG186"/>
+    </row>
+    <row r="187" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A187">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B187">
+        <is>
+          <t xml:space="preserve">14:54:11</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C187">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D187">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E187">
+        <v>200717</v>
+      </c>
+      <c s="19" t="inlineStr" r="F187">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H187">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I187">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J187">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K187">
+        <is>
+          <t xml:space="preserve">5012459561</t>
+        </is>
+      </c>
+      <c s="20" r="L187">
+        <v>2027.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M187">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N187">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O187"/>
+      <c s="19" t="str" r="P187"/>
+      <c s="19" t="str" r="Q187"/>
+      <c s="19" t="str" r="R187"/>
+      <c s="19" t="inlineStr" r="S187">
+        <is>
+          <t xml:space="preserve">2632005168</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T187"/>
+      <c s="19" t="inlineStr" r="U187">
+        <is>
+          <t xml:space="preserve">5001560258</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V187">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y187">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z187">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="20" r="AA187">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB187">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC187">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD187"/>
+      <c s="19" t="inlineStr" r="AF187">
+        <is>
+          <t xml:space="preserve">2003896622</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG187"/>
+    </row>
+    <row r="188" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A188">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B188">
+        <is>
+          <t xml:space="preserve">14:59:10</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C188">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D188">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E188">
+        <v>200800</v>
+      </c>
+      <c s="16" t="inlineStr" r="F188">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,95mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H188">
+        <is>
+          <t xml:space="preserve">1,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I188">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J188">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K188">
+        <is>
+          <t xml:space="preserve">5012459570</t>
+        </is>
+      </c>
+      <c s="17" r="L188">
+        <v>1075.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M188">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N188">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O188"/>
+      <c s="16" t="str" r="P188"/>
+      <c s="16" t="str" r="Q188"/>
+      <c s="16" t="str" r="R188"/>
+      <c s="16" t="inlineStr" r="S188">
+        <is>
+          <t xml:space="preserve">2636005770</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T188"/>
+      <c s="16" t="inlineStr" r="U188">
+        <is>
+          <t xml:space="preserve">5001560267</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V188">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y188">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z188">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="17" r="AA188">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB188">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC188">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD188">
+        <is>
+          <t xml:space="preserve">SOP</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF188">
+        <is>
+          <t xml:space="preserve">2003663043</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG188"/>
+    </row>
+    <row r="189" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A189">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B189">
+        <is>
+          <t xml:space="preserve">15:04:41</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C189">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D189">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E189">
+        <v>200717</v>
+      </c>
+      <c s="19" t="inlineStr" r="F189">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H189">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I189">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J189">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K189">
+        <is>
+          <t xml:space="preserve">5012459605</t>
+        </is>
+      </c>
+      <c s="20" r="L189">
+        <v>2012.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M189">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N189">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O189"/>
+      <c s="19" t="str" r="P189"/>
+      <c s="19" t="str" r="Q189"/>
+      <c s="19" t="str" r="R189"/>
+      <c s="19" t="inlineStr" r="S189">
+        <is>
+          <t xml:space="preserve">2632005169</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T189"/>
+      <c s="19" t="inlineStr" r="U189">
+        <is>
+          <t xml:space="preserve">5001560316</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V189">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y189">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z189">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="20" r="AA189">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB189">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC189">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD189"/>
+      <c s="19" t="inlineStr" r="AF189">
+        <is>
+          <t xml:space="preserve">2003896622</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG189"/>
+    </row>
+    <row r="190" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A190">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B190">
+        <is>
+          <t xml:space="preserve">15:15:36</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C190">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D190">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E190">
+        <v>200717</v>
+      </c>
+      <c s="16" t="inlineStr" r="F190">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H190">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I190">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J190">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K190">
+        <is>
+          <t xml:space="preserve">5012459651</t>
+        </is>
+      </c>
+      <c s="17" r="L190">
+        <v>2011.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M190">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N190">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O190"/>
+      <c s="16" t="str" r="P190"/>
+      <c s="16" t="str" r="Q190"/>
+      <c s="16" t="str" r="R190"/>
+      <c s="16" t="inlineStr" r="S190">
+        <is>
+          <t xml:space="preserve">2632005170</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T190"/>
+      <c s="16" t="inlineStr" r="U190">
+        <is>
+          <t xml:space="preserve">5001560390</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V190">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y190">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z190">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="17" r="AA190">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB190">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC190">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD190"/>
+      <c s="16" t="inlineStr" r="AF190">
+        <is>
+          <t xml:space="preserve">2003896622</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG190"/>
+    </row>
+    <row r="191" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A191">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B191">
+        <is>
+          <t xml:space="preserve">15:24:16</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C191">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D191">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E191">
+        <v>201052</v>
+      </c>
+      <c s="19" t="inlineStr" r="F191">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H191">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I191">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J191">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K191">
+        <is>
+          <t xml:space="preserve">5012459687</t>
+        </is>
+      </c>
+      <c s="20" r="L191">
+        <v>1191.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M191">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N191">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O191">
+        <is>
+          <t xml:space="preserve">0070</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P191">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q191"/>
+      <c s="19" t="str" r="R191"/>
+      <c s="19" t="inlineStr" r="S191">
+        <is>
+          <t xml:space="preserve">2635002641</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T191"/>
+      <c s="19" t="inlineStr" r="U191">
+        <is>
+          <t xml:space="preserve">5001560419</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V191">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y191">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z191">
+        <is>
+          <t xml:space="preserve">10048030    </t>
+        </is>
+      </c>
+      <c s="20" r="AA191">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB191">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC191">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD191">
+        <is>
+          <t xml:space="preserve">USI</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF191">
+        <is>
+          <t xml:space="preserve">2003976352</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG191"/>
+    </row>
+    <row r="192" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A192">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B192">
+        <is>
+          <t xml:space="preserve">15:40:24</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C192">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D192">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E192">
+        <v>200717</v>
+      </c>
+      <c s="16" t="inlineStr" r="F192">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,95mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H192">
+        <is>
+          <t xml:space="preserve">0,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I192">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J192">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K192">
+        <is>
+          <t xml:space="preserve">5012459729</t>
+        </is>
+      </c>
+      <c s="17" r="L192">
+        <v>907.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M192">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N192">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O192"/>
+      <c s="16" t="str" r="P192"/>
+      <c s="16" t="str" r="Q192"/>
+      <c s="16" t="str" r="R192"/>
+      <c s="16" t="inlineStr" r="S192">
+        <is>
+          <t xml:space="preserve">2632005171</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T192"/>
+      <c s="16" t="inlineStr" r="U192">
+        <is>
+          <t xml:space="preserve">5001560515</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V192">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y192">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z192">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="17" r="AA192">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB192">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC192">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD192"/>
+      <c s="16" t="inlineStr" r="AF192">
+        <is>
+          <t xml:space="preserve">2003896622</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG192"/>
+    </row>
+    <row r="193" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A193">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B193">
+        <is>
+          <t xml:space="preserve">15:46:46</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C193">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D193">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E193">
+        <v>200800</v>
+      </c>
+      <c s="19" t="inlineStr" r="F193">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,95mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H193">
+        <is>
+          <t xml:space="preserve">1,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I193">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J193">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K193">
+        <is>
+          <t xml:space="preserve">5012459742</t>
+        </is>
+      </c>
+      <c s="20" r="L193">
+        <v>716.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M193">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N193">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O193"/>
+      <c s="19" t="str" r="P193"/>
+      <c s="19" t="str" r="Q193"/>
+      <c s="19" t="str" r="R193"/>
+      <c s="19" t="inlineStr" r="S193">
+        <is>
+          <t xml:space="preserve">2636005771</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T193"/>
+      <c s="19" t="inlineStr" r="U193">
+        <is>
+          <t xml:space="preserve">5001560529</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V193">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y193">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z193">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" r="AA193">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB193">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC193">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD193">
+        <is>
+          <t xml:space="preserve">SOP</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF193">
+        <is>
+          <t xml:space="preserve">2003663043</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG193"/>
+    </row>
+    <row r="194" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A194">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B194">
+        <is>
+          <t xml:space="preserve">16:04:25</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C194">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D194">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E194">
+        <v>201052</v>
+      </c>
+      <c s="16" t="inlineStr" r="F194">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H194">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I194">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J194">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K194">
+        <is>
+          <t xml:space="preserve">5012459786</t>
+        </is>
+      </c>
+      <c s="17" r="L194">
+        <v>2046.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M194">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N194">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O194"/>
+      <c s="16" t="str" r="P194"/>
+      <c s="16" t="str" r="Q194"/>
+      <c s="16" t="str" r="R194"/>
+      <c s="16" t="inlineStr" r="S194">
+        <is>
+          <t xml:space="preserve">2635002642</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T194"/>
+      <c s="16" t="inlineStr" r="U194">
+        <is>
+          <t xml:space="preserve">5001560619</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V194">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y194">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z194">
+        <is>
+          <t xml:space="preserve">10048030    </t>
+        </is>
+      </c>
+      <c s="17" r="AA194">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB194">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC194">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD194">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF194">
+        <is>
+          <t xml:space="preserve">2003979964</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG194"/>
+    </row>
+    <row r="195" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A195">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B195">
+        <is>
+          <t xml:space="preserve">16:05:27</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C195">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D195">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E195">
+        <v>201052</v>
+      </c>
+      <c s="19" t="inlineStr" r="F195">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H195">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I195">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J195">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K195">
+        <is>
+          <t xml:space="preserve">5012459789</t>
+        </is>
+      </c>
+      <c s="20" r="L195">
+        <v>2061.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M195">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N195">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O195"/>
+      <c s="19" t="str" r="P195"/>
+      <c s="19" t="str" r="Q195"/>
+      <c s="19" t="str" r="R195"/>
+      <c s="19" t="inlineStr" r="S195">
+        <is>
+          <t xml:space="preserve">2635002643</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T195"/>
+      <c s="19" t="inlineStr" r="U195">
+        <is>
+          <t xml:space="preserve">5001560652</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V195">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y195">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z195">
+        <is>
+          <t xml:space="preserve">10048030    </t>
+        </is>
+      </c>
+      <c s="20" r="AA195">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB195">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC195">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD195">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF195">
+        <is>
+          <t xml:space="preserve">2003979964</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG195"/>
+    </row>
+    <row r="196" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A196">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B196">
+        <is>
+          <t xml:space="preserve">16:20:48</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C196">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D196">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E196">
+        <v>201052</v>
+      </c>
+      <c s="16" t="inlineStr" r="F196">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H196">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I196">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J196">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K196">
+        <is>
+          <t xml:space="preserve">5012459822</t>
+        </is>
+      </c>
+      <c s="17" r="L196">
+        <v>2045.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M196">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N196">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O196"/>
+      <c s="16" t="str" r="P196"/>
+      <c s="16" t="str" r="Q196"/>
+      <c s="16" t="str" r="R196"/>
+      <c s="16" t="inlineStr" r="S196">
+        <is>
+          <t xml:space="preserve">2635002644</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T196"/>
+      <c s="16" t="inlineStr" r="U196">
+        <is>
+          <t xml:space="preserve">5001560715</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V196">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y196">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z196">
+        <is>
+          <t xml:space="preserve">10048030    </t>
+        </is>
+      </c>
+      <c s="17" r="AA196">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB196">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC196">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD196">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF196">
+        <is>
+          <t xml:space="preserve">2003979964</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG196"/>
+    </row>
+    <row r="197" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A197">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B197">
+        <is>
+          <t xml:space="preserve">16:26:44</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C197">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D197">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E197">
+        <v>200800</v>
+      </c>
+      <c s="19" t="inlineStr" r="F197">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,95mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H197">
+        <is>
+          <t xml:space="preserve">1,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I197">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J197">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K197">
+        <is>
+          <t xml:space="preserve">5012459862</t>
+        </is>
+      </c>
+      <c s="20" r="L197">
+        <v>1110.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M197">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N197">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O197"/>
+      <c s="19" t="str" r="P197"/>
+      <c s="19" t="str" r="Q197"/>
+      <c s="19" t="str" r="R197"/>
+      <c s="19" t="inlineStr" r="S197">
+        <is>
+          <t xml:space="preserve">2636005772</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T197"/>
+      <c s="19" t="inlineStr" r="U197">
+        <is>
+          <t xml:space="preserve">5001560738</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V197">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y197">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z197">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" r="AA197">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB197">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC197">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD197">
+        <is>
+          <t xml:space="preserve">SOP</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF197">
+        <is>
+          <t xml:space="preserve">2003663043</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG197"/>
+    </row>
+    <row r="198" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A198">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B198">
+        <is>
+          <t xml:space="preserve">16:37:35</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C198">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D198">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E198">
+        <v>200800</v>
+      </c>
+      <c s="16" t="inlineStr" r="F198">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,95mm GA 6000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H198">
+        <is>
+          <t xml:space="preserve">1,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I198">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J198">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K198">
+        <is>
+          <t xml:space="preserve">5012459885</t>
+        </is>
+      </c>
+      <c s="17" r="L198">
+        <v>1107.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M198">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N198">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O198"/>
+      <c s="16" t="str" r="P198"/>
+      <c s="16" t="str" r="Q198"/>
+      <c s="16" t="str" r="R198"/>
+      <c s="16" t="inlineStr" r="S198">
+        <is>
+          <t xml:space="preserve">2636005773</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T198"/>
+      <c s="16" t="inlineStr" r="U198">
+        <is>
+          <t xml:space="preserve">5001560822</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V198">
+        <is>
+          <t xml:space="preserve">20131309</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y198">
+        <is>
+          <t xml:space="preserve">BRASIL FERRO E ACO LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z198">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="17" r="AA198">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB198">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC198">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD198">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF198">
+        <is>
+          <t xml:space="preserve">2003936258</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG198"/>
+    </row>
+    <row r="199" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A199">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B199">
+        <is>
+          <t xml:space="preserve">16:39:44</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C199">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D199">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E199">
+        <v>201052</v>
+      </c>
+      <c s="19" t="inlineStr" r="F199">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H199">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I199">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J199">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K199">
+        <is>
+          <t xml:space="preserve">5012459891</t>
+        </is>
+      </c>
+      <c s="20" r="L199">
+        <v>2685.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M199">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N199">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O199"/>
+      <c s="19" t="str" r="P199"/>
+      <c s="19" t="str" r="Q199"/>
+      <c s="19" t="str" r="R199"/>
+      <c s="19" t="inlineStr" r="S199">
+        <is>
+          <t xml:space="preserve">2635002645</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T199"/>
+      <c s="19" t="inlineStr" r="U199">
+        <is>
+          <t xml:space="preserve">5001560829</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V199">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y199">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z199">
+        <is>
+          <t xml:space="preserve">10048030    </t>
+        </is>
+      </c>
+      <c s="20" r="AA199">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB199">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC199">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD199">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF199">
+        <is>
+          <t xml:space="preserve">2003979964</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG199"/>
+    </row>
+    <row r="200" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A200">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B200">
+        <is>
+          <t xml:space="preserve">16:41:30</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C200">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D200">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E200">
+        <v>200781</v>
+      </c>
+      <c s="16" t="inlineStr" r="F200">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,95mm GA 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H200">
+        <is>
+          <t xml:space="preserve">1,95mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I200">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J200">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K200">
+        <is>
+          <t xml:space="preserve">5012459893</t>
+        </is>
+      </c>
+      <c s="17" r="L200">
+        <v>600.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M200">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N200">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O200">
+        <is>
+          <t xml:space="preserve">0071</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P200">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação galvânica</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q200"/>
+      <c s="16" t="str" r="R200"/>
+      <c s="16" t="inlineStr" r="S200">
+        <is>
+          <t xml:space="preserve">2636005774</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T200"/>
+      <c s="16" t="inlineStr" r="U200">
+        <is>
+          <t xml:space="preserve">5001560831</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V200">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y200">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z200">
+        <is>
+          <t xml:space="preserve">10046766    </t>
+        </is>
+      </c>
+      <c s="17" r="AA200">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB200">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC200">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD200">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF200">
+        <is>
+          <t xml:space="preserve">2003936258</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG200"/>
+    </row>
+    <row r="201" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A201">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B201">
+        <is>
+          <t xml:space="preserve">16:41:53</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C201">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D201">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E201">
+        <v>200781</v>
+      </c>
+      <c s="19" t="inlineStr" r="F201">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,95mm GA 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H201">
+        <is>
+          <t xml:space="preserve">1,95mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I201">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J201">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K201">
+        <is>
+          <t xml:space="preserve">5012459894</t>
+        </is>
+      </c>
+      <c s="20" r="L201">
+        <v>564.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M201">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N201">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O201">
+        <is>
+          <t xml:space="preserve">0071</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P201">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação galvânica</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q201"/>
+      <c s="19" t="str" r="R201"/>
+      <c s="19" t="inlineStr" r="S201">
+        <is>
+          <t xml:space="preserve">2636005775</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T201"/>
+      <c s="19" t="inlineStr" r="U201">
+        <is>
+          <t xml:space="preserve">5001560832</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V201">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y201">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z201">
+        <is>
+          <t xml:space="preserve">10046766    </t>
+        </is>
+      </c>
+      <c s="20" r="AA201">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB201">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC201">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD201">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF201">
+        <is>
+          <t xml:space="preserve">2003936258</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG201"/>
+    </row>
+    <row r="202" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A202">
+        <is>
+          <t xml:space="preserve">05/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B202">
+        <is>
+          <t xml:space="preserve">16:44:44</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C202">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D202">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E202">
+        <v>201052</v>
+      </c>
+      <c s="16" t="inlineStr" r="F202">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H202">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I202">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J202">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K202">
+        <is>
+          <t xml:space="preserve">5012459909</t>
+        </is>
+      </c>
+      <c s="17" r="L202">
+        <v>60.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M202">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N202">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O202">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P202">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q202"/>
+      <c s="16" t="str" r="R202"/>
+      <c s="16" t="inlineStr" r="S202">
+        <is>
+          <t xml:space="preserve">2635002646</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T202"/>
+      <c s="16" t="inlineStr" r="U202">
+        <is>
+          <t xml:space="preserve">5001560835</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V202">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y202">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z202">
+        <is>
+          <t xml:space="preserve">10048030    </t>
+        </is>
+      </c>
+      <c s="17" r="AA202">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB202">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC202">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD202">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF202">
+        <is>
+          <t xml:space="preserve">2003979964</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG202"/>
+    </row>
+    <row r="203" ht="14.7" customHeight="1">
+      <c s="21" t="inlineStr" r="A203">
+        <is>
+          <t xml:space="preserve">Peso Total: 268017,000</t>
+        </is>
+      </c>
+      <c s="13" t="str" r="B203"/>
+      <c s="13" t="str" r="C203"/>
+      <c s="13" t="str" r="D203"/>
+      <c s="13" t="str" r="E203"/>
+      <c s="13" t="str" r="F203"/>
+      <c s="13" t="str" r="G203"/>
+      <c s="13" t="str" r="H203"/>
+      <c s="13" t="str" r="I203"/>
+      <c s="13" t="str" r="J203"/>
+      <c s="13" t="str" r="K203"/>
+      <c s="13" t="str" r="L203"/>
+      <c s="13" t="str" r="M203"/>
+      <c s="13" t="str" r="N203"/>
+      <c s="13" t="str" r="O203"/>
+      <c s="13" t="str" r="P203"/>
+      <c s="13" t="str" r="Q203"/>
+      <c s="13" t="str" r="R203"/>
+      <c s="13" t="str" r="S203"/>
+      <c s="13" t="str" r="T203"/>
+      <c s="13" t="str" r="U203"/>
+      <c s="13" t="str" r="V203"/>
+      <c s="13" t="str" r="W203"/>
+      <c s="13" t="str" r="X203"/>
+      <c s="13" t="str" r="Y203"/>
+      <c s="13" t="str" r="Z203"/>
+      <c s="13" t="str" r="AA203"/>
+      <c s="13" t="str" r="AB203"/>
+      <c s="13" t="str" r="AC203"/>
+      <c s="13" t="str" r="AD203"/>
+      <c s="13" t="str" r="AE203"/>
+      <c s="13" t="str" r="AF203"/>
+      <c s="14" t="str" r="AG203"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -14771,7 +22964,291 @@
     <mergeCell ref="V131:X131"/>
     <mergeCell ref="AD131:AE131"/>
     <mergeCell ref="AF131:AG131"/>
-    <mergeCell ref="A132:AG132"/>
+    <mergeCell ref="F132:G132"/>
+    <mergeCell ref="V132:X132"/>
+    <mergeCell ref="AD132:AE132"/>
+    <mergeCell ref="AF132:AG132"/>
+    <mergeCell ref="F133:G133"/>
+    <mergeCell ref="V133:X133"/>
+    <mergeCell ref="AD133:AE133"/>
+    <mergeCell ref="AF133:AG133"/>
+    <mergeCell ref="F134:G134"/>
+    <mergeCell ref="V134:X134"/>
+    <mergeCell ref="AD134:AE134"/>
+    <mergeCell ref="AF134:AG134"/>
+    <mergeCell ref="F135:G135"/>
+    <mergeCell ref="V135:X135"/>
+    <mergeCell ref="AD135:AE135"/>
+    <mergeCell ref="AF135:AG135"/>
+    <mergeCell ref="F136:G136"/>
+    <mergeCell ref="V136:X136"/>
+    <mergeCell ref="AD136:AE136"/>
+    <mergeCell ref="AF136:AG136"/>
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="V137:X137"/>
+    <mergeCell ref="AD137:AE137"/>
+    <mergeCell ref="AF137:AG137"/>
+    <mergeCell ref="F138:G138"/>
+    <mergeCell ref="V138:X138"/>
+    <mergeCell ref="AD138:AE138"/>
+    <mergeCell ref="AF138:AG138"/>
+    <mergeCell ref="F139:G139"/>
+    <mergeCell ref="V139:X139"/>
+    <mergeCell ref="AD139:AE139"/>
+    <mergeCell ref="AF139:AG139"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="V140:X140"/>
+    <mergeCell ref="AD140:AE140"/>
+    <mergeCell ref="AF140:AG140"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="V141:X141"/>
+    <mergeCell ref="AD141:AE141"/>
+    <mergeCell ref="AF141:AG141"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="V142:X142"/>
+    <mergeCell ref="AD142:AE142"/>
+    <mergeCell ref="AF142:AG142"/>
+    <mergeCell ref="F143:G143"/>
+    <mergeCell ref="V143:X143"/>
+    <mergeCell ref="AD143:AE143"/>
+    <mergeCell ref="AF143:AG143"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="V144:X144"/>
+    <mergeCell ref="AD144:AE144"/>
+    <mergeCell ref="AF144:AG144"/>
+    <mergeCell ref="F145:G145"/>
+    <mergeCell ref="V145:X145"/>
+    <mergeCell ref="AD145:AE145"/>
+    <mergeCell ref="AF145:AG145"/>
+    <mergeCell ref="F146:G146"/>
+    <mergeCell ref="V146:X146"/>
+    <mergeCell ref="AD146:AE146"/>
+    <mergeCell ref="AF146:AG146"/>
+    <mergeCell ref="F147:G147"/>
+    <mergeCell ref="V147:X147"/>
+    <mergeCell ref="AD147:AE147"/>
+    <mergeCell ref="AF147:AG147"/>
+    <mergeCell ref="F148:G148"/>
+    <mergeCell ref="V148:X148"/>
+    <mergeCell ref="AD148:AE148"/>
+    <mergeCell ref="AF148:AG148"/>
+    <mergeCell ref="F149:G149"/>
+    <mergeCell ref="V149:X149"/>
+    <mergeCell ref="AD149:AE149"/>
+    <mergeCell ref="AF149:AG149"/>
+    <mergeCell ref="F150:G150"/>
+    <mergeCell ref="V150:X150"/>
+    <mergeCell ref="AD150:AE150"/>
+    <mergeCell ref="AF150:AG150"/>
+    <mergeCell ref="F151:G151"/>
+    <mergeCell ref="V151:X151"/>
+    <mergeCell ref="AD151:AE151"/>
+    <mergeCell ref="AF151:AG151"/>
+    <mergeCell ref="F152:G152"/>
+    <mergeCell ref="V152:X152"/>
+    <mergeCell ref="AD152:AE152"/>
+    <mergeCell ref="AF152:AG152"/>
+    <mergeCell ref="F153:G153"/>
+    <mergeCell ref="V153:X153"/>
+    <mergeCell ref="AD153:AE153"/>
+    <mergeCell ref="AF153:AG153"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="V154:X154"/>
+    <mergeCell ref="AD154:AE154"/>
+    <mergeCell ref="AF154:AG154"/>
+    <mergeCell ref="F155:G155"/>
+    <mergeCell ref="V155:X155"/>
+    <mergeCell ref="AD155:AE155"/>
+    <mergeCell ref="AF155:AG155"/>
+    <mergeCell ref="F156:G156"/>
+    <mergeCell ref="V156:X156"/>
+    <mergeCell ref="AD156:AE156"/>
+    <mergeCell ref="AF156:AG156"/>
+    <mergeCell ref="F157:G157"/>
+    <mergeCell ref="V157:X157"/>
+    <mergeCell ref="AD157:AE157"/>
+    <mergeCell ref="AF157:AG157"/>
+    <mergeCell ref="F158:G158"/>
+    <mergeCell ref="V158:X158"/>
+    <mergeCell ref="AD158:AE158"/>
+    <mergeCell ref="AF158:AG158"/>
+    <mergeCell ref="F159:G159"/>
+    <mergeCell ref="V159:X159"/>
+    <mergeCell ref="AD159:AE159"/>
+    <mergeCell ref="AF159:AG159"/>
+    <mergeCell ref="F160:G160"/>
+    <mergeCell ref="V160:X160"/>
+    <mergeCell ref="AD160:AE160"/>
+    <mergeCell ref="AF160:AG160"/>
+    <mergeCell ref="F161:G161"/>
+    <mergeCell ref="V161:X161"/>
+    <mergeCell ref="AD161:AE161"/>
+    <mergeCell ref="AF161:AG161"/>
+    <mergeCell ref="F162:G162"/>
+    <mergeCell ref="V162:X162"/>
+    <mergeCell ref="AD162:AE162"/>
+    <mergeCell ref="AF162:AG162"/>
+    <mergeCell ref="F163:G163"/>
+    <mergeCell ref="V163:X163"/>
+    <mergeCell ref="AD163:AE163"/>
+    <mergeCell ref="AF163:AG163"/>
+    <mergeCell ref="F164:G164"/>
+    <mergeCell ref="V164:X164"/>
+    <mergeCell ref="AD164:AE164"/>
+    <mergeCell ref="AF164:AG164"/>
+    <mergeCell ref="F165:G165"/>
+    <mergeCell ref="V165:X165"/>
+    <mergeCell ref="AD165:AE165"/>
+    <mergeCell ref="AF165:AG165"/>
+    <mergeCell ref="F166:G166"/>
+    <mergeCell ref="V166:X166"/>
+    <mergeCell ref="AD166:AE166"/>
+    <mergeCell ref="AF166:AG166"/>
+    <mergeCell ref="F167:G167"/>
+    <mergeCell ref="V167:X167"/>
+    <mergeCell ref="AD167:AE167"/>
+    <mergeCell ref="AF167:AG167"/>
+    <mergeCell ref="F168:G168"/>
+    <mergeCell ref="V168:X168"/>
+    <mergeCell ref="AD168:AE168"/>
+    <mergeCell ref="AF168:AG168"/>
+    <mergeCell ref="F169:G169"/>
+    <mergeCell ref="V169:X169"/>
+    <mergeCell ref="AD169:AE169"/>
+    <mergeCell ref="AF169:AG169"/>
+    <mergeCell ref="F170:G170"/>
+    <mergeCell ref="V170:X170"/>
+    <mergeCell ref="AD170:AE170"/>
+    <mergeCell ref="AF170:AG170"/>
+    <mergeCell ref="F171:G171"/>
+    <mergeCell ref="V171:X171"/>
+    <mergeCell ref="AD171:AE171"/>
+    <mergeCell ref="AF171:AG171"/>
+    <mergeCell ref="F172:G172"/>
+    <mergeCell ref="V172:X172"/>
+    <mergeCell ref="AD172:AE172"/>
+    <mergeCell ref="AF172:AG172"/>
+    <mergeCell ref="F173:G173"/>
+    <mergeCell ref="V173:X173"/>
+    <mergeCell ref="AD173:AE173"/>
+    <mergeCell ref="AF173:AG173"/>
+    <mergeCell ref="F174:G174"/>
+    <mergeCell ref="V174:X174"/>
+    <mergeCell ref="AD174:AE174"/>
+    <mergeCell ref="AF174:AG174"/>
+    <mergeCell ref="F175:G175"/>
+    <mergeCell ref="V175:X175"/>
+    <mergeCell ref="AD175:AE175"/>
+    <mergeCell ref="AF175:AG175"/>
+    <mergeCell ref="F176:G176"/>
+    <mergeCell ref="V176:X176"/>
+    <mergeCell ref="AD176:AE176"/>
+    <mergeCell ref="AF176:AG176"/>
+    <mergeCell ref="F177:G177"/>
+    <mergeCell ref="V177:X177"/>
+    <mergeCell ref="AD177:AE177"/>
+    <mergeCell ref="AF177:AG177"/>
+    <mergeCell ref="F178:G178"/>
+    <mergeCell ref="V178:X178"/>
+    <mergeCell ref="AD178:AE178"/>
+    <mergeCell ref="AF178:AG178"/>
+    <mergeCell ref="F179:G179"/>
+    <mergeCell ref="V179:X179"/>
+    <mergeCell ref="AD179:AE179"/>
+    <mergeCell ref="AF179:AG179"/>
+    <mergeCell ref="F180:G180"/>
+    <mergeCell ref="V180:X180"/>
+    <mergeCell ref="AD180:AE180"/>
+    <mergeCell ref="AF180:AG180"/>
+    <mergeCell ref="F181:G181"/>
+    <mergeCell ref="V181:X181"/>
+    <mergeCell ref="AD181:AE181"/>
+    <mergeCell ref="AF181:AG181"/>
+    <mergeCell ref="F182:G182"/>
+    <mergeCell ref="V182:X182"/>
+    <mergeCell ref="AD182:AE182"/>
+    <mergeCell ref="AF182:AG182"/>
+    <mergeCell ref="F183:G183"/>
+    <mergeCell ref="V183:X183"/>
+    <mergeCell ref="AD183:AE183"/>
+    <mergeCell ref="AF183:AG183"/>
+    <mergeCell ref="F184:G184"/>
+    <mergeCell ref="V184:X184"/>
+    <mergeCell ref="AD184:AE184"/>
+    <mergeCell ref="AF184:AG184"/>
+    <mergeCell ref="F185:G185"/>
+    <mergeCell ref="V185:X185"/>
+    <mergeCell ref="AD185:AE185"/>
+    <mergeCell ref="AF185:AG185"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="V186:X186"/>
+    <mergeCell ref="AD186:AE186"/>
+    <mergeCell ref="AF186:AG186"/>
+    <mergeCell ref="F187:G187"/>
+    <mergeCell ref="V187:X187"/>
+    <mergeCell ref="AD187:AE187"/>
+    <mergeCell ref="AF187:AG187"/>
+    <mergeCell ref="F188:G188"/>
+    <mergeCell ref="V188:X188"/>
+    <mergeCell ref="AD188:AE188"/>
+    <mergeCell ref="AF188:AG188"/>
+    <mergeCell ref="F189:G189"/>
+    <mergeCell ref="V189:X189"/>
+    <mergeCell ref="AD189:AE189"/>
+    <mergeCell ref="AF189:AG189"/>
+    <mergeCell ref="F190:G190"/>
+    <mergeCell ref="V190:X190"/>
+    <mergeCell ref="AD190:AE190"/>
+    <mergeCell ref="AF190:AG190"/>
+    <mergeCell ref="F191:G191"/>
+    <mergeCell ref="V191:X191"/>
+    <mergeCell ref="AD191:AE191"/>
+    <mergeCell ref="AF191:AG191"/>
+    <mergeCell ref="F192:G192"/>
+    <mergeCell ref="V192:X192"/>
+    <mergeCell ref="AD192:AE192"/>
+    <mergeCell ref="AF192:AG192"/>
+    <mergeCell ref="F193:G193"/>
+    <mergeCell ref="V193:X193"/>
+    <mergeCell ref="AD193:AE193"/>
+    <mergeCell ref="AF193:AG193"/>
+    <mergeCell ref="F194:G194"/>
+    <mergeCell ref="V194:X194"/>
+    <mergeCell ref="AD194:AE194"/>
+    <mergeCell ref="AF194:AG194"/>
+    <mergeCell ref="F195:G195"/>
+    <mergeCell ref="V195:X195"/>
+    <mergeCell ref="AD195:AE195"/>
+    <mergeCell ref="AF195:AG195"/>
+    <mergeCell ref="F196:G196"/>
+    <mergeCell ref="V196:X196"/>
+    <mergeCell ref="AD196:AE196"/>
+    <mergeCell ref="AF196:AG196"/>
+    <mergeCell ref="F197:G197"/>
+    <mergeCell ref="V197:X197"/>
+    <mergeCell ref="AD197:AE197"/>
+    <mergeCell ref="AF197:AG197"/>
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="V198:X198"/>
+    <mergeCell ref="AD198:AE198"/>
+    <mergeCell ref="AF198:AG198"/>
+    <mergeCell ref="F199:G199"/>
+    <mergeCell ref="V199:X199"/>
+    <mergeCell ref="AD199:AE199"/>
+    <mergeCell ref="AF199:AG199"/>
+    <mergeCell ref="F200:G200"/>
+    <mergeCell ref="V200:X200"/>
+    <mergeCell ref="AD200:AE200"/>
+    <mergeCell ref="AF200:AG200"/>
+    <mergeCell ref="F201:G201"/>
+    <mergeCell ref="V201:X201"/>
+    <mergeCell ref="AD201:AE201"/>
+    <mergeCell ref="AF201:AG201"/>
+    <mergeCell ref="F202:G202"/>
+    <mergeCell ref="V202:X202"/>
+    <mergeCell ref="AD202:AE202"/>
+    <mergeCell ref="AF202:AG202"/>
+    <mergeCell ref="A203:AG203"/>
   </mergeCells>
   <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="0.393700787401575" header="0.393700787401575" footer="0.393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/Base_Producao.xlsx
+++ b/Base_Producao.xlsx
@@ -503,7 +503,7 @@
       <c s="4" t="str" r="A5"/>
       <c s="6" t="inlineStr" r="AE5">
         <is>
-          <t xml:space="preserve">Emissão: 08/10/2026</t>
+          <t xml:space="preserve">Emissão: 09/10/2026</t>
         </is>
       </c>
       <c s="7" t="str" r="AG5"/>
@@ -512,7 +512,7 @@
       <c s="4" t="str" r="A6"/>
       <c s="8" t="inlineStr" r="G6">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 07/10/2026</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 08/10/2026</t>
         </is>
       </c>
       <c s="7" t="str" r="AG6"/>
@@ -48187,44 +48187,8134 @@
       </c>
       <c s="7" t="str" r="AG427"/>
     </row>
-    <row r="428" ht="14.7" customHeight="1">
-      <c s="21" t="inlineStr" r="A428">
-        <is>
-          <t xml:space="preserve">Peso Total: 631055,000</t>
-        </is>
-      </c>
-      <c s="13" t="str" r="B428"/>
-      <c s="13" t="str" r="C428"/>
-      <c s="13" t="str" r="D428"/>
-      <c s="13" t="str" r="E428"/>
-      <c s="13" t="str" r="F428"/>
-      <c s="13" t="str" r="G428"/>
-      <c s="13" t="str" r="H428"/>
-      <c s="13" t="str" r="I428"/>
-      <c s="13" t="str" r="J428"/>
-      <c s="13" t="str" r="K428"/>
-      <c s="13" t="str" r="L428"/>
-      <c s="13" t="str" r="M428"/>
-      <c s="13" t="str" r="N428"/>
-      <c s="13" t="str" r="O428"/>
-      <c s="13" t="str" r="P428"/>
-      <c s="13" t="str" r="Q428"/>
-      <c s="13" t="str" r="R428"/>
-      <c s="13" t="str" r="S428"/>
-      <c s="13" t="str" r="T428"/>
-      <c s="13" t="str" r="U428"/>
-      <c s="13" t="str" r="V428"/>
-      <c s="13" t="str" r="W428"/>
-      <c s="13" t="str" r="X428"/>
-      <c s="13" t="str" r="Y428"/>
-      <c s="13" t="str" r="Z428"/>
-      <c s="13" t="str" r="AA428"/>
-      <c s="13" t="str" r="AB428"/>
-      <c s="13" t="str" r="AC428"/>
-      <c s="13" t="str" r="AD428"/>
-      <c s="13" t="str" r="AE428"/>
-      <c s="13" t="str" r="AF428"/>
-      <c s="14" t="str" r="AG428"/>
+    <row r="428" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A428">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B428">
+        <is>
+          <t xml:space="preserve">07:20:40</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C428">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D428">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E428">
+        <v>201052</v>
+      </c>
+      <c s="16" t="inlineStr" r="F428">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H428">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I428">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J428">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K428">
+        <is>
+          <t xml:space="preserve">5012468184</t>
+        </is>
+      </c>
+      <c s="17" r="L428">
+        <v>2089.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M428">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N428">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O428"/>
+      <c s="16" t="str" r="P428"/>
+      <c s="16" t="str" r="Q428"/>
+      <c s="16" t="str" r="R428"/>
+      <c s="16" t="inlineStr" r="S428">
+        <is>
+          <t xml:space="preserve">2636005842</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T428"/>
+      <c s="16" t="inlineStr" r="U428">
+        <is>
+          <t xml:space="preserve">5001576704</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V428">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y428">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z428">
+        <is>
+          <t xml:space="preserve">10047305    </t>
+        </is>
+      </c>
+      <c s="17" r="AA428">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB428">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC428">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD428">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF428">
+        <is>
+          <t xml:space="preserve">2003921183</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG428"/>
+    </row>
+    <row r="429" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A429">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B429">
+        <is>
+          <t xml:space="preserve">07:25:48</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C429">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D429">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E429">
+        <v>200906</v>
+      </c>
+      <c s="19" t="inlineStr" r="F429">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H429">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I429">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J429">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K429">
+        <is>
+          <t xml:space="preserve">5012468191</t>
+        </is>
+      </c>
+      <c s="20" r="L429">
+        <v>2026.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M429">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N429">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O429"/>
+      <c s="19" t="str" r="P429"/>
+      <c s="19" t="str" r="Q429"/>
+      <c s="19" t="str" r="R429"/>
+      <c s="19" t="inlineStr" r="S429">
+        <is>
+          <t xml:space="preserve">2632005246</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T429"/>
+      <c s="19" t="inlineStr" r="U429">
+        <is>
+          <t xml:space="preserve">5001576721</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V429">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y429">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z429">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" r="AA429">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB429">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC429">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD429">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF429">
+        <is>
+          <t xml:space="preserve">2003984078</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG429"/>
+    </row>
+    <row r="430" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A430">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B430">
+        <is>
+          <t xml:space="preserve">07:39:34</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C430">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D430">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E430">
+        <v>222348</v>
+      </c>
+      <c s="16" t="inlineStr" r="F430">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H430">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I430">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J430">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K430">
+        <is>
+          <t xml:space="preserve">5012468230</t>
+        </is>
+      </c>
+      <c s="17" r="L430">
+        <v>2028.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M430">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N430">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O430"/>
+      <c s="16" t="str" r="P430"/>
+      <c s="16" t="str" r="Q430"/>
+      <c s="16" t="str" r="R430"/>
+      <c s="16" t="inlineStr" r="S430">
+        <is>
+          <t xml:space="preserve">2633006580</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T430"/>
+      <c s="16" t="inlineStr" r="U430">
+        <is>
+          <t xml:space="preserve">5001576821</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V430">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y430">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z430">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="17" r="AA430">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB430">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC430">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD430">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF430">
+        <is>
+          <t xml:space="preserve">2002644783</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG430"/>
+    </row>
+    <row r="431" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A431">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B431">
+        <is>
+          <t xml:space="preserve">07:47:31</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C431">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D431">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E431">
+        <v>200906</v>
+      </c>
+      <c s="19" t="inlineStr" r="F431">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H431">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I431">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J431">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K431">
+        <is>
+          <t xml:space="preserve">5012468250</t>
+        </is>
+      </c>
+      <c s="20" r="L431">
+        <v>2020.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M431">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N431">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O431"/>
+      <c s="19" t="str" r="P431"/>
+      <c s="19" t="str" r="Q431"/>
+      <c s="19" t="str" r="R431"/>
+      <c s="19" t="inlineStr" r="S431">
+        <is>
+          <t xml:space="preserve">2632005247</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T431"/>
+      <c s="19" t="inlineStr" r="U431">
+        <is>
+          <t xml:space="preserve">5001576858</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V431">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y431">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z431">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" r="AA431">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB431">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC431">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD431">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF431">
+        <is>
+          <t xml:space="preserve">2003984078</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG431"/>
+    </row>
+    <row r="432" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A432">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B432">
+        <is>
+          <t xml:space="preserve">07:52:14</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C432">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D432">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E432">
+        <v>222348</v>
+      </c>
+      <c s="16" t="inlineStr" r="F432">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H432">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I432">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J432">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K432">
+        <is>
+          <t xml:space="preserve">5012468256</t>
+        </is>
+      </c>
+      <c s="17" r="L432">
+        <v>2026.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M432">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N432">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O432"/>
+      <c s="16" t="str" r="P432"/>
+      <c s="16" t="str" r="Q432"/>
+      <c s="16" t="str" r="R432"/>
+      <c s="16" t="inlineStr" r="S432">
+        <is>
+          <t xml:space="preserve">2633006581</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T432"/>
+      <c s="16" t="inlineStr" r="U432">
+        <is>
+          <t xml:space="preserve">5001576875</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V432">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y432">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z432">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="17" r="AA432">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB432">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC432">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD432">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF432">
+        <is>
+          <t xml:space="preserve">2002644783</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG432"/>
+    </row>
+    <row r="433" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A433">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B433">
+        <is>
+          <t xml:space="preserve">08:00:17</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C433">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D433">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E433">
+        <v>222348</v>
+      </c>
+      <c s="19" t="inlineStr" r="F433">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H433">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I433">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J433">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K433">
+        <is>
+          <t xml:space="preserve">5012468280</t>
+        </is>
+      </c>
+      <c s="20" r="L433">
+        <v>2024.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M433">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N433">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O433"/>
+      <c s="19" t="str" r="P433"/>
+      <c s="19" t="str" r="Q433"/>
+      <c s="19" t="str" r="R433"/>
+      <c s="19" t="inlineStr" r="S433">
+        <is>
+          <t xml:space="preserve">2633006582</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T433"/>
+      <c s="19" t="inlineStr" r="U433">
+        <is>
+          <t xml:space="preserve">5001576910</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V433">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y433">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z433">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="20" r="AA433">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB433">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC433">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD433">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF433">
+        <is>
+          <t xml:space="preserve">2002644783</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG433"/>
+    </row>
+    <row r="434" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A434">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B434">
+        <is>
+          <t xml:space="preserve">08:05:54</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C434">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D434">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E434">
+        <v>201052</v>
+      </c>
+      <c s="16" t="inlineStr" r="F434">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H434">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I434">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J434">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K434">
+        <is>
+          <t xml:space="preserve">5012468299</t>
+        </is>
+      </c>
+      <c s="17" r="L434">
+        <v>1144.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M434">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N434">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O434"/>
+      <c s="16" t="str" r="P434"/>
+      <c s="16" t="str" r="Q434"/>
+      <c s="16" t="str" r="R434"/>
+      <c s="16" t="inlineStr" r="S434">
+        <is>
+          <t xml:space="preserve">2636005843</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T434"/>
+      <c s="16" t="inlineStr" r="U434">
+        <is>
+          <t xml:space="preserve">5001576939</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V434">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y434">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z434">
+        <is>
+          <t xml:space="preserve">10047305    </t>
+        </is>
+      </c>
+      <c s="17" r="AA434">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB434">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC434">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD434">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF434">
+        <is>
+          <t xml:space="preserve">2003921183</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG434"/>
+    </row>
+    <row r="435" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A435">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B435">
+        <is>
+          <t xml:space="preserve">08:06:20</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C435">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D435">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E435">
+        <v>201052</v>
+      </c>
+      <c s="19" t="inlineStr" r="F435">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H435">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I435">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J435">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K435">
+        <is>
+          <t xml:space="preserve">5012468303</t>
+        </is>
+      </c>
+      <c s="20" r="L435">
+        <v>102.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M435">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N435">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O435"/>
+      <c s="19" t="str" r="P435"/>
+      <c s="19" t="str" r="Q435"/>
+      <c s="19" t="str" r="R435"/>
+      <c s="19" t="inlineStr" r="S435">
+        <is>
+          <t xml:space="preserve">2636005844</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T435"/>
+      <c s="19" t="inlineStr" r="U435">
+        <is>
+          <t xml:space="preserve">5001576953</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V435">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y435">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z435">
+        <is>
+          <t xml:space="preserve">10047305    </t>
+        </is>
+      </c>
+      <c s="20" r="AA435">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB435">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC435">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD435">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF435">
+        <is>
+          <t xml:space="preserve">2003921183</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG435"/>
+    </row>
+    <row r="436" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A436">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B436">
+        <is>
+          <t xml:space="preserve">08:07:21</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C436">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D436">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E436">
+        <v>201052</v>
+      </c>
+      <c s="16" t="inlineStr" r="F436">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H436">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I436">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J436">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K436">
+        <is>
+          <t xml:space="preserve">5012468303</t>
+        </is>
+      </c>
+      <c s="17" r="L436">
+        <v>-102.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M436">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N436">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O436"/>
+      <c s="16" t="str" r="P436"/>
+      <c s="16" t="str" r="Q436"/>
+      <c s="16" t="str" r="R436"/>
+      <c s="16" t="inlineStr" r="S436">
+        <is>
+          <t xml:space="preserve">2636005844</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T436"/>
+      <c s="16" t="inlineStr" r="U436">
+        <is>
+          <t xml:space="preserve">5001576959</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V436">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y436">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z436">
+        <is>
+          <t xml:space="preserve">10047305    </t>
+        </is>
+      </c>
+      <c s="17" r="AA436">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB436">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC436">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD436"/>
+      <c s="16" t="str" r="AF436"/>
+      <c s="7" t="str" r="AG436"/>
+    </row>
+    <row r="437" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A437">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B437">
+        <is>
+          <t xml:space="preserve">08:07:53</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C437">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D437">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E437">
+        <v>201052</v>
+      </c>
+      <c s="19" t="inlineStr" r="F437">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H437">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I437">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J437">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K437">
+        <is>
+          <t xml:space="preserve">5012468324</t>
+        </is>
+      </c>
+      <c s="20" r="L437">
+        <v>92.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M437">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N437">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O437">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P437">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q437"/>
+      <c s="19" t="str" r="R437"/>
+      <c s="19" t="inlineStr" r="S437">
+        <is>
+          <t xml:space="preserve">2636005845</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T437"/>
+      <c s="19" t="inlineStr" r="U437">
+        <is>
+          <t xml:space="preserve">5001576963</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V437">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y437">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z437">
+        <is>
+          <t xml:space="preserve">10047305    </t>
+        </is>
+      </c>
+      <c s="20" r="AA437">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB437">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC437">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD437">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF437">
+        <is>
+          <t xml:space="preserve">2003921183</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG437"/>
+    </row>
+    <row r="438" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A438">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B438">
+        <is>
+          <t xml:space="preserve">08:10:30</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C438">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D438">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E438">
+        <v>200906</v>
+      </c>
+      <c s="16" t="inlineStr" r="F438">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H438">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I438">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J438">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K438">
+        <is>
+          <t xml:space="preserve">5012468327</t>
+        </is>
+      </c>
+      <c s="17" r="L438">
+        <v>489.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M438">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N438">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O438">
+        <is>
+          <t xml:space="preserve">0072</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P438">
+        <is>
+          <t xml:space="preserve">TRV - Quebra de superfície</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q438"/>
+      <c s="16" t="str" r="R438"/>
+      <c s="16" t="inlineStr" r="S438">
+        <is>
+          <t xml:space="preserve">2632005248</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T438"/>
+      <c s="16" t="inlineStr" r="U438">
+        <is>
+          <t xml:space="preserve">5001576967</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V438">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y438">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z438">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="17" r="AA438">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB438">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC438">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD438">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF438">
+        <is>
+          <t xml:space="preserve">2003984078</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG438"/>
+    </row>
+    <row r="439" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A439">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B439">
+        <is>
+          <t xml:space="preserve">08:10:32</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C439">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D439">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E439">
+        <v>222348</v>
+      </c>
+      <c s="19" t="inlineStr" r="F439">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H439">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I439">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J439">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K439">
+        <is>
+          <t xml:space="preserve">5012468328</t>
+        </is>
+      </c>
+      <c s="20" r="L439">
+        <v>2023.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M439">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N439">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O439"/>
+      <c s="19" t="str" r="P439"/>
+      <c s="19" t="str" r="Q439"/>
+      <c s="19" t="str" r="R439"/>
+      <c s="19" t="inlineStr" r="S439">
+        <is>
+          <t xml:space="preserve">2633006583</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T439"/>
+      <c s="19" t="inlineStr" r="U439">
+        <is>
+          <t xml:space="preserve">5001576968</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V439">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y439">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z439">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="20" r="AA439">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB439">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC439">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD439">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF439">
+        <is>
+          <t xml:space="preserve">2002644783</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG439"/>
+    </row>
+    <row r="440" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A440">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B440">
+        <is>
+          <t xml:space="preserve">08:20:11</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C440">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D440">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E440">
+        <v>222348</v>
+      </c>
+      <c s="16" t="inlineStr" r="F440">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H440">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I440">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J440">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K440">
+        <is>
+          <t xml:space="preserve">5012468348</t>
+        </is>
+      </c>
+      <c s="17" r="L440">
+        <v>2022.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M440">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N440">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O440"/>
+      <c s="16" t="str" r="P440"/>
+      <c s="16" t="str" r="Q440"/>
+      <c s="16" t="str" r="R440"/>
+      <c s="16" t="inlineStr" r="S440">
+        <is>
+          <t xml:space="preserve">2633006584</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T440"/>
+      <c s="16" t="inlineStr" r="U440">
+        <is>
+          <t xml:space="preserve">5001576995</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V440">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y440">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z440">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="17" r="AA440">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB440">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC440">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD440">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF440">
+        <is>
+          <t xml:space="preserve">2002644783</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG440"/>
+    </row>
+    <row r="441" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A441">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B441">
+        <is>
+          <t xml:space="preserve">08:31:26</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C441">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D441">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E441">
+        <v>200906</v>
+      </c>
+      <c s="19" t="inlineStr" r="F441">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H441">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I441">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J441">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K441">
+        <is>
+          <t xml:space="preserve">5012468394</t>
+        </is>
+      </c>
+      <c s="20" r="L441">
+        <v>2024.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M441">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N441">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O441"/>
+      <c s="19" t="str" r="P441"/>
+      <c s="19" t="str" r="Q441"/>
+      <c s="19" t="str" r="R441"/>
+      <c s="19" t="inlineStr" r="S441">
+        <is>
+          <t xml:space="preserve">2632005249</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T441"/>
+      <c s="19" t="inlineStr" r="U441">
+        <is>
+          <t xml:space="preserve">5001577046</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V441">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y441">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z441">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" r="AA441">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB441">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC441">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD441">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF441">
+        <is>
+          <t xml:space="preserve">2003984577</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG441"/>
+    </row>
+    <row r="442" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A442">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B442">
+        <is>
+          <t xml:space="preserve">08:56:41</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C442">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D442">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E442">
+        <v>200906</v>
+      </c>
+      <c s="16" t="inlineStr" r="F442">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H442">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I442">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J442">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K442">
+        <is>
+          <t xml:space="preserve">5012468518</t>
+        </is>
+      </c>
+      <c s="17" r="L442">
+        <v>2025.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M442">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N442">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O442"/>
+      <c s="16" t="str" r="P442"/>
+      <c s="16" t="str" r="Q442"/>
+      <c s="16" t="str" r="R442"/>
+      <c s="16" t="inlineStr" r="S442">
+        <is>
+          <t xml:space="preserve">2632005250</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T442"/>
+      <c s="16" t="inlineStr" r="U442">
+        <is>
+          <t xml:space="preserve">5001577157</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V442">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y442">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z442">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="17" r="AA442">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB442">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC442">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD442">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF442">
+        <is>
+          <t xml:space="preserve">2003984577</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG442"/>
+    </row>
+    <row r="443" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A443">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B443">
+        <is>
+          <t xml:space="preserve">09:16:39</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C443">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D443">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E443">
+        <v>200906</v>
+      </c>
+      <c s="19" t="inlineStr" r="F443">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H443">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I443">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J443">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K443">
+        <is>
+          <t xml:space="preserve">5012468566</t>
+        </is>
+      </c>
+      <c s="20" r="L443">
+        <v>2024.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M443">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N443">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O443"/>
+      <c s="19" t="str" r="P443"/>
+      <c s="19" t="str" r="Q443"/>
+      <c s="19" t="str" r="R443"/>
+      <c s="19" t="inlineStr" r="S443">
+        <is>
+          <t xml:space="preserve">2632005251</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T443"/>
+      <c s="19" t="inlineStr" r="U443">
+        <is>
+          <t xml:space="preserve">5001577247</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V443">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y443">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z443">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" r="AA443">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB443">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC443">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD443">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF443">
+        <is>
+          <t xml:space="preserve">2003984577</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG443"/>
+    </row>
+    <row r="444" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A444">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B444">
+        <is>
+          <t xml:space="preserve">09:35:54</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C444">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D444">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E444">
+        <v>200906</v>
+      </c>
+      <c s="16" t="inlineStr" r="F444">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H444">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I444">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J444">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K444">
+        <is>
+          <t xml:space="preserve">5012468650</t>
+        </is>
+      </c>
+      <c s="17" r="L444">
+        <v>2022.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M444">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N444">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O444"/>
+      <c s="16" t="str" r="P444"/>
+      <c s="16" t="str" r="Q444"/>
+      <c s="16" t="str" r="R444"/>
+      <c s="16" t="inlineStr" r="S444">
+        <is>
+          <t xml:space="preserve">2632005252</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T444"/>
+      <c s="16" t="inlineStr" r="U444">
+        <is>
+          <t xml:space="preserve">5001577332</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V444">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y444">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z444">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="17" r="AA444">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB444">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC444">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD444">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF444">
+        <is>
+          <t xml:space="preserve">2003984577</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG444"/>
+    </row>
+    <row r="445" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A445">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B445">
+        <is>
+          <t xml:space="preserve">09:55:12</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C445">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D445">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E445">
+        <v>200906</v>
+      </c>
+      <c s="19" t="inlineStr" r="F445">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H445">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I445">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J445">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K445">
+        <is>
+          <t xml:space="preserve">5012468747</t>
+        </is>
+      </c>
+      <c s="20" r="L445">
+        <v>2018.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M445">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N445">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O445"/>
+      <c s="19" t="str" r="P445"/>
+      <c s="19" t="str" r="Q445"/>
+      <c s="19" t="str" r="R445"/>
+      <c s="19" t="inlineStr" r="S445">
+        <is>
+          <t xml:space="preserve">2632005253</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T445"/>
+      <c s="19" t="inlineStr" r="U445">
+        <is>
+          <t xml:space="preserve">5001577430</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V445">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y445">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z445">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" r="AA445">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB445">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC445">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD445">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF445">
+        <is>
+          <t xml:space="preserve">2003984577</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG445"/>
+    </row>
+    <row r="446" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A446">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B446">
+        <is>
+          <t xml:space="preserve">10:09:48</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C446">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D446">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E446">
+        <v>222535</v>
+      </c>
+      <c s="16" t="inlineStr" r="F446">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H446">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I446">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J446">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K446">
+        <is>
+          <t xml:space="preserve">5012468806</t>
+        </is>
+      </c>
+      <c s="17" r="L446">
+        <v>2130.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M446">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N446">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O446"/>
+      <c s="16" t="str" r="P446"/>
+      <c s="16" t="str" r="Q446"/>
+      <c s="16" t="str" r="R446"/>
+      <c s="16" t="inlineStr" r="S446">
+        <is>
+          <t xml:space="preserve">2633006585</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T446"/>
+      <c s="16" t="inlineStr" r="U446">
+        <is>
+          <t xml:space="preserve">5001577499</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V446">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y446">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z446">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="17" r="AA446">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB446">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC446">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD446">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF446">
+        <is>
+          <t xml:space="preserve">2002644793</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG446"/>
+    </row>
+    <row r="447" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A447">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B447">
+        <is>
+          <t xml:space="preserve">10:19:08</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C447">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D447">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E447">
+        <v>222535</v>
+      </c>
+      <c s="19" t="inlineStr" r="F447">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H447">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I447">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J447">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K447">
+        <is>
+          <t xml:space="preserve">5012468845</t>
+        </is>
+      </c>
+      <c s="20" r="L447">
+        <v>2016.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M447">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N447">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O447"/>
+      <c s="19" t="str" r="P447"/>
+      <c s="19" t="str" r="Q447"/>
+      <c s="19" t="str" r="R447"/>
+      <c s="19" t="inlineStr" r="S447">
+        <is>
+          <t xml:space="preserve">2633006586</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T447"/>
+      <c s="19" t="inlineStr" r="U447">
+        <is>
+          <t xml:space="preserve">5001577549</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V447">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y447">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z447">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="20" r="AA447">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB447">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC447">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD447">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF447">
+        <is>
+          <t xml:space="preserve">2002644793</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG447"/>
+    </row>
+    <row r="448" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A448">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B448">
+        <is>
+          <t xml:space="preserve">10:26:10</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C448">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D448">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E448">
+        <v>222535</v>
+      </c>
+      <c s="16" t="inlineStr" r="F448">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H448">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I448">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J448">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K448">
+        <is>
+          <t xml:space="preserve">5012468906</t>
+        </is>
+      </c>
+      <c s="17" r="L448">
+        <v>2019.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M448">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N448">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O448"/>
+      <c s="16" t="str" r="P448"/>
+      <c s="16" t="str" r="Q448"/>
+      <c s="16" t="str" r="R448"/>
+      <c s="16" t="inlineStr" r="S448">
+        <is>
+          <t xml:space="preserve">2633006587</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T448"/>
+      <c s="16" t="inlineStr" r="U448">
+        <is>
+          <t xml:space="preserve">5001577611</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V448">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y448">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z448">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="17" r="AA448">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB448">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC448">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD448">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF448">
+        <is>
+          <t xml:space="preserve">2002644793</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG448"/>
+    </row>
+    <row r="449" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A449">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B449">
+        <is>
+          <t xml:space="preserve">10:37:29</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C449">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D449">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E449">
+        <v>222535</v>
+      </c>
+      <c s="19" t="inlineStr" r="F449">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H449">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I449">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J449">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K449">
+        <is>
+          <t xml:space="preserve">5012468939</t>
+        </is>
+      </c>
+      <c s="20" r="L449">
+        <v>2022.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M449">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N449">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O449"/>
+      <c s="19" t="str" r="P449"/>
+      <c s="19" t="str" r="Q449"/>
+      <c s="19" t="str" r="R449"/>
+      <c s="19" t="inlineStr" r="S449">
+        <is>
+          <t xml:space="preserve">2633006588</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T449"/>
+      <c s="19" t="inlineStr" r="U449">
+        <is>
+          <t xml:space="preserve">5001577655</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V449">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y449">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z449">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="20" r="AA449">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB449">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC449">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD449">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF449">
+        <is>
+          <t xml:space="preserve">2002644793</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG449"/>
+    </row>
+    <row r="450" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A450">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B450">
+        <is>
+          <t xml:space="preserve">10:37:51</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C450">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D450">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E450">
+        <v>200906</v>
+      </c>
+      <c s="16" t="inlineStr" r="F450">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H450">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I450">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J450">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K450">
+        <is>
+          <t xml:space="preserve">5012468941</t>
+        </is>
+      </c>
+      <c s="17" r="L450">
+        <v>2017.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M450">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N450">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O450">
+        <is>
+          <t xml:space="preserve">0070</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P450">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q450"/>
+      <c s="16" t="str" r="R450"/>
+      <c s="16" t="inlineStr" r="S450">
+        <is>
+          <t xml:space="preserve">2632005254</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T450"/>
+      <c s="16" t="inlineStr" r="U450">
+        <is>
+          <t xml:space="preserve">5001577657</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V450">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y450">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z450">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="17" r="AA450">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB450">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC450">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD450">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF450">
+        <is>
+          <t xml:space="preserve">2003984577</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG450"/>
+    </row>
+    <row r="451" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A451">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B451">
+        <is>
+          <t xml:space="preserve">10:46:38</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C451">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D451">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E451">
+        <v>222535</v>
+      </c>
+      <c s="19" t="inlineStr" r="F451">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H451">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I451">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J451">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K451">
+        <is>
+          <t xml:space="preserve">5012468956</t>
+        </is>
+      </c>
+      <c s="20" r="L451">
+        <v>2022.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M451">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N451">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O451"/>
+      <c s="19" t="str" r="P451"/>
+      <c s="19" t="str" r="Q451"/>
+      <c s="19" t="str" r="R451"/>
+      <c s="19" t="inlineStr" r="S451">
+        <is>
+          <t xml:space="preserve">2633006589</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T451"/>
+      <c s="19" t="inlineStr" r="U451">
+        <is>
+          <t xml:space="preserve">5001577692</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V451">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y451">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z451">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="20" r="AA451">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB451">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC451">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD451">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF451">
+        <is>
+          <t xml:space="preserve">2002644793</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG451"/>
+    </row>
+    <row r="452" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A452">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B452">
+        <is>
+          <t xml:space="preserve">10:53:10</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C452">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D452">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E452">
+        <v>200906</v>
+      </c>
+      <c s="16" t="inlineStr" r="F452">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H452">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I452">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J452">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K452">
+        <is>
+          <t xml:space="preserve">5012468988</t>
+        </is>
+      </c>
+      <c s="17" r="L452">
+        <v>2022.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M452">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N452">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O452"/>
+      <c s="16" t="str" r="P452"/>
+      <c s="16" t="str" r="Q452"/>
+      <c s="16" t="str" r="R452"/>
+      <c s="16" t="inlineStr" r="S452">
+        <is>
+          <t xml:space="preserve">2632005255</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T452"/>
+      <c s="16" t="inlineStr" r="U452">
+        <is>
+          <t xml:space="preserve">5001577723</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V452">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y452">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z452">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="17" r="AA452">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB452">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC452">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD452">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF452">
+        <is>
+          <t xml:space="preserve">2003994368</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG452"/>
+    </row>
+    <row r="453" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A453">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B453">
+        <is>
+          <t xml:space="preserve">11:14:50</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C453">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D453">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E453">
+        <v>200906</v>
+      </c>
+      <c s="19" t="inlineStr" r="F453">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H453">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I453">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J453">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K453">
+        <is>
+          <t xml:space="preserve">5012469053</t>
+        </is>
+      </c>
+      <c s="20" r="L453">
+        <v>2021.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M453">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N453">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O453"/>
+      <c s="19" t="str" r="P453"/>
+      <c s="19" t="str" r="Q453"/>
+      <c s="19" t="str" r="R453"/>
+      <c s="19" t="inlineStr" r="S453">
+        <is>
+          <t xml:space="preserve">2632005256</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T453"/>
+      <c s="19" t="inlineStr" r="U453">
+        <is>
+          <t xml:space="preserve">5001577862</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V453">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y453">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z453">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" r="AA453">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB453">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC453">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD453">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF453">
+        <is>
+          <t xml:space="preserve">2003994368</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG453"/>
+    </row>
+    <row r="454" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A454">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B454">
+        <is>
+          <t xml:space="preserve">11:35:40</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C454">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D454">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E454">
+        <v>200906</v>
+      </c>
+      <c s="16" t="inlineStr" r="F454">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H454">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I454">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J454">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K454">
+        <is>
+          <t xml:space="preserve">5012469121</t>
+        </is>
+      </c>
+      <c s="17" r="L454">
+        <v>2022.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M454">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N454">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O454"/>
+      <c s="16" t="str" r="P454"/>
+      <c s="16" t="str" r="Q454"/>
+      <c s="16" t="str" r="R454"/>
+      <c s="16" t="inlineStr" r="S454">
+        <is>
+          <t xml:space="preserve">2632005257</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T454"/>
+      <c s="16" t="inlineStr" r="U454">
+        <is>
+          <t xml:space="preserve">5001578079</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V454">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y454">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z454">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="17" r="AA454">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB454">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC454">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD454">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF454">
+        <is>
+          <t xml:space="preserve">2003994368</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG454"/>
+    </row>
+    <row r="455" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A455">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B455">
+        <is>
+          <t xml:space="preserve">11:57:35</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C455">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D455">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E455">
+        <v>200906</v>
+      </c>
+      <c s="19" t="inlineStr" r="F455">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H455">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I455">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J455">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K455">
+        <is>
+          <t xml:space="preserve">5012469189</t>
+        </is>
+      </c>
+      <c s="20" r="L455">
+        <v>2022.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M455">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N455">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O455"/>
+      <c s="19" t="str" r="P455"/>
+      <c s="19" t="str" r="Q455"/>
+      <c s="19" t="str" r="R455"/>
+      <c s="19" t="inlineStr" r="S455">
+        <is>
+          <t xml:space="preserve">2632005258</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T455"/>
+      <c s="19" t="inlineStr" r="U455">
+        <is>
+          <t xml:space="preserve">5001578248</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V455">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y455">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z455">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" r="AA455">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB455">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC455">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD455">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF455">
+        <is>
+          <t xml:space="preserve">2003994368</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG455"/>
+    </row>
+    <row r="456" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A456">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B456">
+        <is>
+          <t xml:space="preserve">12:19:25</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C456">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D456">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E456">
+        <v>200906</v>
+      </c>
+      <c s="16" t="inlineStr" r="F456">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H456">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I456">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J456">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K456">
+        <is>
+          <t xml:space="preserve">5012469236</t>
+        </is>
+      </c>
+      <c s="17" r="L456">
+        <v>2025.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M456">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N456">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O456"/>
+      <c s="16" t="str" r="P456"/>
+      <c s="16" t="str" r="Q456"/>
+      <c s="16" t="str" r="R456"/>
+      <c s="16" t="inlineStr" r="S456">
+        <is>
+          <t xml:space="preserve">2632005259</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T456"/>
+      <c s="16" t="inlineStr" r="U456">
+        <is>
+          <t xml:space="preserve">5001578405</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V456">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y456">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z456">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="17" r="AA456">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB456">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC456">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD456">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF456">
+        <is>
+          <t xml:space="preserve">2003994368</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG456"/>
+    </row>
+    <row r="457" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A457">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B457">
+        <is>
+          <t xml:space="preserve">12:36:59</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C457">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D457">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E457">
+        <v>222535</v>
+      </c>
+      <c s="19" t="inlineStr" r="F457">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H457">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I457">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J457">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K457">
+        <is>
+          <t xml:space="preserve">5012469278</t>
+        </is>
+      </c>
+      <c s="20" r="L457">
+        <v>1920.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M457">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N457">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O457"/>
+      <c s="19" t="str" r="P457"/>
+      <c s="19" t="str" r="Q457"/>
+      <c s="19" t="str" r="R457"/>
+      <c s="19" t="inlineStr" r="S457">
+        <is>
+          <t xml:space="preserve">2633006590</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T457"/>
+      <c s="19" t="inlineStr" r="U457">
+        <is>
+          <t xml:space="preserve">5001578467</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V457">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y457">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z457">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="20" r="AA457">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB457">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC457">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD457">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF457">
+        <is>
+          <t xml:space="preserve">2002644770</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG457"/>
+    </row>
+    <row r="458" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A458">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B458">
+        <is>
+          <t xml:space="preserve">12:41:54</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C458">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D458">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E458">
+        <v>222535</v>
+      </c>
+      <c s="16" t="inlineStr" r="F458">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H458">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I458">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J458">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K458">
+        <is>
+          <t xml:space="preserve">5012469286</t>
+        </is>
+      </c>
+      <c s="17" r="L458">
+        <v>2035.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M458">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N458">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O458"/>
+      <c s="16" t="str" r="P458"/>
+      <c s="16" t="str" r="Q458"/>
+      <c s="16" t="str" r="R458"/>
+      <c s="16" t="inlineStr" r="S458">
+        <is>
+          <t xml:space="preserve">2633006591</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T458"/>
+      <c s="16" t="inlineStr" r="U458">
+        <is>
+          <t xml:space="preserve">5001578495</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V458">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y458">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z458">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="17" r="AA458">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB458">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC458">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD458">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF458">
+        <is>
+          <t xml:space="preserve">2002644770</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG458"/>
+    </row>
+    <row r="459" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A459">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B459">
+        <is>
+          <t xml:space="preserve">12:44:35</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C459">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D459">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E459">
+        <v>200906</v>
+      </c>
+      <c s="19" t="inlineStr" r="F459">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H459">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I459">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J459">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K459">
+        <is>
+          <t xml:space="preserve">5012469291</t>
+        </is>
+      </c>
+      <c s="20" r="L459">
+        <v>1126.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M459">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N459">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O459"/>
+      <c s="19" t="str" r="P459"/>
+      <c s="19" t="str" r="Q459"/>
+      <c s="19" t="str" r="R459"/>
+      <c s="19" t="inlineStr" r="S459">
+        <is>
+          <t xml:space="preserve">2632005260</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T459"/>
+      <c s="19" t="inlineStr" r="U459">
+        <is>
+          <t xml:space="preserve">5001578510</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V459">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y459">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z459">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" r="AA459">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB459">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC459">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD459">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF459">
+        <is>
+          <t xml:space="preserve">2003994368</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG459"/>
+    </row>
+    <row r="460" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A460">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B460">
+        <is>
+          <t xml:space="preserve">12:49:13</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C460">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D460">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E460">
+        <v>200906</v>
+      </c>
+      <c s="16" t="inlineStr" r="F460">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H460">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I460">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J460">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K460">
+        <is>
+          <t xml:space="preserve">5012469316</t>
+        </is>
+      </c>
+      <c s="17" r="L460">
+        <v>403.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M460">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N460">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O460">
+        <is>
+          <t xml:space="preserve">0072</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P460">
+        <is>
+          <t xml:space="preserve">TRV - Quebra de superfície</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q460"/>
+      <c s="16" t="str" r="R460"/>
+      <c s="16" t="inlineStr" r="S460">
+        <is>
+          <t xml:space="preserve">2632005261</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T460"/>
+      <c s="16" t="inlineStr" r="U460">
+        <is>
+          <t xml:space="preserve">5001578522</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V460">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y460">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z460">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="17" r="AA460">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB460">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC460">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD460">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF460">
+        <is>
+          <t xml:space="preserve">2003994369</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG460"/>
+    </row>
+    <row r="461" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A461">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B461">
+        <is>
+          <t xml:space="preserve">12:51:01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C461">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D461">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E461">
+        <v>222535</v>
+      </c>
+      <c s="19" t="inlineStr" r="F461">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H461">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I461">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J461">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K461">
+        <is>
+          <t xml:space="preserve">5012469318</t>
+        </is>
+      </c>
+      <c s="20" r="L461">
+        <v>2033.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M461">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N461">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O461"/>
+      <c s="19" t="str" r="P461"/>
+      <c s="19" t="str" r="Q461"/>
+      <c s="19" t="str" r="R461"/>
+      <c s="19" t="inlineStr" r="S461">
+        <is>
+          <t xml:space="preserve">2633006592</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T461"/>
+      <c s="19" t="inlineStr" r="U461">
+        <is>
+          <t xml:space="preserve">5001578525</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V461">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y461">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z461">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="20" r="AA461">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB461">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC461">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD461">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF461">
+        <is>
+          <t xml:space="preserve">2002644770</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG461"/>
+    </row>
+    <row r="462" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A462">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B462">
+        <is>
+          <t xml:space="preserve">12:59:17</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C462">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D462">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E462">
+        <v>222535</v>
+      </c>
+      <c s="16" t="inlineStr" r="F462">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H462">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I462">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J462">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K462">
+        <is>
+          <t xml:space="preserve">5012469333</t>
+        </is>
+      </c>
+      <c s="17" r="L462">
+        <v>2034.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M462">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N462">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O462"/>
+      <c s="16" t="str" r="P462"/>
+      <c s="16" t="str" r="Q462"/>
+      <c s="16" t="str" r="R462"/>
+      <c s="16" t="inlineStr" r="S462">
+        <is>
+          <t xml:space="preserve">2633006593</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T462"/>
+      <c s="16" t="inlineStr" r="U462">
+        <is>
+          <t xml:space="preserve">5001578560</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V462">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y462">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z462">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="17" r="AA462">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB462">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC462">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD462">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF462">
+        <is>
+          <t xml:space="preserve">2002644770</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG462"/>
+    </row>
+    <row r="463" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A463">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B463">
+        <is>
+          <t xml:space="preserve">13:09:42</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C463">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D463">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E463">
+        <v>200906</v>
+      </c>
+      <c s="19" t="inlineStr" r="F463">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H463">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I463">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J463">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K463">
+        <is>
+          <t xml:space="preserve">5012469391</t>
+        </is>
+      </c>
+      <c s="20" r="L463">
+        <v>2018.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M463">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N463">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O463"/>
+      <c s="19" t="str" r="P463"/>
+      <c s="19" t="str" r="Q463"/>
+      <c s="19" t="str" r="R463"/>
+      <c s="19" t="inlineStr" r="S463">
+        <is>
+          <t xml:space="preserve">2632005262</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T463"/>
+      <c s="19" t="inlineStr" r="U463">
+        <is>
+          <t xml:space="preserve">5001578681</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V463">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y463">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z463">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" r="AA463">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB463">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC463">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD463">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF463">
+        <is>
+          <t xml:space="preserve">2003994369</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG463"/>
+    </row>
+    <row r="464" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A464">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B464">
+        <is>
+          <t xml:space="preserve">13:10:26</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C464">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D464">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E464">
+        <v>222535</v>
+      </c>
+      <c s="16" t="inlineStr" r="F464">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H464">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I464">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J464">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K464">
+        <is>
+          <t xml:space="preserve">5012469395</t>
+        </is>
+      </c>
+      <c s="17" r="L464">
+        <v>2032.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M464">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N464">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O464"/>
+      <c s="16" t="str" r="P464"/>
+      <c s="16" t="str" r="Q464"/>
+      <c s="16" t="str" r="R464"/>
+      <c s="16" t="inlineStr" r="S464">
+        <is>
+          <t xml:space="preserve">2633006594</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T464"/>
+      <c s="16" t="inlineStr" r="U464">
+        <is>
+          <t xml:space="preserve">5001578685</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V464">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y464">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z464">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="17" r="AA464">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB464">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC464">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD464">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF464">
+        <is>
+          <t xml:space="preserve">2002644770</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG464"/>
+    </row>
+    <row r="465" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A465">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B465">
+        <is>
+          <t xml:space="preserve">13:17:43</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C465">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D465">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E465">
+        <v>222535</v>
+      </c>
+      <c s="19" t="inlineStr" r="F465">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H465">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I465">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J465">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K465">
+        <is>
+          <t xml:space="preserve">5012469417</t>
+        </is>
+      </c>
+      <c s="20" r="L465">
+        <v>337.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M465">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N465">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O465"/>
+      <c s="19" t="str" r="P465"/>
+      <c s="19" t="str" r="Q465"/>
+      <c s="19" t="str" r="R465"/>
+      <c s="19" t="inlineStr" r="S465">
+        <is>
+          <t xml:space="preserve">2633006595</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T465"/>
+      <c s="19" t="inlineStr" r="U465">
+        <is>
+          <t xml:space="preserve">5001578708</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V465">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y465">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z465">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="20" r="AA465">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB465">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC465">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD465">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF465">
+        <is>
+          <t xml:space="preserve">2002644770</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG465"/>
+    </row>
+    <row r="466" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A466">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B466">
+        <is>
+          <t xml:space="preserve">13:18:56</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C466">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D466">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E466">
+        <v>222535</v>
+      </c>
+      <c s="16" t="inlineStr" r="F466">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H466">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I466">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J466">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K466">
+        <is>
+          <t xml:space="preserve">5012469421</t>
+        </is>
+      </c>
+      <c s="17" r="L466">
+        <v>685.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M466">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N466">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O466"/>
+      <c s="16" t="str" r="P466"/>
+      <c s="16" t="str" r="Q466"/>
+      <c s="16" t="str" r="R466"/>
+      <c s="16" t="inlineStr" r="S466">
+        <is>
+          <t xml:space="preserve">2633006596</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T466"/>
+      <c s="16" t="inlineStr" r="U466">
+        <is>
+          <t xml:space="preserve">5001578732</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V466">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y466">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z466">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="17" r="AA466">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB466">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC466">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD466">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF466">
+        <is>
+          <t xml:space="preserve">2002644770</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG466"/>
+    </row>
+    <row r="467" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A467">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B467">
+        <is>
+          <t xml:space="preserve">13:19:17</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C467">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D467">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E467">
+        <v>222535</v>
+      </c>
+      <c s="19" t="inlineStr" r="F467">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H467">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I467">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J467">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K467">
+        <is>
+          <t xml:space="preserve">5012469421</t>
+        </is>
+      </c>
+      <c s="20" r="L467">
+        <v>-685.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M467">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N467">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O467"/>
+      <c s="19" t="str" r="P467"/>
+      <c s="19" t="str" r="Q467"/>
+      <c s="19" t="str" r="R467"/>
+      <c s="19" t="inlineStr" r="S467">
+        <is>
+          <t xml:space="preserve">2633006596</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T467"/>
+      <c s="19" t="inlineStr" r="U467">
+        <is>
+          <t xml:space="preserve">5001578733</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V467">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y467">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z467">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="20" r="AA467">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB467">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC467">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD467"/>
+      <c s="19" t="str" r="AF467"/>
+      <c s="7" t="str" r="AG467"/>
+    </row>
+    <row r="468" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A468">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B468">
+        <is>
+          <t xml:space="preserve">13:19:42</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C468">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D468">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E468">
+        <v>222535</v>
+      </c>
+      <c s="16" t="inlineStr" r="F468">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H468">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I468">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J468">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K468">
+        <is>
+          <t xml:space="preserve">5012469422</t>
+        </is>
+      </c>
+      <c s="17" r="L468">
+        <v>682.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M468">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N468">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O468">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P468">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q468"/>
+      <c s="16" t="str" r="R468"/>
+      <c s="16" t="inlineStr" r="S468">
+        <is>
+          <t xml:space="preserve">2633006597</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T468"/>
+      <c s="16" t="inlineStr" r="U468">
+        <is>
+          <t xml:space="preserve">5001578734</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V468">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y468">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z468">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="17" r="AA468">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB468">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC468">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD468">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF468">
+        <is>
+          <t xml:space="preserve">2002644770</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG468"/>
+    </row>
+    <row r="469" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A469">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B469">
+        <is>
+          <t xml:space="preserve">13:30:01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C469">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D469">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E469">
+        <v>200906</v>
+      </c>
+      <c s="19" t="inlineStr" r="F469">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H469">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I469">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J469">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K469">
+        <is>
+          <t xml:space="preserve">5012469458</t>
+        </is>
+      </c>
+      <c s="20" r="L469">
+        <v>2017.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M469">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N469">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O469"/>
+      <c s="19" t="str" r="P469"/>
+      <c s="19" t="str" r="Q469"/>
+      <c s="19" t="str" r="R469"/>
+      <c s="19" t="inlineStr" r="S469">
+        <is>
+          <t xml:space="preserve">2632005263</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T469"/>
+      <c s="19" t="inlineStr" r="U469">
+        <is>
+          <t xml:space="preserve">5001578790</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V469">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y469">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z469">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" r="AA469">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB469">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC469">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD469">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF469">
+        <is>
+          <t xml:space="preserve">2003994369</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG469"/>
+    </row>
+    <row r="470" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A470">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B470">
+        <is>
+          <t xml:space="preserve">13:50:51</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C470">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D470">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E470">
+        <v>200906</v>
+      </c>
+      <c s="16" t="inlineStr" r="F470">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H470">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I470">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J470">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K470">
+        <is>
+          <t xml:space="preserve">5012469555</t>
+        </is>
+      </c>
+      <c s="17" r="L470">
+        <v>2019.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M470">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N470">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O470"/>
+      <c s="16" t="str" r="P470"/>
+      <c s="16" t="str" r="Q470"/>
+      <c s="16" t="str" r="R470"/>
+      <c s="16" t="inlineStr" r="S470">
+        <is>
+          <t xml:space="preserve">2632005264</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T470"/>
+      <c s="16" t="inlineStr" r="U470">
+        <is>
+          <t xml:space="preserve">5001578919</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V470">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y470">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z470">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="17" r="AA470">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB470">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC470">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD470">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF470">
+        <is>
+          <t xml:space="preserve">2003994369</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG470"/>
+    </row>
+    <row r="471" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A471">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B471">
+        <is>
+          <t xml:space="preserve">13:53:58</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C471">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D471">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E471">
+        <v>222535</v>
+      </c>
+      <c s="19" t="inlineStr" r="F471">
+        <is>
+          <t xml:space="preserve">CH PLANA 4,25mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H471">
+        <is>
+          <t xml:space="preserve">4,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I471">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J471">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K471">
+        <is>
+          <t xml:space="preserve">5012469568</t>
+        </is>
+      </c>
+      <c s="20" r="L471">
+        <v>443.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M471">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N471">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O471">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P471">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q471"/>
+      <c s="19" t="str" r="R471"/>
+      <c s="19" t="inlineStr" r="S471">
+        <is>
+          <t xml:space="preserve">2633006598</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T471"/>
+      <c s="19" t="inlineStr" r="U471">
+        <is>
+          <t xml:space="preserve">5001578942</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V471">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y471">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z471">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="20" r="AA471">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB471">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC471">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD471">
+        <is>
+          <t xml:space="preserve">SDC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF471">
+        <is>
+          <t xml:space="preserve">2002644770</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG471"/>
+    </row>
+    <row r="472" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A472">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B472">
+        <is>
+          <t xml:space="preserve">14:13:59</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C472">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D472">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E472">
+        <v>200906</v>
+      </c>
+      <c s="16" t="inlineStr" r="F472">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H472">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I472">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J472">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K472">
+        <is>
+          <t xml:space="preserve">5012469615</t>
+        </is>
+      </c>
+      <c s="17" r="L472">
+        <v>2016.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M472">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N472">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O472"/>
+      <c s="16" t="str" r="P472"/>
+      <c s="16" t="str" r="Q472"/>
+      <c s="16" t="str" r="R472"/>
+      <c s="16" t="inlineStr" r="S472">
+        <is>
+          <t xml:space="preserve">2632005265</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T472"/>
+      <c s="16" t="inlineStr" r="U472">
+        <is>
+          <t xml:space="preserve">5001579091</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V472">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y472">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z472">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="17" r="AA472">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB472">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC472">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD472">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF472">
+        <is>
+          <t xml:space="preserve">2003994369</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG472"/>
+    </row>
+    <row r="473" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A473">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B473">
+        <is>
+          <t xml:space="preserve">14:18:29</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C473">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D473">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E473">
+        <v>201157</v>
+      </c>
+      <c s="19" t="inlineStr" r="F473">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,65mm LQ 2300mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H473">
+        <is>
+          <t xml:space="preserve">2,65mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I473">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J473">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K473">
+        <is>
+          <t xml:space="preserve">5012469621</t>
+        </is>
+      </c>
+      <c s="20" r="L473">
+        <v>2030.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M473">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N473">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O473"/>
+      <c s="19" t="str" r="P473"/>
+      <c s="19" t="str" r="Q473"/>
+      <c s="19" t="str" r="R473"/>
+      <c s="19" t="inlineStr" r="S473">
+        <is>
+          <t xml:space="preserve">2633006599</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T473"/>
+      <c s="19" t="inlineStr" r="U473">
+        <is>
+          <t xml:space="preserve">5001579097</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V473">
+        <is>
+          <t xml:space="preserve">20131838</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y473">
+        <is>
+          <t xml:space="preserve">JVI INSTALACOES COMERCIAIS LTDA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z473">
+        <is>
+          <t xml:space="preserve">10048736    </t>
+        </is>
+      </c>
+      <c s="20" r="AA473">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB473">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC473">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD473">
+        <is>
+          <t xml:space="preserve">EFS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF473">
+        <is>
+          <t xml:space="preserve">2003853003</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG473"/>
+    </row>
+    <row r="474" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A474">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B474">
+        <is>
+          <t xml:space="preserve">14:30:35</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C474">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D474">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E474">
+        <v>201157</v>
+      </c>
+      <c s="16" t="inlineStr" r="F474">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,65mm LQ 2300mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H474">
+        <is>
+          <t xml:space="preserve">2,65mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I474">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J474">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K474">
+        <is>
+          <t xml:space="preserve">5012469635</t>
+        </is>
+      </c>
+      <c s="17" r="L474">
+        <v>1975.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M474">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N474">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O474"/>
+      <c s="16" t="str" r="P474"/>
+      <c s="16" t="str" r="Q474"/>
+      <c s="16" t="str" r="R474"/>
+      <c s="16" t="inlineStr" r="S474">
+        <is>
+          <t xml:space="preserve">2633006600</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T474"/>
+      <c s="16" t="inlineStr" r="U474">
+        <is>
+          <t xml:space="preserve">5001579171</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V474">
+        <is>
+          <t xml:space="preserve">20131838</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y474">
+        <is>
+          <t xml:space="preserve">JVI INSTALACOES COMERCIAIS LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z474">
+        <is>
+          <t xml:space="preserve">10048736    </t>
+        </is>
+      </c>
+      <c s="17" r="AA474">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB474">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC474">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD474">
+        <is>
+          <t xml:space="preserve">EFS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF474">
+        <is>
+          <t xml:space="preserve">2003853003</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG474"/>
+    </row>
+    <row r="475" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A475">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B475">
+        <is>
+          <t xml:space="preserve">14:54:00</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C475">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D475">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E475">
+        <v>208890</v>
+      </c>
+      <c s="19" t="inlineStr" r="F475">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,65mm LQ 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H475">
+        <is>
+          <t xml:space="preserve">2,65mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I475">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J475">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K475">
+        <is>
+          <t xml:space="preserve">5012469642</t>
+        </is>
+      </c>
+      <c s="20" r="L475">
+        <v>2168.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M475">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N475">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O475"/>
+      <c s="19" t="str" r="P475"/>
+      <c s="19" t="str" r="Q475"/>
+      <c s="19" t="str" r="R475"/>
+      <c s="19" t="inlineStr" r="S475">
+        <is>
+          <t xml:space="preserve">2633006601</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T475"/>
+      <c s="19" t="inlineStr" r="U475">
+        <is>
+          <t xml:space="preserve">5001579178</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V475">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y475">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z475">
+        <is>
+          <t xml:space="preserve">10048737    </t>
+        </is>
+      </c>
+      <c s="20" r="AA475">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB475">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC475">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD475">
+        <is>
+          <t xml:space="preserve">EFS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF475">
+        <is>
+          <t xml:space="preserve">2003853003</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG475"/>
+    </row>
+    <row r="476" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A476">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B476">
+        <is>
+          <t xml:space="preserve">15:03:23</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C476">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D476">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E476">
+        <v>200906</v>
+      </c>
+      <c s="16" t="inlineStr" r="F476">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,45mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H476">
+        <is>
+          <t xml:space="preserve">0,45mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I476">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J476">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K476">
+        <is>
+          <t xml:space="preserve">5012469652</t>
+        </is>
+      </c>
+      <c s="17" r="L476">
+        <v>2093.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M476">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N476">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O476"/>
+      <c s="16" t="str" r="P476"/>
+      <c s="16" t="str" r="Q476"/>
+      <c s="16" t="str" r="R476"/>
+      <c s="16" t="inlineStr" r="S476">
+        <is>
+          <t xml:space="preserve">2632005266</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T476"/>
+      <c s="16" t="inlineStr" r="U476">
+        <is>
+          <t xml:space="preserve">5001579279</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V476">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y476">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z476">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="17" r="AA476">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB476">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC476">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD476">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF476">
+        <is>
+          <t xml:space="preserve">2003994369</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG476"/>
+    </row>
+    <row r="477" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A477">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B477">
+        <is>
+          <t xml:space="preserve">15:11:02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C477">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D477">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E477">
+        <v>208890</v>
+      </c>
+      <c s="19" t="inlineStr" r="F477">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,65mm LQ 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H477">
+        <is>
+          <t xml:space="preserve">2,65mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I477">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J477">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K477">
+        <is>
+          <t xml:space="preserve">5012469665</t>
+        </is>
+      </c>
+      <c s="20" r="L477">
+        <v>2112.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M477">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N477">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O477"/>
+      <c s="19" t="str" r="P477"/>
+      <c s="19" t="str" r="Q477"/>
+      <c s="19" t="str" r="R477"/>
+      <c s="19" t="inlineStr" r="S477">
+        <is>
+          <t xml:space="preserve">2633006602</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T477"/>
+      <c s="19" t="inlineStr" r="U477">
+        <is>
+          <t xml:space="preserve">5001579323</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V477">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y477">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z477">
+        <is>
+          <t xml:space="preserve">10048737    </t>
+        </is>
+      </c>
+      <c s="20" r="AA477">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB477">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC477">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD477">
+        <is>
+          <t xml:space="preserve">EFS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF477">
+        <is>
+          <t xml:space="preserve">2003853003</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG477"/>
+    </row>
+    <row r="478" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A478">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B478">
+        <is>
+          <t xml:space="preserve">15:22:38</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C478">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D478">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E478">
+        <v>200902</v>
+      </c>
+      <c s="16" t="inlineStr" r="F478">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 1350mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H478">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I478">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J478">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K478">
+        <is>
+          <t xml:space="preserve">5012469705</t>
+        </is>
+      </c>
+      <c s="17" r="L478">
+        <v>1005.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M478">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N478">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O478"/>
+      <c s="16" t="str" r="P478"/>
+      <c s="16" t="str" r="Q478"/>
+      <c s="16" t="str" r="R478"/>
+      <c s="16" t="inlineStr" r="S478">
+        <is>
+          <t xml:space="preserve">2635002679</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T478"/>
+      <c s="16" t="inlineStr" r="U478">
+        <is>
+          <t xml:space="preserve">5001579403</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V478">
+        <is>
+          <t xml:space="preserve">20131838</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y478">
+        <is>
+          <t xml:space="preserve">JVI INSTALACOES COMERCIAIS LTDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z478">
+        <is>
+          <t xml:space="preserve">10048747    </t>
+        </is>
+      </c>
+      <c s="17" r="AA478">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB478">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC478">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD478">
+        <is>
+          <t xml:space="preserve">AMS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF478">
+        <is>
+          <t xml:space="preserve">2003627070</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG478"/>
+    </row>
+    <row r="479" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A479">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B479">
+        <is>
+          <t xml:space="preserve">15:27:48</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C479">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D479">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E479">
+        <v>207635</v>
+      </c>
+      <c s="19" t="inlineStr" r="F479">
+        <is>
+          <t xml:space="preserve">SUCATA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H479">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I479">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J479">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="K479"/>
+      <c s="20" r="L479">
+        <v>300.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M479">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N479">
+        <is>
+          <t xml:space="preserve">SUCATA</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O479"/>
+      <c s="19" t="str" r="P479"/>
+      <c s="19" t="str" r="Q479"/>
+      <c s="19" t="str" r="R479"/>
+      <c s="19" t="str" r="S479"/>
+      <c s="19" t="str" r="T479"/>
+      <c s="19" t="inlineStr" r="U479">
+        <is>
+          <t xml:space="preserve">5001579461</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V479">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y479">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z479">
+        <is>
+          <t xml:space="preserve">10048754    </t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AA479"/>
+      <c s="19" t="str" r="AB479"/>
+      <c s="19" t="inlineStr" r="AC479">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD479">
+        <is>
+          <t xml:space="preserve">AMS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF479">
+        <is>
+          <t xml:space="preserve">2003627070</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG479"/>
+    </row>
+    <row r="480" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A480">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B480">
+        <is>
+          <t xml:space="preserve">15:28:05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C480">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D480">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E480">
+        <v>200943</v>
+      </c>
+      <c s="16" t="inlineStr" r="F480">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H480">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I480">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J480">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K480">
+        <is>
+          <t xml:space="preserve">5012469731</t>
+        </is>
+      </c>
+      <c s="17" r="L480">
+        <v>2030.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M480">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N480">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O480"/>
+      <c s="16" t="str" r="P480"/>
+      <c s="16" t="str" r="Q480"/>
+      <c s="16" t="str" r="R480"/>
+      <c s="16" t="inlineStr" r="S480">
+        <is>
+          <t xml:space="preserve">2635002680</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T480"/>
+      <c s="16" t="inlineStr" r="U480">
+        <is>
+          <t xml:space="preserve">5001579462</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V480">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y480">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z480">
+        <is>
+          <t xml:space="preserve">10048754    </t>
+        </is>
+      </c>
+      <c s="17" r="AA480">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB480">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC480">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD480">
+        <is>
+          <t xml:space="preserve">AMS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF480">
+        <is>
+          <t xml:space="preserve">2003627070</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG480"/>
+    </row>
+    <row r="481" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A481">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B481">
+        <is>
+          <t xml:space="preserve">15:28:23</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C481">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D481">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E481">
+        <v>200943</v>
+      </c>
+      <c s="19" t="inlineStr" r="F481">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H481">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I481">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J481">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K481">
+        <is>
+          <t xml:space="preserve">5012469733</t>
+        </is>
+      </c>
+      <c s="20" r="L481">
+        <v>2029.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M481">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N481">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O481"/>
+      <c s="19" t="str" r="P481"/>
+      <c s="19" t="str" r="Q481"/>
+      <c s="19" t="str" r="R481"/>
+      <c s="19" t="inlineStr" r="S481">
+        <is>
+          <t xml:space="preserve">2635002681</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T481"/>
+      <c s="19" t="inlineStr" r="U481">
+        <is>
+          <t xml:space="preserve">5001579464</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V481">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y481">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z481">
+        <is>
+          <t xml:space="preserve">10048754    </t>
+        </is>
+      </c>
+      <c s="20" r="AA481">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB481">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC481">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD481">
+        <is>
+          <t xml:space="preserve">AMS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF481">
+        <is>
+          <t xml:space="preserve">2003627070</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG481"/>
+    </row>
+    <row r="482" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A482">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B482">
+        <is>
+          <t xml:space="preserve">15:28:39</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C482">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D482">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E482">
+        <v>200943</v>
+      </c>
+      <c s="16" t="inlineStr" r="F482">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H482">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I482">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J482">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K482">
+        <is>
+          <t xml:space="preserve">5012469734</t>
+        </is>
+      </c>
+      <c s="17" r="L482">
+        <v>2031.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M482">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N482">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O482"/>
+      <c s="16" t="str" r="P482"/>
+      <c s="16" t="str" r="Q482"/>
+      <c s="16" t="str" r="R482"/>
+      <c s="16" t="inlineStr" r="S482">
+        <is>
+          <t xml:space="preserve">2635002682</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T482"/>
+      <c s="16" t="inlineStr" r="U482">
+        <is>
+          <t xml:space="preserve">5001579465</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V482">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y482">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z482">
+        <is>
+          <t xml:space="preserve">10048754    </t>
+        </is>
+      </c>
+      <c s="17" r="AA482">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB482">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC482">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD482">
+        <is>
+          <t xml:space="preserve">AMS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF482">
+        <is>
+          <t xml:space="preserve">2003627070</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG482"/>
+    </row>
+    <row r="483" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A483">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B483">
+        <is>
+          <t xml:space="preserve">15:31:04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C483">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D483">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E483">
+        <v>207635</v>
+      </c>
+      <c s="19" t="inlineStr" r="F483">
+        <is>
+          <t xml:space="preserve">SUCATA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H483">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I483">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J483">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="K483"/>
+      <c s="20" r="L483">
+        <v>189.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M483">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N483">
+        <is>
+          <t xml:space="preserve">SUCATA</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O483"/>
+      <c s="19" t="str" r="P483"/>
+      <c s="19" t="str" r="Q483"/>
+      <c s="19" t="str" r="R483"/>
+      <c s="19" t="str" r="S483"/>
+      <c s="19" t="str" r="T483"/>
+      <c s="19" t="inlineStr" r="U483">
+        <is>
+          <t xml:space="preserve">5001579478</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V483">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y483">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z483">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AA483"/>
+      <c s="19" t="str" r="AB483"/>
+      <c s="19" t="inlineStr" r="AC483">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD483">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF483">
+        <is>
+          <t xml:space="preserve">2003994369</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG483"/>
+    </row>
+    <row r="484" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A484">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B484">
+        <is>
+          <t xml:space="preserve">15:35:24</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C484">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D484">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E484">
+        <v>200943</v>
+      </c>
+      <c s="16" t="inlineStr" r="F484">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,60mm LF 2000mm X 1000mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H484">
+        <is>
+          <t xml:space="preserve">0,60mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I484">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J484">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K484">
+        <is>
+          <t xml:space="preserve">5012469756</t>
+        </is>
+      </c>
+      <c s="17" r="L484">
+        <v>492.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M484">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N484">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O484">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P484">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q484"/>
+      <c s="16" t="str" r="R484"/>
+      <c s="16" t="inlineStr" r="S484">
+        <is>
+          <t xml:space="preserve">2635002683</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T484"/>
+      <c s="16" t="inlineStr" r="U484">
+        <is>
+          <t xml:space="preserve">5001579510</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V484">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y484">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z484">
+        <is>
+          <t xml:space="preserve">10048754    </t>
+        </is>
+      </c>
+      <c s="17" r="AA484">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB484">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC484">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD484">
+        <is>
+          <t xml:space="preserve">AMS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF484">
+        <is>
+          <t xml:space="preserve">2003627070</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG484"/>
+    </row>
+    <row r="485" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A485">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B485">
+        <is>
+          <t xml:space="preserve">15:39:25</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C485">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D485">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E485">
+        <v>212394</v>
+      </c>
+      <c s="19" t="inlineStr" r="F485">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H485">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I485">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J485">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K485">
+        <is>
+          <t xml:space="preserve">5012469762</t>
+        </is>
+      </c>
+      <c s="20" r="L485">
+        <v>1972.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M485">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N485">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O485">
+        <is>
+          <t xml:space="preserve">0071</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P485">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação galvânica</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q485"/>
+      <c s="19" t="str" r="R485"/>
+      <c s="19" t="inlineStr" r="S485">
+        <is>
+          <t xml:space="preserve">2632005267</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T485"/>
+      <c s="19" t="inlineStr" r="U485">
+        <is>
+          <t xml:space="preserve">5001579519</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V485">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y485">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z485">
+        <is>
+          <t xml:space="preserve">10048823    </t>
+        </is>
+      </c>
+      <c s="20" r="AA485">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB485">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC485">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD485">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF485">
+        <is>
+          <t xml:space="preserve">2003683051</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG485"/>
+    </row>
+    <row r="486" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A486">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B486">
+        <is>
+          <t xml:space="preserve">15:40:57</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C486">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D486">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E486">
+        <v>212394</v>
+      </c>
+      <c s="16" t="inlineStr" r="F486">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H486">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I486">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J486">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K486">
+        <is>
+          <t xml:space="preserve">5012469769</t>
+        </is>
+      </c>
+      <c s="17" r="L486">
+        <v>661.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M486">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N486">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O486">
+        <is>
+          <t xml:space="preserve">0071</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P486">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação galvânica</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q486"/>
+      <c s="16" t="str" r="R486"/>
+      <c s="16" t="inlineStr" r="S486">
+        <is>
+          <t xml:space="preserve">2632005268</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T486"/>
+      <c s="16" t="inlineStr" r="U486">
+        <is>
+          <t xml:space="preserve">5001579556</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V486">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y486">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z486">
+        <is>
+          <t xml:space="preserve">10048823    </t>
+        </is>
+      </c>
+      <c s="17" r="AA486">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB486">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC486">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD486">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF486">
+        <is>
+          <t xml:space="preserve">2003683061</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG486"/>
+    </row>
+    <row r="487" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A487">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B487">
+        <is>
+          <t xml:space="preserve">15:42:54</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C487">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D487">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E487">
+        <v>207635</v>
+      </c>
+      <c s="19" t="inlineStr" r="F487">
+        <is>
+          <t xml:space="preserve">SUCATA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H487">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I487">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J487">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="K487"/>
+      <c s="20" r="L487">
+        <v>173.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M487">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N487">
+        <is>
+          <t xml:space="preserve">SUCATA</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O487"/>
+      <c s="19" t="str" r="P487"/>
+      <c s="19" t="str" r="Q487"/>
+      <c s="19" t="str" r="R487"/>
+      <c s="19" t="str" r="S487"/>
+      <c s="19" t="str" r="T487"/>
+      <c s="19" t="inlineStr" r="U487">
+        <is>
+          <t xml:space="preserve">5001579562</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V487">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y487">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z487">
+        <is>
+          <t xml:space="preserve">10048754    </t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AA487"/>
+      <c s="19" t="str" r="AB487"/>
+      <c s="19" t="inlineStr" r="AC487">
+        <is>
+          <t xml:space="preserve">transversal04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD487">
+        <is>
+          <t xml:space="preserve">AMS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF487">
+        <is>
+          <t xml:space="preserve">2003627070</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG487"/>
+    </row>
+    <row r="488" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A488">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B488">
+        <is>
+          <t xml:space="preserve">15:43:19</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C488">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D488">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E488">
+        <v>212394</v>
+      </c>
+      <c s="16" t="inlineStr" r="F488">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H488">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I488">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J488">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K488">
+        <is>
+          <t xml:space="preserve">5012469786</t>
+        </is>
+      </c>
+      <c s="17" r="L488">
+        <v>761.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M488">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N488">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O488">
+        <is>
+          <t xml:space="preserve">0071</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P488">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação galvânica</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q488"/>
+      <c s="16" t="str" r="R488"/>
+      <c s="16" t="inlineStr" r="S488">
+        <is>
+          <t xml:space="preserve">2632005269</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T488"/>
+      <c s="16" t="inlineStr" r="U488">
+        <is>
+          <t xml:space="preserve">5001579563</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V488">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y488">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z488">
+        <is>
+          <t xml:space="preserve">10048823    </t>
+        </is>
+      </c>
+      <c s="17" r="AA488">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB488">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC488">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD488">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF488">
+        <is>
+          <t xml:space="preserve">2003683109</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG488"/>
+    </row>
+    <row r="489" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A489">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B489">
+        <is>
+          <t xml:space="preserve">15:44:25</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C489">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D489">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E489">
+        <v>212394</v>
+      </c>
+      <c s="19" t="inlineStr" r="F489">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm ZIN 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H489">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I489">
+        <is>
+          <t xml:space="preserve">CINC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J489">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K489">
+        <is>
+          <t xml:space="preserve">5012469788</t>
+        </is>
+      </c>
+      <c s="20" r="L489">
+        <v>811.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M489">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N489">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O489">
+        <is>
+          <t xml:space="preserve">0071</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P489">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação galvânica</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q489"/>
+      <c s="19" t="str" r="R489"/>
+      <c s="19" t="inlineStr" r="S489">
+        <is>
+          <t xml:space="preserve">2632005270</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T489"/>
+      <c s="19" t="inlineStr" r="U489">
+        <is>
+          <t xml:space="preserve">5001579565</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V489">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y489">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z489">
+        <is>
+          <t xml:space="preserve">10048823    </t>
+        </is>
+      </c>
+      <c s="20" r="AA489">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB489">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC489">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD489">
+        <is>
+          <t xml:space="preserve">SYS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF489">
+        <is>
+          <t xml:space="preserve">2003683109</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG489"/>
+    </row>
+    <row r="490" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A490">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B490">
+        <is>
+          <t xml:space="preserve">15:48:31</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C490">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D490">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E490">
+        <v>208890</v>
+      </c>
+      <c s="16" t="inlineStr" r="F490">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,65mm LQ 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H490">
+        <is>
+          <t xml:space="preserve">2,65mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I490">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J490">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K490">
+        <is>
+          <t xml:space="preserve">5012469801</t>
+        </is>
+      </c>
+      <c s="17" r="L490">
+        <v>1758.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M490">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N490">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O490"/>
+      <c s="16" t="str" r="P490"/>
+      <c s="16" t="str" r="Q490"/>
+      <c s="16" t="str" r="R490"/>
+      <c s="16" t="inlineStr" r="S490">
+        <is>
+          <t xml:space="preserve">2633006603</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T490"/>
+      <c s="16" t="inlineStr" r="U490">
+        <is>
+          <t xml:space="preserve">5001579609</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V490">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y490">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z490">
+        <is>
+          <t xml:space="preserve">10048737    </t>
+        </is>
+      </c>
+      <c s="17" r="AA490">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB490">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC490">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD490">
+        <is>
+          <t xml:space="preserve">EFS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF490">
+        <is>
+          <t xml:space="preserve">2003853003</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG490"/>
+    </row>
+    <row r="491" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A491">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B491">
+        <is>
+          <t xml:space="preserve">15:48:52</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C491">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D491">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E491">
+        <v>208890</v>
+      </c>
+      <c s="19" t="inlineStr" r="F491">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,65mm LQ 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H491">
+        <is>
+          <t xml:space="preserve">2,65mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I491">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J491">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K491">
+        <is>
+          <t xml:space="preserve">5012469802</t>
+        </is>
+      </c>
+      <c s="20" r="L491">
+        <v>247.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M491">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N491">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O491">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P491">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q491"/>
+      <c s="19" t="str" r="R491"/>
+      <c s="19" t="inlineStr" r="S491">
+        <is>
+          <t xml:space="preserve">2633006604</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T491"/>
+      <c s="19" t="inlineStr" r="U491">
+        <is>
+          <t xml:space="preserve">5001579610</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V491">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y491">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z491">
+        <is>
+          <t xml:space="preserve">10048737    </t>
+        </is>
+      </c>
+      <c s="20" r="AA491">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB491">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC491">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD491">
+        <is>
+          <t xml:space="preserve">EFS</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF491">
+        <is>
+          <t xml:space="preserve">2003853003</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG491"/>
+    </row>
+    <row r="492" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A492">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B492">
+        <is>
+          <t xml:space="preserve">15:48:55</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C492">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D492">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E492">
+        <v>200584</v>
+      </c>
+      <c s="16" t="inlineStr" r="F492">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H492">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I492">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J492">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K492">
+        <is>
+          <t xml:space="preserve">5012469803</t>
+        </is>
+      </c>
+      <c s="17" r="L492">
+        <v>130.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M492">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N492">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O492">
+        <is>
+          <t xml:space="preserve">0072</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P492">
+        <is>
+          <t xml:space="preserve">TRV - Quebra de superfície</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q492"/>
+      <c s="16" t="str" r="R492"/>
+      <c s="16" t="inlineStr" r="S492">
+        <is>
+          <t xml:space="preserve">2632005271</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T492"/>
+      <c s="16" t="inlineStr" r="U492">
+        <is>
+          <t xml:space="preserve">5001579611</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V492">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y492">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z492">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="17" r="AA492">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB492">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC492">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD492"/>
+      <c s="16" t="inlineStr" r="AF492">
+        <is>
+          <t xml:space="preserve">2003967780</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG492"/>
+    </row>
+    <row r="493" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A493">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B493">
+        <is>
+          <t xml:space="preserve">15:59:24</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C493">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D493">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E493">
+        <v>200584</v>
+      </c>
+      <c s="19" t="inlineStr" r="F493">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H493">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I493">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J493">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K493">
+        <is>
+          <t xml:space="preserve">5012469821</t>
+        </is>
+      </c>
+      <c s="20" r="L493">
+        <v>1950.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M493">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N493">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O493"/>
+      <c s="19" t="str" r="P493"/>
+      <c s="19" t="str" r="Q493"/>
+      <c s="19" t="str" r="R493"/>
+      <c s="19" t="inlineStr" r="S493">
+        <is>
+          <t xml:space="preserve">2632005272</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T493"/>
+      <c s="19" t="inlineStr" r="U493">
+        <is>
+          <t xml:space="preserve">5001579649</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V493">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y493">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z493">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="20" r="AA493">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB493">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC493">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD493"/>
+      <c s="19" t="inlineStr" r="AF493">
+        <is>
+          <t xml:space="preserve">2003967780</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG493"/>
+    </row>
+    <row r="494" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A494">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B494">
+        <is>
+          <t xml:space="preserve">16:15:02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C494">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D494">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E494">
+        <v>208892</v>
+      </c>
+      <c s="16" t="inlineStr" r="F494">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,00mm LQ 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H494">
+        <is>
+          <t xml:space="preserve">2,00mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I494">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J494">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K494">
+        <is>
+          <t xml:space="preserve">5012469873</t>
+        </is>
+      </c>
+      <c s="17" r="L494">
+        <v>2068.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M494">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N494">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O494"/>
+      <c s="16" t="str" r="P494"/>
+      <c s="16" t="str" r="Q494"/>
+      <c s="16" t="str" r="R494"/>
+      <c s="16" t="inlineStr" r="S494">
+        <is>
+          <t xml:space="preserve">2633006605</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T494"/>
+      <c s="16" t="inlineStr" r="U494">
+        <is>
+          <t xml:space="preserve">5001579744</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V494">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y494">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z494">
+        <is>
+          <t xml:space="preserve">10048738    </t>
+        </is>
+      </c>
+      <c s="17" r="AA494">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB494">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC494">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD494">
+        <is>
+          <t xml:space="preserve">AES</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF494">
+        <is>
+          <t xml:space="preserve">2003882145</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG494"/>
+    </row>
+    <row r="495" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A495">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B495">
+        <is>
+          <t xml:space="preserve">16:22:46</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C495">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D495">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E495">
+        <v>200584</v>
+      </c>
+      <c s="19" t="inlineStr" r="F495">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H495">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I495">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J495">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K495">
+        <is>
+          <t xml:space="preserve">5012469887</t>
+        </is>
+      </c>
+      <c s="20" r="L495">
+        <v>2004.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M495">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N495">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O495"/>
+      <c s="19" t="str" r="P495"/>
+      <c s="19" t="str" r="Q495"/>
+      <c s="19" t="str" r="R495"/>
+      <c s="19" t="inlineStr" r="S495">
+        <is>
+          <t xml:space="preserve">2632005273</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T495"/>
+      <c s="19" t="inlineStr" r="U495">
+        <is>
+          <t xml:space="preserve">5001579788</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V495">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y495">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z495">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="20" r="AA495">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB495">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC495">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD495"/>
+      <c s="19" t="inlineStr" r="AF495">
+        <is>
+          <t xml:space="preserve">2003967780</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG495"/>
+    </row>
+    <row r="496" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A496">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B496">
+        <is>
+          <t xml:space="preserve">16:26:01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C496">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D496">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E496">
+        <v>208892</v>
+      </c>
+      <c s="16" t="inlineStr" r="F496">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,00mm LQ 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H496">
+        <is>
+          <t xml:space="preserve">2,00mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I496">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J496">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K496">
+        <is>
+          <t xml:space="preserve">5012469893</t>
+        </is>
+      </c>
+      <c s="17" r="L496">
+        <v>2065.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M496">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N496">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O496"/>
+      <c s="16" t="str" r="P496"/>
+      <c s="16" t="str" r="Q496"/>
+      <c s="16" t="str" r="R496"/>
+      <c s="16" t="inlineStr" r="S496">
+        <is>
+          <t xml:space="preserve">2633006606</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T496"/>
+      <c s="16" t="inlineStr" r="U496">
+        <is>
+          <t xml:space="preserve">5001579805</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V496">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y496">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z496">
+        <is>
+          <t xml:space="preserve">10048738    </t>
+        </is>
+      </c>
+      <c s="17" r="AA496">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB496">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC496">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD496">
+        <is>
+          <t xml:space="preserve">AES</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF496">
+        <is>
+          <t xml:space="preserve">2003882145</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG496"/>
+    </row>
+    <row r="497" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A497">
+        <is>
+          <t xml:space="preserve">08/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B497">
+        <is>
+          <t xml:space="preserve">16:42:26</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C497">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D497">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E497">
+        <v>208892</v>
+      </c>
+      <c s="19" t="inlineStr" r="F497">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,00mm LQ 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H497">
+        <is>
+          <t xml:space="preserve">2,00mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I497">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J497">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K497">
+        <is>
+          <t xml:space="preserve">5012469921</t>
+        </is>
+      </c>
+      <c s="20" r="L497">
+        <v>2057.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M497">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N497">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O497"/>
+      <c s="19" t="str" r="P497"/>
+      <c s="19" t="str" r="Q497"/>
+      <c s="19" t="str" r="R497"/>
+      <c s="19" t="inlineStr" r="S497">
+        <is>
+          <t xml:space="preserve">2633006607</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T497"/>
+      <c s="19" t="inlineStr" r="U497">
+        <is>
+          <t xml:space="preserve">5001579885</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V497">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y497">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z497">
+        <is>
+          <t xml:space="preserve">10048738    </t>
+        </is>
+      </c>
+      <c s="20" r="AA497">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB497">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC497">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD497">
+        <is>
+          <t xml:space="preserve">AES</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF497">
+        <is>
+          <t xml:space="preserve">2003882145</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG497"/>
+    </row>
+    <row r="498" ht="14.7" customHeight="1">
+      <c s="21" t="inlineStr" r="A498">
+        <is>
+          <t xml:space="preserve">Peso Total: 737715,000</t>
+        </is>
+      </c>
+      <c s="13" t="str" r="B498"/>
+      <c s="13" t="str" r="C498"/>
+      <c s="13" t="str" r="D498"/>
+      <c s="13" t="str" r="E498"/>
+      <c s="13" t="str" r="F498"/>
+      <c s="13" t="str" r="G498"/>
+      <c s="13" t="str" r="H498"/>
+      <c s="13" t="str" r="I498"/>
+      <c s="13" t="str" r="J498"/>
+      <c s="13" t="str" r="K498"/>
+      <c s="13" t="str" r="L498"/>
+      <c s="13" t="str" r="M498"/>
+      <c s="13" t="str" r="N498"/>
+      <c s="13" t="str" r="O498"/>
+      <c s="13" t="str" r="P498"/>
+      <c s="13" t="str" r="Q498"/>
+      <c s="13" t="str" r="R498"/>
+      <c s="13" t="str" r="S498"/>
+      <c s="13" t="str" r="T498"/>
+      <c s="13" t="str" r="U498"/>
+      <c s="13" t="str" r="V498"/>
+      <c s="13" t="str" r="W498"/>
+      <c s="13" t="str" r="X498"/>
+      <c s="13" t="str" r="Y498"/>
+      <c s="13" t="str" r="Z498"/>
+      <c s="13" t="str" r="AA498"/>
+      <c s="13" t="str" r="AB498"/>
+      <c s="13" t="str" r="AC498"/>
+      <c s="13" t="str" r="AD498"/>
+      <c s="13" t="str" r="AE498"/>
+      <c s="13" t="str" r="AF498"/>
+      <c s="14" t="str" r="AG498"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -49895,7 +57985,287 @@
     <mergeCell ref="V427:X427"/>
     <mergeCell ref="AD427:AE427"/>
     <mergeCell ref="AF427:AG427"/>
-    <mergeCell ref="A428:AG428"/>
+    <mergeCell ref="F428:G428"/>
+    <mergeCell ref="V428:X428"/>
+    <mergeCell ref="AD428:AE428"/>
+    <mergeCell ref="AF428:AG428"/>
+    <mergeCell ref="F429:G429"/>
+    <mergeCell ref="V429:X429"/>
+    <mergeCell ref="AD429:AE429"/>
+    <mergeCell ref="AF429:AG429"/>
+    <mergeCell ref="F430:G430"/>
+    <mergeCell ref="V430:X430"/>
+    <mergeCell ref="AD430:AE430"/>
+    <mergeCell ref="AF430:AG430"/>
+    <mergeCell ref="F431:G431"/>
+    <mergeCell ref="V431:X431"/>
+    <mergeCell ref="AD431:AE431"/>
+    <mergeCell ref="AF431:AG431"/>
+    <mergeCell ref="F432:G432"/>
+    <mergeCell ref="V432:X432"/>
+    <mergeCell ref="AD432:AE432"/>
+    <mergeCell ref="AF432:AG432"/>
+    <mergeCell ref="F433:G433"/>
+    <mergeCell ref="V433:X433"/>
+    <mergeCell ref="AD433:AE433"/>
+    <mergeCell ref="AF433:AG433"/>
+    <mergeCell ref="F434:G434"/>
+    <mergeCell ref="V434:X434"/>
+    <mergeCell ref="AD434:AE434"/>
+    <mergeCell ref="AF434:AG434"/>
+    <mergeCell ref="F435:G435"/>
+    <mergeCell ref="V435:X435"/>
+    <mergeCell ref="AD435:AE435"/>
+    <mergeCell ref="AF435:AG435"/>
+    <mergeCell ref="F436:G436"/>
+    <mergeCell ref="V436:X436"/>
+    <mergeCell ref="AD436:AE436"/>
+    <mergeCell ref="AF436:AG436"/>
+    <mergeCell ref="F437:G437"/>
+    <mergeCell ref="V437:X437"/>
+    <mergeCell ref="AD437:AE437"/>
+    <mergeCell ref="AF437:AG437"/>
+    <mergeCell ref="F438:G438"/>
+    <mergeCell ref="V438:X438"/>
+    <mergeCell ref="AD438:AE438"/>
+    <mergeCell ref="AF438:AG438"/>
+    <mergeCell ref="F439:G439"/>
+    <mergeCell ref="V439:X439"/>
+    <mergeCell ref="AD439:AE439"/>
+    <mergeCell ref="AF439:AG439"/>
+    <mergeCell ref="F440:G440"/>
+    <mergeCell ref="V440:X440"/>
+    <mergeCell ref="AD440:AE440"/>
+    <mergeCell ref="AF440:AG440"/>
+    <mergeCell ref="F441:G441"/>
+    <mergeCell ref="V441:X441"/>
+    <mergeCell ref="AD441:AE441"/>
+    <mergeCell ref="AF441:AG441"/>
+    <mergeCell ref="F442:G442"/>
+    <mergeCell ref="V442:X442"/>
+    <mergeCell ref="AD442:AE442"/>
+    <mergeCell ref="AF442:AG442"/>
+    <mergeCell ref="F443:G443"/>
+    <mergeCell ref="V443:X443"/>
+    <mergeCell ref="AD443:AE443"/>
+    <mergeCell ref="AF443:AG443"/>
+    <mergeCell ref="F444:G444"/>
+    <mergeCell ref="V444:X444"/>
+    <mergeCell ref="AD444:AE444"/>
+    <mergeCell ref="AF444:AG444"/>
+    <mergeCell ref="F445:G445"/>
+    <mergeCell ref="V445:X445"/>
+    <mergeCell ref="AD445:AE445"/>
+    <mergeCell ref="AF445:AG445"/>
+    <mergeCell ref="F446:G446"/>
+    <mergeCell ref="V446:X446"/>
+    <mergeCell ref="AD446:AE446"/>
+    <mergeCell ref="AF446:AG446"/>
+    <mergeCell ref="F447:G447"/>
+    <mergeCell ref="V447:X447"/>
+    <mergeCell ref="AD447:AE447"/>
+    <mergeCell ref="AF447:AG447"/>
+    <mergeCell ref="F448:G448"/>
+    <mergeCell ref="V448:X448"/>
+    <mergeCell ref="AD448:AE448"/>
+    <mergeCell ref="AF448:AG448"/>
+    <mergeCell ref="F449:G449"/>
+    <mergeCell ref="V449:X449"/>
+    <mergeCell ref="AD449:AE449"/>
+    <mergeCell ref="AF449:AG449"/>
+    <mergeCell ref="F450:G450"/>
+    <mergeCell ref="V450:X450"/>
+    <mergeCell ref="AD450:AE450"/>
+    <mergeCell ref="AF450:AG450"/>
+    <mergeCell ref="F451:G451"/>
+    <mergeCell ref="V451:X451"/>
+    <mergeCell ref="AD451:AE451"/>
+    <mergeCell ref="AF451:AG451"/>
+    <mergeCell ref="F452:G452"/>
+    <mergeCell ref="V452:X452"/>
+    <mergeCell ref="AD452:AE452"/>
+    <mergeCell ref="AF452:AG452"/>
+    <mergeCell ref="F453:G453"/>
+    <mergeCell ref="V453:X453"/>
+    <mergeCell ref="AD453:AE453"/>
+    <mergeCell ref="AF453:AG453"/>
+    <mergeCell ref="F454:G454"/>
+    <mergeCell ref="V454:X454"/>
+    <mergeCell ref="AD454:AE454"/>
+    <mergeCell ref="AF454:AG454"/>
+    <mergeCell ref="F455:G455"/>
+    <mergeCell ref="V455:X455"/>
+    <mergeCell ref="AD455:AE455"/>
+    <mergeCell ref="AF455:AG455"/>
+    <mergeCell ref="F456:G456"/>
+    <mergeCell ref="V456:X456"/>
+    <mergeCell ref="AD456:AE456"/>
+    <mergeCell ref="AF456:AG456"/>
+    <mergeCell ref="F457:G457"/>
+    <mergeCell ref="V457:X457"/>
+    <mergeCell ref="AD457:AE457"/>
+    <mergeCell ref="AF457:AG457"/>
+    <mergeCell ref="F458:G458"/>
+    <mergeCell ref="V458:X458"/>
+    <mergeCell ref="AD458:AE458"/>
+    <mergeCell ref="AF458:AG458"/>
+    <mergeCell ref="F459:G459"/>
+    <mergeCell ref="V459:X459"/>
+    <mergeCell ref="AD459:AE459"/>
+    <mergeCell ref="AF459:AG459"/>
+    <mergeCell ref="F460:G460"/>
+    <mergeCell ref="V460:X460"/>
+    <mergeCell ref="AD460:AE460"/>
+    <mergeCell ref="AF460:AG460"/>
+    <mergeCell ref="F461:G461"/>
+    <mergeCell ref="V461:X461"/>
+    <mergeCell ref="AD461:AE461"/>
+    <mergeCell ref="AF461:AG461"/>
+    <mergeCell ref="F462:G462"/>
+    <mergeCell ref="V462:X462"/>
+    <mergeCell ref="AD462:AE462"/>
+    <mergeCell ref="AF462:AG462"/>
+    <mergeCell ref="F463:G463"/>
+    <mergeCell ref="V463:X463"/>
+    <mergeCell ref="AD463:AE463"/>
+    <mergeCell ref="AF463:AG463"/>
+    <mergeCell ref="F464:G464"/>
+    <mergeCell ref="V464:X464"/>
+    <mergeCell ref="AD464:AE464"/>
+    <mergeCell ref="AF464:AG464"/>
+    <mergeCell ref="F465:G465"/>
+    <mergeCell ref="V465:X465"/>
+    <mergeCell ref="AD465:AE465"/>
+    <mergeCell ref="AF465:AG465"/>
+    <mergeCell ref="F466:G466"/>
+    <mergeCell ref="V466:X466"/>
+    <mergeCell ref="AD466:AE466"/>
+    <mergeCell ref="AF466:AG466"/>
+    <mergeCell ref="F467:G467"/>
+    <mergeCell ref="V467:X467"/>
+    <mergeCell ref="AD467:AE467"/>
+    <mergeCell ref="AF467:AG467"/>
+    <mergeCell ref="F468:G468"/>
+    <mergeCell ref="V468:X468"/>
+    <mergeCell ref="AD468:AE468"/>
+    <mergeCell ref="AF468:AG468"/>
+    <mergeCell ref="F469:G469"/>
+    <mergeCell ref="V469:X469"/>
+    <mergeCell ref="AD469:AE469"/>
+    <mergeCell ref="AF469:AG469"/>
+    <mergeCell ref="F470:G470"/>
+    <mergeCell ref="V470:X470"/>
+    <mergeCell ref="AD470:AE470"/>
+    <mergeCell ref="AF470:AG470"/>
+    <mergeCell ref="F471:G471"/>
+    <mergeCell ref="V471:X471"/>
+    <mergeCell ref="AD471:AE471"/>
+    <mergeCell ref="AF471:AG471"/>
+    <mergeCell ref="F472:G472"/>
+    <mergeCell ref="V472:X472"/>
+    <mergeCell ref="AD472:AE472"/>
+    <mergeCell ref="AF472:AG472"/>
+    <mergeCell ref="F473:G473"/>
+    <mergeCell ref="V473:X473"/>
+    <mergeCell ref="AD473:AE473"/>
+    <mergeCell ref="AF473:AG473"/>
+    <mergeCell ref="F474:G474"/>
+    <mergeCell ref="V474:X474"/>
+    <mergeCell ref="AD474:AE474"/>
+    <mergeCell ref="AF474:AG474"/>
+    <mergeCell ref="F475:G475"/>
+    <mergeCell ref="V475:X475"/>
+    <mergeCell ref="AD475:AE475"/>
+    <mergeCell ref="AF475:AG475"/>
+    <mergeCell ref="F476:G476"/>
+    <mergeCell ref="V476:X476"/>
+    <mergeCell ref="AD476:AE476"/>
+    <mergeCell ref="AF476:AG476"/>
+    <mergeCell ref="F477:G477"/>
+    <mergeCell ref="V477:X477"/>
+    <mergeCell ref="AD477:AE477"/>
+    <mergeCell ref="AF477:AG477"/>
+    <mergeCell ref="F478:G478"/>
+    <mergeCell ref="V478:X478"/>
+    <mergeCell ref="AD478:AE478"/>
+    <mergeCell ref="AF478:AG478"/>
+    <mergeCell ref="F479:G479"/>
+    <mergeCell ref="V479:X479"/>
+    <mergeCell ref="AD479:AE479"/>
+    <mergeCell ref="AF479:AG479"/>
+    <mergeCell ref="F480:G480"/>
+    <mergeCell ref="V480:X480"/>
+    <mergeCell ref="AD480:AE480"/>
+    <mergeCell ref="AF480:AG480"/>
+    <mergeCell ref="F481:G481"/>
+    <mergeCell ref="V481:X481"/>
+    <mergeCell ref="AD481:AE481"/>
+    <mergeCell ref="AF481:AG481"/>
+    <mergeCell ref="F482:G482"/>
+    <mergeCell ref="V482:X482"/>
+    <mergeCell ref="AD482:AE482"/>
+    <mergeCell ref="AF482:AG482"/>
+    <mergeCell ref="F483:G483"/>
+    <mergeCell ref="V483:X483"/>
+    <mergeCell ref="AD483:AE483"/>
+    <mergeCell ref="AF483:AG483"/>
+    <mergeCell ref="F484:G484"/>
+    <mergeCell ref="V484:X484"/>
+    <mergeCell ref="AD484:AE484"/>
+    <mergeCell ref="AF484:AG484"/>
+    <mergeCell ref="F485:G485"/>
+    <mergeCell ref="V485:X485"/>
+    <mergeCell ref="AD485:AE485"/>
+    <mergeCell ref="AF485:AG485"/>
+    <mergeCell ref="F486:G486"/>
+    <mergeCell ref="V486:X486"/>
+    <mergeCell ref="AD486:AE486"/>
+    <mergeCell ref="AF486:AG486"/>
+    <mergeCell ref="F487:G487"/>
+    <mergeCell ref="V487:X487"/>
+    <mergeCell ref="AD487:AE487"/>
+    <mergeCell ref="AF487:AG487"/>
+    <mergeCell ref="F488:G488"/>
+    <mergeCell ref="V488:X488"/>
+    <mergeCell ref="AD488:AE488"/>
+    <mergeCell ref="AF488:AG488"/>
+    <mergeCell ref="F489:G489"/>
+    <mergeCell ref="V489:X489"/>
+    <mergeCell ref="AD489:AE489"/>
+    <mergeCell ref="AF489:AG489"/>
+    <mergeCell ref="F490:G490"/>
+    <mergeCell ref="V490:X490"/>
+    <mergeCell ref="AD490:AE490"/>
+    <mergeCell ref="AF490:AG490"/>
+    <mergeCell ref="F491:G491"/>
+    <mergeCell ref="V491:X491"/>
+    <mergeCell ref="AD491:AE491"/>
+    <mergeCell ref="AF491:AG491"/>
+    <mergeCell ref="F492:G492"/>
+    <mergeCell ref="V492:X492"/>
+    <mergeCell ref="AD492:AE492"/>
+    <mergeCell ref="AF492:AG492"/>
+    <mergeCell ref="F493:G493"/>
+    <mergeCell ref="V493:X493"/>
+    <mergeCell ref="AD493:AE493"/>
+    <mergeCell ref="AF493:AG493"/>
+    <mergeCell ref="F494:G494"/>
+    <mergeCell ref="V494:X494"/>
+    <mergeCell ref="AD494:AE494"/>
+    <mergeCell ref="AF494:AG494"/>
+    <mergeCell ref="F495:G495"/>
+    <mergeCell ref="V495:X495"/>
+    <mergeCell ref="AD495:AE495"/>
+    <mergeCell ref="AF495:AG495"/>
+    <mergeCell ref="F496:G496"/>
+    <mergeCell ref="V496:X496"/>
+    <mergeCell ref="AD496:AE496"/>
+    <mergeCell ref="AF496:AG496"/>
+    <mergeCell ref="F497:G497"/>
+    <mergeCell ref="V497:X497"/>
+    <mergeCell ref="AD497:AE497"/>
+    <mergeCell ref="AF497:AG497"/>
+    <mergeCell ref="A498:AG498"/>
   </mergeCells>
   <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="0.393700787401575" header="0.393700787401575" footer="0.393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/Base_Producao.xlsx
+++ b/Base_Producao.xlsx
@@ -503,7 +503,7 @@
       <c s="4" t="str" r="A5"/>
       <c s="6" t="inlineStr" r="AE5">
         <is>
-          <t xml:space="preserve">Emissão: 09/10/2026</t>
+          <t xml:space="preserve">Emissão: 13/10/2026</t>
         </is>
       </c>
       <c s="7" t="str" r="AG5"/>
@@ -512,7 +512,7 @@
       <c s="4" t="str" r="A6"/>
       <c s="8" t="inlineStr" r="G6">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 08/10/2026</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 12/10/2026</t>
         </is>
       </c>
       <c s="7" t="str" r="AG6"/>
@@ -56277,45 +56277,4971 @@
       </c>
       <c s="7" t="str" r="AG497"/>
     </row>
-    <row r="498" ht="14.7" customHeight="1">
-      <c s="21" t="inlineStr" r="A498">
-        <is>
-          <t xml:space="preserve">Peso Total: 737715,000</t>
-        </is>
-      </c>
-      <c s="13" t="str" r="B498"/>
-      <c s="13" t="str" r="C498"/>
-      <c s="13" t="str" r="D498"/>
-      <c s="13" t="str" r="E498"/>
-      <c s="13" t="str" r="F498"/>
-      <c s="13" t="str" r="G498"/>
-      <c s="13" t="str" r="H498"/>
-      <c s="13" t="str" r="I498"/>
-      <c s="13" t="str" r="J498"/>
-      <c s="13" t="str" r="K498"/>
-      <c s="13" t="str" r="L498"/>
-      <c s="13" t="str" r="M498"/>
-      <c s="13" t="str" r="N498"/>
-      <c s="13" t="str" r="O498"/>
-      <c s="13" t="str" r="P498"/>
-      <c s="13" t="str" r="Q498"/>
-      <c s="13" t="str" r="R498"/>
-      <c s="13" t="str" r="S498"/>
-      <c s="13" t="str" r="T498"/>
-      <c s="13" t="str" r="U498"/>
-      <c s="13" t="str" r="V498"/>
-      <c s="13" t="str" r="W498"/>
-      <c s="13" t="str" r="X498"/>
-      <c s="13" t="str" r="Y498"/>
-      <c s="13" t="str" r="Z498"/>
-      <c s="13" t="str" r="AA498"/>
-      <c s="13" t="str" r="AB498"/>
-      <c s="13" t="str" r="AC498"/>
-      <c s="13" t="str" r="AD498"/>
-      <c s="13" t="str" r="AE498"/>
-      <c s="13" t="str" r="AF498"/>
-      <c s="14" t="str" r="AG498"/>
+    <row r="498" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A498">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B498">
+        <is>
+          <t xml:space="preserve">07:30:17</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C498">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D498">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E498">
+        <v>200584</v>
+      </c>
+      <c s="16" t="inlineStr" r="F498">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H498">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I498">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J498">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K498">
+        <is>
+          <t xml:space="preserve">5012471545</t>
+        </is>
+      </c>
+      <c s="17" r="L498">
+        <v>2003.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M498">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N498">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O498"/>
+      <c s="16" t="str" r="P498"/>
+      <c s="16" t="str" r="Q498"/>
+      <c s="16" t="str" r="R498"/>
+      <c s="16" t="inlineStr" r="S498">
+        <is>
+          <t xml:space="preserve">2632005274</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T498"/>
+      <c s="16" t="inlineStr" r="U498">
+        <is>
+          <t xml:space="preserve">5001582956</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V498">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y498">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z498">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="17" r="AA498">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB498">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC498">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD498"/>
+      <c s="16" t="inlineStr" r="AF498">
+        <is>
+          <t xml:space="preserve">2003967780</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG498"/>
     </row>
+    <row r="499" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A499">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B499">
+        <is>
+          <t xml:space="preserve">07:53:30</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C499">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D499">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E499">
+        <v>200584</v>
+      </c>
+      <c s="19" t="inlineStr" r="F499">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H499">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I499">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J499">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K499">
+        <is>
+          <t xml:space="preserve">5012471626</t>
+        </is>
+      </c>
+      <c s="20" r="L499">
+        <v>2005.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M499">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N499">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O499"/>
+      <c s="19" t="str" r="P499"/>
+      <c s="19" t="str" r="Q499"/>
+      <c s="19" t="str" r="R499"/>
+      <c s="19" t="inlineStr" r="S499">
+        <is>
+          <t xml:space="preserve">2632005275</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T499"/>
+      <c s="19" t="inlineStr" r="U499">
+        <is>
+          <t xml:space="preserve">5001583107</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V499">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y499">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z499">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="20" r="AA499">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB499">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC499">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD499"/>
+      <c s="19" t="inlineStr" r="AF499">
+        <is>
+          <t xml:space="preserve">2003967780</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG499"/>
+    </row>
+    <row r="500" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A500">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B500">
+        <is>
+          <t xml:space="preserve">08:07:12</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C500">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D500">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E500">
+        <v>208892</v>
+      </c>
+      <c s="16" t="inlineStr" r="F500">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,00mm LQ 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H500">
+        <is>
+          <t xml:space="preserve">2,00mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I500">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J500">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K500">
+        <is>
+          <t xml:space="preserve">5012471671</t>
+        </is>
+      </c>
+      <c s="17" r="L500">
+        <v>686.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M500">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N500">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O500"/>
+      <c s="16" t="str" r="P500"/>
+      <c s="16" t="str" r="Q500"/>
+      <c s="16" t="str" r="R500"/>
+      <c s="16" t="inlineStr" r="S500">
+        <is>
+          <t xml:space="preserve">2633006608</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T500"/>
+      <c s="16" t="inlineStr" r="U500">
+        <is>
+          <t xml:space="preserve">5001583204</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V500">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y500">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z500">
+        <is>
+          <t xml:space="preserve">10048738    </t>
+        </is>
+      </c>
+      <c s="17" r="AA500">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB500">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC500">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD500">
+        <is>
+          <t xml:space="preserve">AES</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF500">
+        <is>
+          <t xml:space="preserve">2003882145</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG500"/>
+    </row>
+    <row r="501" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A501">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B501">
+        <is>
+          <t xml:space="preserve">08:17:17</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C501">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D501">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E501">
+        <v>200584</v>
+      </c>
+      <c s="19" t="inlineStr" r="F501">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H501">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I501">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J501">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K501">
+        <is>
+          <t xml:space="preserve">5012471690</t>
+        </is>
+      </c>
+      <c s="20" r="L501">
+        <v>2007.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M501">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N501">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O501"/>
+      <c s="19" t="str" r="P501"/>
+      <c s="19" t="str" r="Q501"/>
+      <c s="19" t="str" r="R501"/>
+      <c s="19" t="inlineStr" r="S501">
+        <is>
+          <t xml:space="preserve">2632005276</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T501"/>
+      <c s="19" t="inlineStr" r="U501">
+        <is>
+          <t xml:space="preserve">5001583283</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V501">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y501">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z501">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="20" r="AA501">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB501">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC501">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD501"/>
+      <c s="19" t="inlineStr" r="AF501">
+        <is>
+          <t xml:space="preserve">2003967780</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG501"/>
+    </row>
+    <row r="502" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A502">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B502">
+        <is>
+          <t xml:space="preserve">08:33:05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C502">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D502">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E502">
+        <v>201131</v>
+      </c>
+      <c s="16" t="inlineStr" r="F502">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,00mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H502">
+        <is>
+          <t xml:space="preserve">2,00mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I502">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J502">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K502">
+        <is>
+          <t xml:space="preserve">5012471732</t>
+        </is>
+      </c>
+      <c s="17" r="L502">
+        <v>2043.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M502">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N502">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O502">
+        <is>
+          <t xml:space="preserve">0072</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P502">
+        <is>
+          <t xml:space="preserve">TRV - Quebra de superfície</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q502"/>
+      <c s="16" t="str" r="R502"/>
+      <c s="16" t="inlineStr" r="S502">
+        <is>
+          <t xml:space="preserve">2633006609</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T502"/>
+      <c s="16" t="inlineStr" r="U502">
+        <is>
+          <t xml:space="preserve">5001583395</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V502">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y502">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z502">
+        <is>
+          <t xml:space="preserve">10048739    </t>
+        </is>
+      </c>
+      <c s="17" r="AA502">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB502">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC502">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD502">
+        <is>
+          <t xml:space="preserve">AES</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF502">
+        <is>
+          <t xml:space="preserve">2003882145</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG502"/>
+    </row>
+    <row r="503" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A503">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B503">
+        <is>
+          <t xml:space="preserve">08:43:05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C503">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D503">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E503">
+        <v>201131</v>
+      </c>
+      <c s="19" t="inlineStr" r="F503">
+        <is>
+          <t xml:space="preserve">CH PLANA 2,00mm LQ 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H503">
+        <is>
+          <t xml:space="preserve">2,00mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I503">
+        <is>
+          <t xml:space="preserve">LQ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J503">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K503">
+        <is>
+          <t xml:space="preserve">5012471772</t>
+        </is>
+      </c>
+      <c s="20" r="L503">
+        <v>287.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M503">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N503">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O503">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P503">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q503"/>
+      <c s="19" t="str" r="R503"/>
+      <c s="19" t="inlineStr" r="S503">
+        <is>
+          <t xml:space="preserve">2633006610</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T503"/>
+      <c s="19" t="inlineStr" r="U503">
+        <is>
+          <t xml:space="preserve">5001583446</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V503">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y503">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z503">
+        <is>
+          <t xml:space="preserve">10048739    </t>
+        </is>
+      </c>
+      <c s="20" r="AA503">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB503">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC503">
+        <is>
+          <t xml:space="preserve">transversal02</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD503">
+        <is>
+          <t xml:space="preserve">AES</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF503">
+        <is>
+          <t xml:space="preserve">2003882145</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG503"/>
+    </row>
+    <row r="504" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A504">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B504">
+        <is>
+          <t xml:space="preserve">08:57:53</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C504">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D504">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E504">
+        <v>200584</v>
+      </c>
+      <c s="16" t="inlineStr" r="F504">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H504">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I504">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J504">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K504">
+        <is>
+          <t xml:space="preserve">5012471810</t>
+        </is>
+      </c>
+      <c s="17" r="L504">
+        <v>1863.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M504">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N504">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O504"/>
+      <c s="16" t="str" r="P504"/>
+      <c s="16" t="str" r="Q504"/>
+      <c s="16" t="str" r="R504"/>
+      <c s="16" t="inlineStr" r="S504">
+        <is>
+          <t xml:space="preserve">2632005277</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T504"/>
+      <c s="16" t="inlineStr" r="U504">
+        <is>
+          <t xml:space="preserve">5001583525</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V504">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y504">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z504">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="17" r="AA504">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB504">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC504">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD504"/>
+      <c s="16" t="inlineStr" r="AF504">
+        <is>
+          <t xml:space="preserve">2003967780</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG504"/>
+    </row>
+    <row r="505" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A505">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B505">
+        <is>
+          <t xml:space="preserve">08:59:01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C505">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D505">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E505">
+        <v>200584</v>
+      </c>
+      <c s="19" t="inlineStr" r="F505">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,43mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H505">
+        <is>
+          <t xml:space="preserve">0,43mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I505">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J505">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K505">
+        <is>
+          <t xml:space="preserve">5012471811</t>
+        </is>
+      </c>
+      <c s="20" r="L505">
+        <v>123.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M505">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N505">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O505">
+        <is>
+          <t xml:space="preserve">0168</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P505">
+        <is>
+          <t xml:space="preserve">TRV - Final de bobina</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q505"/>
+      <c s="19" t="str" r="R505"/>
+      <c s="19" t="inlineStr" r="S505">
+        <is>
+          <t xml:space="preserve">2632005278</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T505"/>
+      <c s="19" t="inlineStr" r="U505">
+        <is>
+          <t xml:space="preserve">5001583526</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V505">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y505">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z505">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="20" r="AA505">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB505">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC505">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD505"/>
+      <c s="19" t="inlineStr" r="AF505">
+        <is>
+          <t xml:space="preserve">2003967780</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG505"/>
+    </row>
+    <row r="506" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A506">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B506">
+        <is>
+          <t xml:space="preserve">09:07:46</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C506">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D506">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E506">
+        <v>200683</v>
+      </c>
+      <c s="16" t="inlineStr" r="F506">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H506">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I506">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J506">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K506">
+        <is>
+          <t xml:space="preserve">5012471843</t>
+        </is>
+      </c>
+      <c s="17" r="L506">
+        <v>157.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M506">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N506">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O506">
+        <is>
+          <t xml:space="preserve">0070</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P506">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q506"/>
+      <c s="16" t="str" r="R506"/>
+      <c s="16" t="inlineStr" r="S506">
+        <is>
+          <t xml:space="preserve">2632005279</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T506"/>
+      <c s="16" t="inlineStr" r="U506">
+        <is>
+          <t xml:space="preserve">5001583579</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V506">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y506">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z506">
+        <is>
+          <t xml:space="preserve">10048418    </t>
+        </is>
+      </c>
+      <c s="17" r="AA506">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB506">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC506">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD506"/>
+      <c s="16" t="inlineStr" r="AF506">
+        <is>
+          <t xml:space="preserve">2003643869</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG506"/>
+    </row>
+    <row r="507" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A507">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B507">
+        <is>
+          <t xml:space="preserve">09:19:52</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C507">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D507">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E507">
+        <v>200683</v>
+      </c>
+      <c s="19" t="inlineStr" r="F507">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H507">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I507">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J507">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K507">
+        <is>
+          <t xml:space="preserve">5012471888</t>
+        </is>
+      </c>
+      <c s="20" r="L507">
+        <v>2053.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M507">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N507">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O507"/>
+      <c s="19" t="str" r="P507"/>
+      <c s="19" t="str" r="Q507"/>
+      <c s="19" t="str" r="R507"/>
+      <c s="19" t="inlineStr" r="S507">
+        <is>
+          <t xml:space="preserve">2632005280</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T507"/>
+      <c s="19" t="inlineStr" r="U507">
+        <is>
+          <t xml:space="preserve">5001583659</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V507">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y507">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z507">
+        <is>
+          <t xml:space="preserve">10048418    </t>
+        </is>
+      </c>
+      <c s="20" r="AA507">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB507">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC507">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD507"/>
+      <c s="19" t="inlineStr" r="AF507">
+        <is>
+          <t xml:space="preserve">2003643869</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG507"/>
+    </row>
+    <row r="508" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A508">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B508">
+        <is>
+          <t xml:space="preserve">09:35:24</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C508">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D508">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E508">
+        <v>200683</v>
+      </c>
+      <c s="16" t="inlineStr" r="F508">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H508">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I508">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J508">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K508">
+        <is>
+          <t xml:space="preserve">5012471963</t>
+        </is>
+      </c>
+      <c s="17" r="L508">
+        <v>2048.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M508">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N508">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O508"/>
+      <c s="16" t="str" r="P508"/>
+      <c s="16" t="str" r="Q508"/>
+      <c s="16" t="str" r="R508"/>
+      <c s="16" t="inlineStr" r="S508">
+        <is>
+          <t xml:space="preserve">2632005281</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T508"/>
+      <c s="16" t="inlineStr" r="U508">
+        <is>
+          <t xml:space="preserve">5001583766</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V508">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y508">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z508">
+        <is>
+          <t xml:space="preserve">10048418    </t>
+        </is>
+      </c>
+      <c s="17" r="AA508">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB508">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC508">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD508"/>
+      <c s="16" t="inlineStr" r="AF508">
+        <is>
+          <t xml:space="preserve">2003643869</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG508"/>
+    </row>
+    <row r="509" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A509">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B509">
+        <is>
+          <t xml:space="preserve">09:51:26</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C509">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D509">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E509">
+        <v>200683</v>
+      </c>
+      <c s="19" t="inlineStr" r="F509">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H509">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I509">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J509">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K509">
+        <is>
+          <t xml:space="preserve">5012472003</t>
+        </is>
+      </c>
+      <c s="20" r="L509">
+        <v>2049.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M509">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N509">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O509"/>
+      <c s="19" t="str" r="P509"/>
+      <c s="19" t="str" r="Q509"/>
+      <c s="19" t="str" r="R509"/>
+      <c s="19" t="inlineStr" r="S509">
+        <is>
+          <t xml:space="preserve">2632005282</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T509"/>
+      <c s="19" t="inlineStr" r="U509">
+        <is>
+          <t xml:space="preserve">5001583886</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V509">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y509">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z509">
+        <is>
+          <t xml:space="preserve">10048418    </t>
+        </is>
+      </c>
+      <c s="20" r="AA509">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB509">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC509">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD509"/>
+      <c s="19" t="inlineStr" r="AF509">
+        <is>
+          <t xml:space="preserve">2003643869</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG509"/>
+    </row>
+    <row r="510" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A510">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B510">
+        <is>
+          <t xml:space="preserve">10:46:31</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C510">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D510">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E510">
+        <v>200683</v>
+      </c>
+      <c s="16" t="inlineStr" r="F510">
+        <is>
+          <t xml:space="preserve">CH PLANA 0,65mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H510">
+        <is>
+          <t xml:space="preserve">0,65mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I510">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J510">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K510">
+        <is>
+          <t xml:space="preserve">5012472234</t>
+        </is>
+      </c>
+      <c s="17" r="L510">
+        <v>1054.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M510">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N510">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O510">
+        <is>
+          <t xml:space="preserve">0071</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P510">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação galvânica</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="Q510"/>
+      <c s="16" t="str" r="R510"/>
+      <c s="16" t="inlineStr" r="S510">
+        <is>
+          <t xml:space="preserve">2632005283</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T510"/>
+      <c s="16" t="inlineStr" r="U510">
+        <is>
+          <t xml:space="preserve">5001584249</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V510">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y510">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z510">
+        <is>
+          <t xml:space="preserve">10048418    </t>
+        </is>
+      </c>
+      <c s="17" r="AA510">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB510">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC510">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AD510"/>
+      <c s="16" t="inlineStr" r="AF510">
+        <is>
+          <t xml:space="preserve">2003643869</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG510"/>
+    </row>
+    <row r="511" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A511">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B511">
+        <is>
+          <t xml:space="preserve">10:51:04</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C511">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D511">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E511">
+        <v>207635</v>
+      </c>
+      <c s="19" t="inlineStr" r="F511">
+        <is>
+          <t xml:space="preserve">SUCATA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H511">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I511">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J511">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="K511"/>
+      <c s="20" r="L511">
+        <v>639.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M511">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N511">
+        <is>
+          <t xml:space="preserve">SUCATA</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O511"/>
+      <c s="19" t="str" r="P511"/>
+      <c s="19" t="str" r="Q511"/>
+      <c s="19" t="str" r="R511"/>
+      <c s="19" t="str" r="S511"/>
+      <c s="19" t="str" r="T511"/>
+      <c s="19" t="inlineStr" r="U511">
+        <is>
+          <t xml:space="preserve">5001584292</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V511">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y511">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z511">
+        <is>
+          <t xml:space="preserve">10048418    </t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AA511"/>
+      <c s="19" t="str" r="AB511"/>
+      <c s="19" t="inlineStr" r="AC511">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="AD511"/>
+      <c s="19" t="inlineStr" r="AF511">
+        <is>
+          <t xml:space="preserve">2003643869</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG511"/>
+    </row>
+    <row r="512" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A512">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B512">
+        <is>
+          <t xml:space="preserve">11:18:35</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C512">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D512">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E512">
+        <v>201082</v>
+      </c>
+      <c s="16" t="inlineStr" r="F512">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H512">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I512">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J512">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K512">
+        <is>
+          <t xml:space="preserve">5012472378</t>
+        </is>
+      </c>
+      <c s="17" r="L512">
+        <v>2508.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M512">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N512">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O512"/>
+      <c s="16" t="str" r="P512"/>
+      <c s="16" t="str" r="Q512"/>
+      <c s="16" t="str" r="R512"/>
+      <c s="16" t="inlineStr" r="S512">
+        <is>
+          <t xml:space="preserve">2632005284</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T512"/>
+      <c s="16" t="inlineStr" r="U512">
+        <is>
+          <t xml:space="preserve">5001584461</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V512">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y512">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z512">
+        <is>
+          <t xml:space="preserve">10048939    </t>
+        </is>
+      </c>
+      <c s="17" r="AA512">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB512">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC512">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD512">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF512">
+        <is>
+          <t xml:space="preserve">2003921327</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG512"/>
+    </row>
+    <row r="513" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A513">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B513">
+        <is>
+          <t xml:space="preserve">11:44:52</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C513">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D513">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E513">
+        <v>201082</v>
+      </c>
+      <c s="19" t="inlineStr" r="F513">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H513">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I513">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J513">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K513">
+        <is>
+          <t xml:space="preserve">5012472433</t>
+        </is>
+      </c>
+      <c s="20" r="L513">
+        <v>2542.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M513">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N513">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O513"/>
+      <c s="19" t="str" r="P513"/>
+      <c s="19" t="str" r="Q513"/>
+      <c s="19" t="str" r="R513"/>
+      <c s="19" t="inlineStr" r="S513">
+        <is>
+          <t xml:space="preserve">2632005285</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T513"/>
+      <c s="19" t="inlineStr" r="U513">
+        <is>
+          <t xml:space="preserve">5001584913</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V513">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y513">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z513">
+        <is>
+          <t xml:space="preserve">10048939    </t>
+        </is>
+      </c>
+      <c s="20" r="AA513">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB513">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC513">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD513">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF513">
+        <is>
+          <t xml:space="preserve">2003921327</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG513"/>
+    </row>
+    <row r="514" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A514">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B514">
+        <is>
+          <t xml:space="preserve">12:36:29</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C514">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D514">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E514">
+        <v>201082</v>
+      </c>
+      <c s="16" t="inlineStr" r="F514">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H514">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I514">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J514">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K514">
+        <is>
+          <t xml:space="preserve">5012472564</t>
+        </is>
+      </c>
+      <c s="17" r="L514">
+        <v>2546.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M514">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N514">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O514"/>
+      <c s="16" t="str" r="P514"/>
+      <c s="16" t="str" r="Q514"/>
+      <c s="16" t="str" r="R514"/>
+      <c s="16" t="inlineStr" r="S514">
+        <is>
+          <t xml:space="preserve">2632005286</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T514"/>
+      <c s="16" t="inlineStr" r="U514">
+        <is>
+          <t xml:space="preserve">5001585141</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V514">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y514">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z514">
+        <is>
+          <t xml:space="preserve">10048939    </t>
+        </is>
+      </c>
+      <c s="17" r="AA514">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB514">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC514">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD514">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF514">
+        <is>
+          <t xml:space="preserve">2003921327</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG514"/>
+    </row>
+    <row r="515" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A515">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B515">
+        <is>
+          <t xml:space="preserve">12:43:43</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C515">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D515">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E515">
+        <v>201082</v>
+      </c>
+      <c s="19" t="inlineStr" r="F515">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H515">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I515">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J515">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K515">
+        <is>
+          <t xml:space="preserve">5012472604</t>
+        </is>
+      </c>
+      <c s="20" r="L515">
+        <v>2038.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M515">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N515">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O515"/>
+      <c s="19" t="str" r="P515"/>
+      <c s="19" t="str" r="Q515"/>
+      <c s="19" t="str" r="R515"/>
+      <c s="19" t="inlineStr" r="S515">
+        <is>
+          <t xml:space="preserve">2632005287</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T515"/>
+      <c s="19" t="inlineStr" r="U515">
+        <is>
+          <t xml:space="preserve">5001585176</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V515">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y515">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z515">
+        <is>
+          <t xml:space="preserve">10048939    </t>
+        </is>
+      </c>
+      <c s="20" r="AA515">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB515">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC515">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD515">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF515">
+        <is>
+          <t xml:space="preserve">2003921327</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG515"/>
+    </row>
+    <row r="516" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A516">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B516">
+        <is>
+          <t xml:space="preserve">12:50:30</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C516">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D516">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E516">
+        <v>201082</v>
+      </c>
+      <c s="16" t="inlineStr" r="F516">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H516">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I516">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J516">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K516">
+        <is>
+          <t xml:space="preserve">5012472624</t>
+        </is>
+      </c>
+      <c s="17" r="L516">
+        <v>2041.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M516">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N516">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O516"/>
+      <c s="16" t="str" r="P516"/>
+      <c s="16" t="str" r="Q516"/>
+      <c s="16" t="str" r="R516"/>
+      <c s="16" t="inlineStr" r="S516">
+        <is>
+          <t xml:space="preserve">2632005288</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T516"/>
+      <c s="16" t="inlineStr" r="U516">
+        <is>
+          <t xml:space="preserve">5001585197</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V516">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y516">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z516">
+        <is>
+          <t xml:space="preserve">10048939    </t>
+        </is>
+      </c>
+      <c s="17" r="AA516">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB516">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC516">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD516">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF516">
+        <is>
+          <t xml:space="preserve">2003921327</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG516"/>
+    </row>
+    <row r="517" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A517">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B517">
+        <is>
+          <t xml:space="preserve">13:16:36</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C517">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D517">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E517">
+        <v>201082</v>
+      </c>
+      <c s="19" t="inlineStr" r="F517">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H517">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I517">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J517">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K517">
+        <is>
+          <t xml:space="preserve">5012472718</t>
+        </is>
+      </c>
+      <c s="20" r="L517">
+        <v>2414.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M517">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N517">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O517"/>
+      <c s="19" t="str" r="P517"/>
+      <c s="19" t="str" r="Q517"/>
+      <c s="19" t="str" r="R517"/>
+      <c s="19" t="inlineStr" r="S517">
+        <is>
+          <t xml:space="preserve">2632005289</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T517"/>
+      <c s="19" t="inlineStr" r="U517">
+        <is>
+          <t xml:space="preserve">5001585310</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V517">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y517">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z517">
+        <is>
+          <t xml:space="preserve">10048939    </t>
+        </is>
+      </c>
+      <c s="20" r="AA517">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB517">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC517">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD517">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF517">
+        <is>
+          <t xml:space="preserve">2003921327</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG517"/>
+    </row>
+    <row r="518" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A518">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B518">
+        <is>
+          <t xml:space="preserve">13:16:57</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C518">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D518">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E518">
+        <v>207635</v>
+      </c>
+      <c s="16" t="inlineStr" r="F518">
+        <is>
+          <t xml:space="preserve">SUCATA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H518">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I518">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J518">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="K518"/>
+      <c s="17" r="L518">
+        <v>41.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M518">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N518">
+        <is>
+          <t xml:space="preserve">SUCATA</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O518"/>
+      <c s="16" t="str" r="P518"/>
+      <c s="16" t="str" r="Q518"/>
+      <c s="16" t="str" r="R518"/>
+      <c s="16" t="str" r="S518"/>
+      <c s="16" t="str" r="T518"/>
+      <c s="16" t="inlineStr" r="U518">
+        <is>
+          <t xml:space="preserve">5001585312</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V518">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y518">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z518">
+        <is>
+          <t xml:space="preserve">10048939    </t>
+        </is>
+      </c>
+      <c s="16" t="str" r="AA518"/>
+      <c s="16" t="str" r="AB518"/>
+      <c s="16" t="inlineStr" r="AC518">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD518">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF518">
+        <is>
+          <t xml:space="preserve">2003921327</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG518"/>
+    </row>
+    <row r="519" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A519">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B519">
+        <is>
+          <t xml:space="preserve">13:22:36</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C519">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D519">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E519">
+        <v>201083</v>
+      </c>
+      <c s="19" t="inlineStr" r="F519">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H519">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I519">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J519">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K519">
+        <is>
+          <t xml:space="preserve">5012472742</t>
+        </is>
+      </c>
+      <c s="20" r="L519">
+        <v>2030.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M519">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N519">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O519"/>
+      <c s="19" t="str" r="P519"/>
+      <c s="19" t="str" r="Q519"/>
+      <c s="19" t="str" r="R519"/>
+      <c s="19" t="inlineStr" r="S519">
+        <is>
+          <t xml:space="preserve">2632005290</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T519"/>
+      <c s="19" t="inlineStr" r="U519">
+        <is>
+          <t xml:space="preserve">5001585356</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V519">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y519">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z519">
+        <is>
+          <t xml:space="preserve">10048941    </t>
+        </is>
+      </c>
+      <c s="20" r="AA519">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB519">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC519">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD519">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF519">
+        <is>
+          <t xml:space="preserve">2003922689</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG519"/>
+    </row>
+    <row r="520" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A520">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B520">
+        <is>
+          <t xml:space="preserve">13:29:13</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C520">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D520">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E520">
+        <v>201083</v>
+      </c>
+      <c s="16" t="inlineStr" r="F520">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H520">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I520">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J520">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K520">
+        <is>
+          <t xml:space="preserve">5012472762</t>
+        </is>
+      </c>
+      <c s="17" r="L520">
+        <v>2581.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M520">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N520">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O520"/>
+      <c s="16" t="str" r="P520"/>
+      <c s="16" t="str" r="Q520"/>
+      <c s="16" t="str" r="R520"/>
+      <c s="16" t="inlineStr" r="S520">
+        <is>
+          <t xml:space="preserve">2632005291</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T520"/>
+      <c s="16" t="inlineStr" r="U520">
+        <is>
+          <t xml:space="preserve">5001585396</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V520">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y520">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z520">
+        <is>
+          <t xml:space="preserve">10048941    </t>
+        </is>
+      </c>
+      <c s="17" r="AA520">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB520">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC520">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD520">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF520">
+        <is>
+          <t xml:space="preserve">2003922689</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG520"/>
+    </row>
+    <row r="521" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A521">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B521">
+        <is>
+          <t xml:space="preserve">13:36:56</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C521">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D521">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E521">
+        <v>201083</v>
+      </c>
+      <c s="19" t="inlineStr" r="F521">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H521">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I521">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J521">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K521">
+        <is>
+          <t xml:space="preserve">5012472788</t>
+        </is>
+      </c>
+      <c s="20" r="L521">
+        <v>2581.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M521">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N521">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O521"/>
+      <c s="19" t="str" r="P521"/>
+      <c s="19" t="str" r="Q521"/>
+      <c s="19" t="str" r="R521"/>
+      <c s="19" t="inlineStr" r="S521">
+        <is>
+          <t xml:space="preserve">2632005292</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T521"/>
+      <c s="19" t="inlineStr" r="U521">
+        <is>
+          <t xml:space="preserve">5001585426</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V521">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y521">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z521">
+        <is>
+          <t xml:space="preserve">10048941    </t>
+        </is>
+      </c>
+      <c s="20" r="AA521">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB521">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC521">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD521">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF521">
+        <is>
+          <t xml:space="preserve">2003922689</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG521"/>
+    </row>
+    <row r="522" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A522">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B522">
+        <is>
+          <t xml:space="preserve">13:45:26</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C522">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D522">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E522">
+        <v>201083</v>
+      </c>
+      <c s="16" t="inlineStr" r="F522">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H522">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I522">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J522">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K522">
+        <is>
+          <t xml:space="preserve">5012472845</t>
+        </is>
+      </c>
+      <c s="17" r="L522">
+        <v>2581.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M522">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N522">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O522"/>
+      <c s="16" t="str" r="P522"/>
+      <c s="16" t="str" r="Q522"/>
+      <c s="16" t="str" r="R522"/>
+      <c s="16" t="inlineStr" r="S522">
+        <is>
+          <t xml:space="preserve">2632005293</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T522"/>
+      <c s="16" t="inlineStr" r="U522">
+        <is>
+          <t xml:space="preserve">5001585499</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V522">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y522">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z522">
+        <is>
+          <t xml:space="preserve">10048941    </t>
+        </is>
+      </c>
+      <c s="17" r="AA522">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB522">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC522">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD522">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF522">
+        <is>
+          <t xml:space="preserve">2003922689</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG522"/>
+    </row>
+    <row r="523" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A523">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B523">
+        <is>
+          <t xml:space="preserve">13:51:18</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C523">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D523">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E523">
+        <v>201083</v>
+      </c>
+      <c s="19" t="inlineStr" r="F523">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H523">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I523">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J523">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K523">
+        <is>
+          <t xml:space="preserve">5012472894</t>
+        </is>
+      </c>
+      <c s="20" r="L523">
+        <v>2032.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M523">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N523">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O523"/>
+      <c s="19" t="str" r="P523"/>
+      <c s="19" t="str" r="Q523"/>
+      <c s="19" t="str" r="R523"/>
+      <c s="19" t="inlineStr" r="S523">
+        <is>
+          <t xml:space="preserve">2632005294</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T523"/>
+      <c s="19" t="inlineStr" r="U523">
+        <is>
+          <t xml:space="preserve">5001585558</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V523">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y523">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z523">
+        <is>
+          <t xml:space="preserve">10048941    </t>
+        </is>
+      </c>
+      <c s="20" r="AA523">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB523">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC523">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD523">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF523">
+        <is>
+          <t xml:space="preserve">2003922689</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG523"/>
+    </row>
+    <row r="524" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A524">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B524">
+        <is>
+          <t xml:space="preserve">14:11:06</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C524">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D524">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E524">
+        <v>201083</v>
+      </c>
+      <c s="16" t="inlineStr" r="F524">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,50mm LF 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H524">
+        <is>
+          <t xml:space="preserve">1,50mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I524">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J524">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K524">
+        <is>
+          <t xml:space="preserve">5012472961</t>
+        </is>
+      </c>
+      <c s="17" r="L524">
+        <v>2161.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M524">
+        <is>
+          <t xml:space="preserve">TURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N524">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O524"/>
+      <c s="16" t="str" r="P524"/>
+      <c s="16" t="str" r="Q524"/>
+      <c s="16" t="str" r="R524"/>
+      <c s="16" t="inlineStr" r="S524">
+        <is>
+          <t xml:space="preserve">2632005295</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T524"/>
+      <c s="16" t="inlineStr" r="U524">
+        <is>
+          <t xml:space="preserve">5001585666</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V524">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y524">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z524">
+        <is>
+          <t xml:space="preserve">10048941    </t>
+        </is>
+      </c>
+      <c s="17" r="AA524">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB524">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC524">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD524">
+        <is>
+          <t xml:space="preserve">PCO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF524">
+        <is>
+          <t xml:space="preserve">2003922689</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG524"/>
+    </row>
+    <row r="525" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A525">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B525">
+        <is>
+          <t xml:space="preserve">14:20:05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C525">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D525">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E525">
+        <v>200738</v>
+      </c>
+      <c s="19" t="inlineStr" r="F525">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H525">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I525">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J525">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K525">
+        <is>
+          <t xml:space="preserve">5012472984</t>
+        </is>
+      </c>
+      <c s="20" r="L525">
+        <v>2012.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M525">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N525">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O525"/>
+      <c s="19" t="str" r="P525"/>
+      <c s="19" t="str" r="Q525"/>
+      <c s="19" t="str" r="R525"/>
+      <c s="19" t="inlineStr" r="S525">
+        <is>
+          <t xml:space="preserve">2632005296</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T525"/>
+      <c s="19" t="inlineStr" r="U525">
+        <is>
+          <t xml:space="preserve">5001585750</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V525">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y525">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z525">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="20" r="AA525">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB525">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC525">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD525">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF525">
+        <is>
+          <t xml:space="preserve">2003896836</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG525"/>
+    </row>
+    <row r="526" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A526">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B526">
+        <is>
+          <t xml:space="preserve">14:27:00</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C526">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D526">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E526">
+        <v>200738</v>
+      </c>
+      <c s="16" t="inlineStr" r="F526">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H526">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I526">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J526">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K526">
+        <is>
+          <t xml:space="preserve">5012472995</t>
+        </is>
+      </c>
+      <c s="17" r="L526">
+        <v>1994.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M526">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N526">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O526"/>
+      <c s="16" t="str" r="P526"/>
+      <c s="16" t="str" r="Q526"/>
+      <c s="16" t="str" r="R526"/>
+      <c s="16" t="inlineStr" r="S526">
+        <is>
+          <t xml:space="preserve">2632005297</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T526"/>
+      <c s="16" t="inlineStr" r="U526">
+        <is>
+          <t xml:space="preserve">5001585790</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V526">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y526">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z526">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="17" r="AA526">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB526">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC526">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD526">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF526">
+        <is>
+          <t xml:space="preserve">2003896836</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG526"/>
+    </row>
+    <row r="527" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A527">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B527">
+        <is>
+          <t xml:space="preserve">14:34:59</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C527">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D527">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E527">
+        <v>200738</v>
+      </c>
+      <c s="19" t="inlineStr" r="F527">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H527">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I527">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J527">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K527">
+        <is>
+          <t xml:space="preserve">5012473009</t>
+        </is>
+      </c>
+      <c s="20" r="L527">
+        <v>2022.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M527">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N527">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O527"/>
+      <c s="19" t="str" r="P527"/>
+      <c s="19" t="str" r="Q527"/>
+      <c s="19" t="str" r="R527"/>
+      <c s="19" t="inlineStr" r="S527">
+        <is>
+          <t xml:space="preserve">2632005298</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T527"/>
+      <c s="19" t="inlineStr" r="U527">
+        <is>
+          <t xml:space="preserve">5001585834</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V527">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y527">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z527">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="20" r="AA527">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB527">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC527">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD527">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF527">
+        <is>
+          <t xml:space="preserve">2003896836</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG527"/>
+    </row>
+    <row r="528" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A528">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B528">
+        <is>
+          <t xml:space="preserve">14:55:16</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C528">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D528">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E528">
+        <v>200738</v>
+      </c>
+      <c s="16" t="inlineStr" r="F528">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H528">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I528">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J528">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K528">
+        <is>
+          <t xml:space="preserve">5012473044</t>
+        </is>
+      </c>
+      <c s="17" r="L528">
+        <v>1056.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M528">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N528">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O528"/>
+      <c s="16" t="str" r="P528"/>
+      <c s="16" t="str" r="Q528"/>
+      <c s="16" t="str" r="R528"/>
+      <c s="16" t="inlineStr" r="S528">
+        <is>
+          <t xml:space="preserve">2632005299</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T528"/>
+      <c s="16" t="inlineStr" r="U528">
+        <is>
+          <t xml:space="preserve">5001586001</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V528">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y528">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z528">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="17" r="AA528">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB528">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC528">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD528">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF528">
+        <is>
+          <t xml:space="preserve">2003896836</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG528"/>
+    </row>
+    <row r="529" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A529">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B529">
+        <is>
+          <t xml:space="preserve">14:56:22</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C529">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D529">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E529">
+        <v>200738</v>
+      </c>
+      <c s="19" t="inlineStr" r="F529">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H529">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I529">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J529">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K529">
+        <is>
+          <t xml:space="preserve">5012473046</t>
+        </is>
+      </c>
+      <c s="20" r="L529">
+        <v>422.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M529">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N529">
+        <is>
+          <t xml:space="preserve">PNC</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="O529">
+        <is>
+          <t xml:space="preserve">0071</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="P529">
+        <is>
+          <t xml:space="preserve">TRV - Oxidação galvânica</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="Q529"/>
+      <c s="19" t="str" r="R529"/>
+      <c s="19" t="inlineStr" r="S529">
+        <is>
+          <t xml:space="preserve">2632005300</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T529"/>
+      <c s="19" t="inlineStr" r="U529">
+        <is>
+          <t xml:space="preserve">5001586003</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V529">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y529">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z529">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="20" r="AA529">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB529">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC529">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD529">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF529">
+        <is>
+          <t xml:space="preserve">2003908529</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG529"/>
+    </row>
+    <row r="530" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A530">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B530">
+        <is>
+          <t xml:space="preserve">15:03:20</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C530">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D530">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E530">
+        <v>200738</v>
+      </c>
+      <c s="16" t="inlineStr" r="F530">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H530">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I530">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J530">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K530">
+        <is>
+          <t xml:space="preserve">5012473054</t>
+        </is>
+      </c>
+      <c s="17" r="L530">
+        <v>2016.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M530">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N530">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O530"/>
+      <c s="16" t="str" r="P530"/>
+      <c s="16" t="str" r="Q530"/>
+      <c s="16" t="str" r="R530"/>
+      <c s="16" t="inlineStr" r="S530">
+        <is>
+          <t xml:space="preserve">2632005301</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T530"/>
+      <c s="16" t="inlineStr" r="U530">
+        <is>
+          <t xml:space="preserve">5001586062</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V530">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y530">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z530">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="17" r="AA530">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB530">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC530">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD530">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF530">
+        <is>
+          <t xml:space="preserve">2003908529</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG530"/>
+    </row>
+    <row r="531" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A531">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B531">
+        <is>
+          <t xml:space="preserve">15:11:38</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C531">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D531">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E531">
+        <v>200738</v>
+      </c>
+      <c s="19" t="inlineStr" r="F531">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H531">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I531">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J531">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K531">
+        <is>
+          <t xml:space="preserve">5012473087</t>
+        </is>
+      </c>
+      <c s="20" r="L531">
+        <v>2016.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M531">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N531">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O531"/>
+      <c s="19" t="str" r="P531"/>
+      <c s="19" t="str" r="Q531"/>
+      <c s="19" t="str" r="R531"/>
+      <c s="19" t="inlineStr" r="S531">
+        <is>
+          <t xml:space="preserve">2632005302</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T531"/>
+      <c s="19" t="inlineStr" r="U531">
+        <is>
+          <t xml:space="preserve">5001586113</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V531">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y531">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z531">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="20" r="AA531">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB531">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC531">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD531">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF531">
+        <is>
+          <t xml:space="preserve">2003908529</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG531"/>
+    </row>
+    <row r="532" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A532">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B532">
+        <is>
+          <t xml:space="preserve">15:22:59</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C532">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D532">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E532">
+        <v>200738</v>
+      </c>
+      <c s="16" t="inlineStr" r="F532">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H532">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I532">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J532">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K532">
+        <is>
+          <t xml:space="preserve">5012473119</t>
+        </is>
+      </c>
+      <c s="17" r="L532">
+        <v>2013.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M532">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N532">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O532"/>
+      <c s="16" t="str" r="P532"/>
+      <c s="16" t="str" r="Q532"/>
+      <c s="16" t="str" r="R532"/>
+      <c s="16" t="inlineStr" r="S532">
+        <is>
+          <t xml:space="preserve">2632005303</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T532"/>
+      <c s="16" t="inlineStr" r="U532">
+        <is>
+          <t xml:space="preserve">5001586161</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V532">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y532">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z532">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="17" r="AA532">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB532">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC532">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD532">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF532">
+        <is>
+          <t xml:space="preserve">2003908529</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG532"/>
+    </row>
+    <row r="533" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A533">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B533">
+        <is>
+          <t xml:space="preserve">15:36:07</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C533">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D533">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E533">
+        <v>201079</v>
+      </c>
+      <c s="19" t="inlineStr" r="F533">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H533">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I533">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J533">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K533">
+        <is>
+          <t xml:space="preserve">5012473148</t>
+        </is>
+      </c>
+      <c s="20" r="L533">
+        <v>1095.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M533">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N533">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O533"/>
+      <c s="19" t="str" r="P533"/>
+      <c s="19" t="str" r="Q533"/>
+      <c s="19" t="str" r="R533"/>
+      <c s="19" t="inlineStr" r="S533">
+        <is>
+          <t xml:space="preserve">2636005846</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T533"/>
+      <c s="19" t="inlineStr" r="U533">
+        <is>
+          <t xml:space="preserve">5001586215</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V533">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y533">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z533">
+        <is>
+          <t xml:space="preserve">10048016    </t>
+        </is>
+      </c>
+      <c s="20" r="AA533">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB533">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC533">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD533">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF533">
+        <is>
+          <t xml:space="preserve">2003992553</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG533"/>
+    </row>
+    <row r="534" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A534">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B534">
+        <is>
+          <t xml:space="preserve">15:42:51</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C534">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D534">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E534">
+        <v>200738</v>
+      </c>
+      <c s="16" t="inlineStr" r="F534">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 2000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H534">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I534">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J534">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K534">
+        <is>
+          <t xml:space="preserve">5012473162</t>
+        </is>
+      </c>
+      <c s="17" r="L534">
+        <v>911.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M534">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N534">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O534"/>
+      <c s="16" t="str" r="P534"/>
+      <c s="16" t="str" r="Q534"/>
+      <c s="16" t="str" r="R534"/>
+      <c s="16" t="inlineStr" r="S534">
+        <is>
+          <t xml:space="preserve">2632005304</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T534"/>
+      <c s="16" t="inlineStr" r="U534">
+        <is>
+          <t xml:space="preserve">5001586253</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V534">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y534">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z534">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="17" r="AA534">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB534">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC534">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD534">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF534">
+        <is>
+          <t xml:space="preserve">2003908529</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG534"/>
+    </row>
+    <row r="535" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A535">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B535">
+        <is>
+          <t xml:space="preserve">15:46:07</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C535">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D535">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E535">
+        <v>201079</v>
+      </c>
+      <c s="19" t="inlineStr" r="F535">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H535">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I535">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J535">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K535">
+        <is>
+          <t xml:space="preserve">5012473167</t>
+        </is>
+      </c>
+      <c s="20" r="L535">
+        <v>1096.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M535">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N535">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O535"/>
+      <c s="19" t="str" r="P535"/>
+      <c s="19" t="str" r="Q535"/>
+      <c s="19" t="str" r="R535"/>
+      <c s="19" t="inlineStr" r="S535">
+        <is>
+          <t xml:space="preserve">2636005847</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T535"/>
+      <c s="19" t="inlineStr" r="U535">
+        <is>
+          <t xml:space="preserve">5001586257</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V535">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y535">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z535">
+        <is>
+          <t xml:space="preserve">10048016    </t>
+        </is>
+      </c>
+      <c s="20" r="AA535">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB535">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC535">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD535">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF535">
+        <is>
+          <t xml:space="preserve">2003992553</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG535"/>
+    </row>
+    <row r="536" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A536">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B536">
+        <is>
+          <t xml:space="preserve">15:47:25</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C536">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D536">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E536">
+        <v>200758</v>
+      </c>
+      <c s="16" t="inlineStr" r="F536">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H536">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I536">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J536">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K536">
+        <is>
+          <t xml:space="preserve">5012473172</t>
+        </is>
+      </c>
+      <c s="17" r="L536">
+        <v>2008.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M536">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N536">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O536"/>
+      <c s="16" t="str" r="P536"/>
+      <c s="16" t="str" r="Q536"/>
+      <c s="16" t="str" r="R536"/>
+      <c s="16" t="inlineStr" r="S536">
+        <is>
+          <t xml:space="preserve">2632005305</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T536"/>
+      <c s="16" t="inlineStr" r="U536">
+        <is>
+          <t xml:space="preserve">5001586282</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V536">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y536">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z536">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="17" r="AA536">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB536">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC536">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD536">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF536">
+        <is>
+          <t xml:space="preserve">2003896821</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG536"/>
+    </row>
+    <row r="537" ht="15.55" customHeight="0">
+      <c s="18" t="inlineStr" r="A537">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B537">
+        <is>
+          <t xml:space="preserve">15:54:35</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C537">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D537">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E537">
+        <v>201079</v>
+      </c>
+      <c s="19" t="inlineStr" r="F537">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,20mm LF 6000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H537">
+        <is>
+          <t xml:space="preserve">1,20mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I537">
+        <is>
+          <t xml:space="preserve">LF</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J537">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K537">
+        <is>
+          <t xml:space="preserve">5012473194</t>
+        </is>
+      </c>
+      <c s="20" r="L537">
+        <v>1095.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M537">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N537">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O537"/>
+      <c s="19" t="str" r="P537"/>
+      <c s="19" t="str" r="Q537"/>
+      <c s="19" t="str" r="R537"/>
+      <c s="19" t="inlineStr" r="S537">
+        <is>
+          <t xml:space="preserve">2636005848</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T537"/>
+      <c s="19" t="inlineStr" r="U537">
+        <is>
+          <t xml:space="preserve">5001586307</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V537">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y537">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z537">
+        <is>
+          <t xml:space="preserve">10048016    </t>
+        </is>
+      </c>
+      <c s="20" r="AA537">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB537">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC537">
+        <is>
+          <t xml:space="preserve">transversal05</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD537">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF537">
+        <is>
+          <t xml:space="preserve">2003992553</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG537"/>
+    </row>
+    <row r="538" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A538">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B538">
+        <is>
+          <t xml:space="preserve">15:59:25</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C538">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D538">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E538">
+        <v>200758</v>
+      </c>
+      <c s="16" t="inlineStr" r="F538">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H538">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I538">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J538">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K538">
+        <is>
+          <t xml:space="preserve">5012473206</t>
+        </is>
+      </c>
+      <c s="17" r="L538">
+        <v>2005.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M538">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N538">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O538"/>
+      <c s="16" t="str" r="P538"/>
+      <c s="16" t="str" r="Q538"/>
+      <c s="16" t="str" r="R538"/>
+      <c s="16" t="inlineStr" r="S538">
+        <is>
+          <t xml:space="preserve">2632005306</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T538"/>
+      <c s="16" t="inlineStr" r="U538">
+        <is>
+          <t xml:space="preserve">5001586319</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V538">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y538">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z538">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="17" r="AA538">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB538">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC538">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD538">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF538">
+        <is>
+          <t xml:space="preserve">2003896821</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG538"/>
+    </row>
+    <row r="539" ht="15.6" customHeight="0">
+      <c s="18" t="inlineStr" r="A539">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="B539">
+        <is>
+          <t xml:space="preserve">16:09:49</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C539">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D539">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="20" r="E539">
+        <v>200758</v>
+      </c>
+      <c s="19" t="inlineStr" r="F539">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="H539">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="I539">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="J539">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="K539">
+        <is>
+          <t xml:space="preserve">5012473215</t>
+        </is>
+      </c>
+      <c s="20" r="L539">
+        <v>1997.000</v>
+      </c>
+      <c s="19" t="inlineStr" r="M539">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="N539">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="O539"/>
+      <c s="19" t="str" r="P539"/>
+      <c s="19" t="str" r="Q539"/>
+      <c s="19" t="str" r="R539"/>
+      <c s="19" t="inlineStr" r="S539">
+        <is>
+          <t xml:space="preserve">2632005307</t>
+        </is>
+      </c>
+      <c s="19" t="str" r="T539"/>
+      <c s="19" t="inlineStr" r="U539">
+        <is>
+          <t xml:space="preserve">5001586337</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="V539">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Y539">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="Z539">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="20" r="AA539">
+        <v>0</v>
+      </c>
+      <c s="20" r="AB539">
+        <v>0</v>
+      </c>
+      <c s="19" t="inlineStr" r="AC539">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AD539">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="AF539">
+        <is>
+          <t xml:space="preserve">2003896821</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG539"/>
+    </row>
+    <row r="540" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A540">
+        <is>
+          <t xml:space="preserve">09/10/2026</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B540">
+        <is>
+          <t xml:space="preserve">16:38:05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="C540">
+        <is>
+          <t xml:space="preserve">ACI - MATRIZ</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="D540">
+        <is>
+          <t xml:space="preserve">TRAN</t>
+        </is>
+      </c>
+      <c s="17" r="E540">
+        <v>200758</v>
+      </c>
+      <c s="16" t="inlineStr" r="F540">
+        <is>
+          <t xml:space="preserve">CH PLANA 1,25mm GA 3000mm X 1200mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="H540">
+        <is>
+          <t xml:space="preserve">1,25mm</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="I540">
+        <is>
+          <t xml:space="preserve">GA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="J540">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K540">
+        <is>
+          <t xml:space="preserve">5012473301</t>
+        </is>
+      </c>
+      <c s="17" r="L540">
+        <v>842.000</v>
+      </c>
+      <c s="16" t="inlineStr" r="M540">
+        <is>
+          <t xml:space="preserve">TURB</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="N540">
+        <is>
+          <t xml:space="preserve">BOM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="O540"/>
+      <c s="16" t="str" r="P540"/>
+      <c s="16" t="str" r="Q540"/>
+      <c s="16" t="str" r="R540"/>
+      <c s="16" t="inlineStr" r="S540">
+        <is>
+          <t xml:space="preserve">2632005308</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="T540"/>
+      <c s="16" t="inlineStr" r="U540">
+        <is>
+          <t xml:space="preserve">5001586509</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="V540">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Y540">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="Z540">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="17" r="AA540">
+        <v>0</v>
+      </c>
+      <c s="17" r="AB540">
+        <v>0</v>
+      </c>
+      <c s="16" t="inlineStr" r="AC540">
+        <is>
+          <t xml:space="preserve">transversal01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AD540">
+        <is>
+          <t xml:space="preserve">HOA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="AF540">
+        <is>
+          <t xml:space="preserve">2003896821</t>
+        </is>
+      </c>
+      <c s="7" t="str" r="AG540"/>
+    </row>
+    <row r="541" ht="14.7" customHeight="1">
+      <c s="21" t="inlineStr" r="A541">
+        <is>
+          <t xml:space="preserve">Peso Total: 809428,000</t>
+        </is>
+      </c>
+      <c s="13" t="str" r="B541"/>
+      <c s="13" t="str" r="C541"/>
+      <c s="13" t="str" r="D541"/>
+      <c s="13" t="str" r="E541"/>
+      <c s="13" t="str" r="F541"/>
+      <c s="13" t="str" r="G541"/>
+      <c s="13" t="str" r="H541"/>
+      <c s="13" t="str" r="I541"/>
+      <c s="13" t="str" r="J541"/>
+      <c s="13" t="str" r="K541"/>
+      <c s="13" t="str" r="L541"/>
+      <c s="13" t="str" r="M541"/>
+      <c s="13" t="str" r="N541"/>
+      <c s="13" t="str" r="O541"/>
+      <c s="13" t="str" r="P541"/>
+      <c s="13" t="str" r="Q541"/>
+      <c s="13" t="str" r="R541"/>
+      <c s="13" t="str" r="S541"/>
+      <c s="13" t="str" r="T541"/>
+      <c s="13" t="str" r="U541"/>
+      <c s="13" t="str" r="V541"/>
+      <c s="13" t="str" r="W541"/>
+      <c s="13" t="str" r="X541"/>
+      <c s="13" t="str" r="Y541"/>
+      <c s="13" t="str" r="Z541"/>
+      <c s="13" t="str" r="AA541"/>
+      <c s="13" t="str" r="AB541"/>
+      <c s="13" t="str" r="AC541"/>
+      <c s="13" t="str" r="AD541"/>
+      <c s="13" t="str" r="AE541"/>
+      <c s="13" t="str" r="AF541"/>
+      <c s="14" t="str" r="AG541"/>
+    </row>
+    <row r="542" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A2:B6"/>
@@ -58265,7 +63191,179 @@
     <mergeCell ref="V497:X497"/>
     <mergeCell ref="AD497:AE497"/>
     <mergeCell ref="AF497:AG497"/>
-    <mergeCell ref="A498:AG498"/>
+    <mergeCell ref="F498:G498"/>
+    <mergeCell ref="V498:X498"/>
+    <mergeCell ref="AD498:AE498"/>
+    <mergeCell ref="AF498:AG498"/>
+    <mergeCell ref="F499:G499"/>
+    <mergeCell ref="V499:X499"/>
+    <mergeCell ref="AD499:AE499"/>
+    <mergeCell ref="AF499:AG499"/>
+    <mergeCell ref="F500:G500"/>
+    <mergeCell ref="V500:X500"/>
+    <mergeCell ref="AD500:AE500"/>
+    <mergeCell ref="AF500:AG500"/>
+    <mergeCell ref="F501:G501"/>
+    <mergeCell ref="V501:X501"/>
+    <mergeCell ref="AD501:AE501"/>
+    <mergeCell ref="AF501:AG501"/>
+    <mergeCell ref="F502:G502"/>
+    <mergeCell ref="V502:X502"/>
+    <mergeCell ref="AD502:AE502"/>
+    <mergeCell ref="AF502:AG502"/>
+    <mergeCell ref="F503:G503"/>
+    <mergeCell ref="V503:X503"/>
+    <mergeCell ref="AD503:AE503"/>
+    <mergeCell ref="AF503:AG503"/>
+    <mergeCell ref="F504:G504"/>
+    <mergeCell ref="V504:X504"/>
+    <mergeCell ref="AD504:AE504"/>
+    <mergeCell ref="AF504:AG504"/>
+    <mergeCell ref="F505:G505"/>
+    <mergeCell ref="V505:X505"/>
+    <mergeCell ref="AD505:AE505"/>
+    <mergeCell ref="AF505:AG505"/>
+    <mergeCell ref="F506:G506"/>
+    <mergeCell ref="V506:X506"/>
+    <mergeCell ref="AD506:AE506"/>
+    <mergeCell ref="AF506:AG506"/>
+    <mergeCell ref="F507:G507"/>
+    <mergeCell ref="V507:X507"/>
+    <mergeCell ref="AD507:AE507"/>
+    <mergeCell ref="AF507:AG507"/>
+    <mergeCell ref="F508:G508"/>
+    <mergeCell ref="V508:X508"/>
+    <mergeCell ref="AD508:AE508"/>
+    <mergeCell ref="AF508:AG508"/>
+    <mergeCell ref="F509:G509"/>
+    <mergeCell ref="V509:X509"/>
+    <mergeCell ref="AD509:AE509"/>
+    <mergeCell ref="AF509:AG509"/>
+    <mergeCell ref="F510:G510"/>
+    <mergeCell ref="V510:X510"/>
+    <mergeCell ref="AD510:AE510"/>
+    <mergeCell ref="AF510:AG510"/>
+    <mergeCell ref="F511:G511"/>
+    <mergeCell ref="V511:X511"/>
+    <mergeCell ref="AD511:AE511"/>
+    <mergeCell ref="AF511:AG511"/>
+    <mergeCell ref="F512:G512"/>
+    <mergeCell ref="V512:X512"/>
+    <mergeCell ref="AD512:AE512"/>
+    <mergeCell ref="AF512:AG512"/>
+    <mergeCell ref="F513:G513"/>
+    <mergeCell ref="V513:X513"/>
+    <mergeCell ref="AD513:AE513"/>
+    <mergeCell ref="AF513:AG513"/>
+    <mergeCell ref="F514:G514"/>
+    <mergeCell ref="V514:X514"/>
+    <mergeCell ref="AD514:AE514"/>
+    <mergeCell ref="AF514:AG514"/>
+    <mergeCell ref="F515:G515"/>
+    <mergeCell ref="V515:X515"/>
+    <mergeCell ref="AD515:AE515"/>
+    <mergeCell ref="AF515:AG515"/>
+    <mergeCell ref="F516:G516"/>
+    <mergeCell ref="V516:X516"/>
+    <mergeCell ref="AD516:AE516"/>
+    <mergeCell ref="AF516:AG516"/>
+    <mergeCell ref="F517:G517"/>
+    <mergeCell ref="V517:X517"/>
+    <mergeCell ref="AD517:AE517"/>
+    <mergeCell ref="AF517:AG517"/>
+    <mergeCell ref="F518:G518"/>
+    <mergeCell ref="V518:X518"/>
+    <mergeCell ref="AD518:AE518"/>
+    <mergeCell ref="AF518:AG518"/>
+    <mergeCell ref="F519:G519"/>
+    <mergeCell ref="V519:X519"/>
+    <mergeCell ref="AD519:AE519"/>
+    <mergeCell ref="AF519:AG519"/>
+    <mergeCell ref="F520:G520"/>
+    <mergeCell ref="V520:X520"/>
+    <mergeCell ref="AD520:AE520"/>
+    <mergeCell ref="AF520:AG520"/>
+    <mergeCell ref="F521:G521"/>
+    <mergeCell ref="V521:X521"/>
+    <mergeCell ref="AD521:AE521"/>
+    <mergeCell ref="AF521:AG521"/>
+    <mergeCell ref="F522:G522"/>
+    <mergeCell ref="V522:X522"/>
+    <mergeCell ref="AD522:AE522"/>
+    <mergeCell ref="AF522:AG522"/>
+    <mergeCell ref="F523:G523"/>
+    <mergeCell ref="V523:X523"/>
+    <mergeCell ref="AD523:AE523"/>
+    <mergeCell ref="AF523:AG523"/>
+    <mergeCell ref="F524:G524"/>
+    <mergeCell ref="V524:X524"/>
+    <mergeCell ref="AD524:AE524"/>
+    <mergeCell ref="AF524:AG524"/>
+    <mergeCell ref="F525:G525"/>
+    <mergeCell ref="V525:X525"/>
+    <mergeCell ref="AD525:AE525"/>
+    <mergeCell ref="AF525:AG525"/>
+    <mergeCell ref="F526:G526"/>
+    <mergeCell ref="V526:X526"/>
+    <mergeCell ref="AD526:AE526"/>
+    <mergeCell ref="AF526:AG526"/>
+    <mergeCell ref="F527:G527"/>
+    <mergeCell ref="V527:X527"/>
+    <mergeCell ref="AD527:AE527"/>
+    <mergeCell ref="AF527:AG527"/>
+    <mergeCell ref="F528:G528"/>
+    <mergeCell ref="V528:X528"/>
+    <mergeCell ref="AD528:AE528"/>
+    <mergeCell ref="AF528:AG528"/>
+    <mergeCell ref="F529:G529"/>
+    <mergeCell ref="V529:X529"/>
+    <mergeCell ref="AD529:AE529"/>
+    <mergeCell ref="AF529:AG529"/>
+    <mergeCell ref="F530:G530"/>
+    <mergeCell ref="V530:X530"/>
+    <mergeCell ref="AD530:AE530"/>
+    <mergeCell ref="AF530:AG530"/>
+    <mergeCell ref="F531:G531"/>
+    <mergeCell ref="V531:X531"/>
+    <mergeCell ref="AD531:AE531"/>
+    <mergeCell ref="AF531:AG531"/>
+    <mergeCell ref="F532:G532"/>
+    <mergeCell ref="V532:X532"/>
+    <mergeCell ref="AD532:AE532"/>
+    <mergeCell ref="AF532:AG532"/>
+    <mergeCell ref="F533:G533"/>
+    <mergeCell ref="V533:X533"/>
+    <mergeCell ref="AD533:AE533"/>
+    <mergeCell ref="AF533:AG533"/>
+    <mergeCell ref="F534:G534"/>
+    <mergeCell ref="V534:X534"/>
+    <mergeCell ref="AD534:AE534"/>
+    <mergeCell ref="AF534:AG534"/>
+    <mergeCell ref="F535:G535"/>
+    <mergeCell ref="V535:X535"/>
+    <mergeCell ref="AD535:AE535"/>
+    <mergeCell ref="AF535:AG535"/>
+    <mergeCell ref="F536:G536"/>
+    <mergeCell ref="V536:X536"/>
+    <mergeCell ref="AD536:AE536"/>
+    <mergeCell ref="AF536:AG536"/>
+    <mergeCell ref="F537:G537"/>
+    <mergeCell ref="V537:X537"/>
+    <mergeCell ref="AD537:AE537"/>
+    <mergeCell ref="AF537:AG537"/>
+    <mergeCell ref="F538:G538"/>
+    <mergeCell ref="V538:X538"/>
+    <mergeCell ref="AD538:AE538"/>
+    <mergeCell ref="AF538:AG538"/>
+    <mergeCell ref="F539:G539"/>
+    <mergeCell ref="V539:X539"/>
+    <mergeCell ref="AD539:AE539"/>
+    <mergeCell ref="AF539:AG539"/>
+    <mergeCell ref="F540:G540"/>
+    <mergeCell ref="V540:X540"/>
+    <mergeCell ref="AD540:AE540"/>
+    <mergeCell ref="AF540:AG540"/>
+    <mergeCell ref="A541:AG541"/>
   </mergeCells>
   <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="0.393700787401575" header="0.393700787401575" footer="0.393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
